--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121742198</v>
+        <v>121742191</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564489</v>
+        <v>564496</v>
       </c>
       <c r="R2" t="n">
-        <v>6991655</v>
+        <v>6991571</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,6 +754,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Lunglav på flera granar samt sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121742191</v>
+        <v>121742198</v>
       </c>
       <c r="B3" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564496</v>
+        <v>564489</v>
       </c>
       <c r="R3" t="n">
-        <v>6991571</v>
+        <v>6991655</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,11 +865,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lunglav på flera granar samt sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1106,7 +1106,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121798905</v>
+        <v>121798890</v>
       </c>
       <c r="B6" t="n">
         <v>79726</v>
@@ -1146,13 +1146,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564433</v>
+        <v>564502</v>
       </c>
       <c r="R6" t="n">
-        <v>6991692</v>
+        <v>6991645</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121798188</v>
+        <v>121798373</v>
       </c>
       <c r="B7" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,21 +1224,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,13 +1248,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564369</v>
+        <v>564425</v>
       </c>
       <c r="R7" t="n">
-        <v>6991688</v>
+        <v>6991636</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Lunglav på björk</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121798373</v>
+        <v>121797975</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>79697</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,21 +1331,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,13 +1355,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564425</v>
+        <v>564433</v>
       </c>
       <c r="R8" t="n">
-        <v>6991636</v>
+        <v>6991692</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1391,11 +1391,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121798890</v>
+        <v>121798905</v>
       </c>
       <c r="B9" t="n">
         <v>79726</v>
@@ -1462,13 +1457,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564502</v>
+        <v>564433</v>
       </c>
       <c r="R9" t="n">
-        <v>6991645</v>
+        <v>6991692</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1524,7 +1519,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121797975</v>
+        <v>121798188</v>
       </c>
       <c r="B10" t="n">
         <v>79697</v>
@@ -1564,13 +1559,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564433</v>
+        <v>564369</v>
       </c>
       <c r="R10" t="n">
-        <v>6991692</v>
+        <v>6991688</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1600,6 +1595,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121742191</v>
+        <v>121742198</v>
       </c>
       <c r="B2" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564496</v>
+        <v>564489</v>
       </c>
       <c r="R2" t="n">
-        <v>6991571</v>
+        <v>6991655</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,11 +754,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Lunglav på flera granar samt sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121742198</v>
+        <v>121742191</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564489</v>
+        <v>564496</v>
       </c>
       <c r="R3" t="n">
-        <v>6991655</v>
+        <v>6991571</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,6 +860,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lunglav på flera granar samt sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121798890</v>
+        <v>121797975</v>
       </c>
       <c r="B6" t="n">
-        <v>79726</v>
+        <v>79697</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,25 +1118,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,13 +1146,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564502</v>
+        <v>564433</v>
       </c>
       <c r="R6" t="n">
-        <v>6991645</v>
+        <v>6991692</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121798373</v>
+        <v>121798890</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>79726</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,25 +1220,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564425</v>
+        <v>564502</v>
       </c>
       <c r="R7" t="n">
-        <v>6991636</v>
+        <v>6991645</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1284,11 +1284,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121797975</v>
+        <v>121797957</v>
       </c>
       <c r="B8" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,21 +1326,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,13 +1350,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564433</v>
+        <v>564365</v>
       </c>
       <c r="R8" t="n">
-        <v>6991692</v>
+        <v>6991638</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1391,6 +1386,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121798905</v>
+        <v>121798373</v>
       </c>
       <c r="B9" t="n">
-        <v>79726</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,13 +1457,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564433</v>
+        <v>564425</v>
       </c>
       <c r="R9" t="n">
-        <v>6991692</v>
+        <v>6991636</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1493,6 +1493,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1519,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121798188</v>
+        <v>121798905</v>
       </c>
       <c r="B10" t="n">
-        <v>79697</v>
+        <v>79726</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,25 +1536,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1559,13 +1564,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564369</v>
+        <v>564433</v>
       </c>
       <c r="R10" t="n">
-        <v>6991688</v>
+        <v>6991692</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1595,11 +1600,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,10 +1626,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121797957</v>
+        <v>121798188</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>79697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,21 +1642,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1666,13 +1666,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564365</v>
+        <v>564369</v>
       </c>
       <c r="R11" t="n">
-        <v>6991638</v>
+        <v>6991688</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121742191</v>
+        <v>121742429</v>
       </c>
       <c r="B3" t="n">
-        <v>79697</v>
+        <v>97067</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +793,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564496</v>
+        <v>564502</v>
       </c>
       <c r="R3" t="n">
-        <v>6991571</v>
+        <v>6991645</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -860,11 +861,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lunglav på flera granar samt sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121742429</v>
+        <v>121742191</v>
       </c>
       <c r="B4" t="n">
-        <v>97067</v>
+        <v>79697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,31 +900,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564502</v>
+        <v>564496</v>
       </c>
       <c r="R4" t="n">
-        <v>6991645</v>
+        <v>6991571</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -972,6 +967,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Lunglav på flera granar samt sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121797975</v>
+        <v>121797957</v>
       </c>
       <c r="B6" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,21 +1122,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,13 +1146,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564433</v>
+        <v>564365</v>
       </c>
       <c r="R6" t="n">
-        <v>6991692</v>
+        <v>6991638</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,6 +1182,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121798890</v>
+        <v>121797975</v>
       </c>
       <c r="B7" t="n">
-        <v>79726</v>
+        <v>79697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,25 +1225,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,13 +1253,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564502</v>
+        <v>564433</v>
       </c>
       <c r="R7" t="n">
-        <v>6991645</v>
+        <v>6991692</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1315,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121797957</v>
+        <v>121798373</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1350,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564365</v>
+        <v>564425</v>
       </c>
       <c r="R8" t="n">
-        <v>6991638</v>
+        <v>6991636</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1390,7 +1395,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121798373</v>
+        <v>121798905</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>79726</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,13 +1462,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564425</v>
+        <v>564433</v>
       </c>
       <c r="R9" t="n">
-        <v>6991636</v>
+        <v>6991692</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1493,11 +1498,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,7 +1524,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121798905</v>
+        <v>121798890</v>
       </c>
       <c r="B10" t="n">
         <v>79726</v>
@@ -1564,13 +1564,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564433</v>
+        <v>564502</v>
       </c>
       <c r="R10" t="n">
-        <v>6991692</v>
+        <v>6991645</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121742198</v>
+        <v>121742429</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564489</v>
+        <v>564502</v>
       </c>
       <c r="R2" t="n">
-        <v>6991655</v>
+        <v>6991645</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121742429</v>
+        <v>121742198</v>
       </c>
       <c r="B3" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,31 +794,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564502</v>
+        <v>564489</v>
       </c>
       <c r="R3" t="n">
-        <v>6991645</v>
+        <v>6991655</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121797975</v>
+        <v>121798188</v>
       </c>
       <c r="B7" t="n">
         <v>79697</v>
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564433</v>
+        <v>564369</v>
       </c>
       <c r="R7" t="n">
-        <v>6991692</v>
+        <v>6991688</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1289,6 +1289,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121798373</v>
+        <v>121798905</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>79726</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,25 +1332,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,13 +1360,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564425</v>
+        <v>564433</v>
       </c>
       <c r="R8" t="n">
-        <v>6991636</v>
+        <v>6991692</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1391,11 +1396,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,7 +1422,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121798905</v>
+        <v>121798890</v>
       </c>
       <c r="B9" t="n">
         <v>79726</v>
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564433</v>
+        <v>564502</v>
       </c>
       <c r="R9" t="n">
-        <v>6991692</v>
+        <v>6991645</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121798890</v>
+        <v>121797975</v>
       </c>
       <c r="B10" t="n">
-        <v>79726</v>
+        <v>79697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,25 +1536,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1564,13 +1564,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564502</v>
+        <v>564433</v>
       </c>
       <c r="R10" t="n">
-        <v>6991645</v>
+        <v>6991692</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121798188</v>
+        <v>121798373</v>
       </c>
       <c r="B11" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,21 +1642,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1666,13 +1666,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564369</v>
+        <v>564425</v>
       </c>
       <c r="R11" t="n">
-        <v>6991688</v>
+        <v>6991636</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Lunglav på björk</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121742429</v>
+        <v>121742191</v>
       </c>
       <c r="B2" t="n">
-        <v>97067</v>
+        <v>79697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564502</v>
+        <v>564496</v>
       </c>
       <c r="R2" t="n">
-        <v>6991645</v>
+        <v>6991571</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -755,6 +754,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Lunglav på flera granar samt sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -888,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121742191</v>
+        <v>121742429</v>
       </c>
       <c r="B4" t="n">
-        <v>79697</v>
+        <v>97067</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,30 +904,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564496</v>
+        <v>564502</v>
       </c>
       <c r="R4" t="n">
-        <v>6991571</v>
+        <v>6991645</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -967,11 +972,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Lunglav på flera granar samt sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121797957</v>
+        <v>121798905</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>79726</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,25 +1118,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,13 +1146,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564365</v>
+        <v>564433</v>
       </c>
       <c r="R6" t="n">
-        <v>6991638</v>
+        <v>6991692</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,11 +1182,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,7 +1208,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121798188</v>
+        <v>121797975</v>
       </c>
       <c r="B7" t="n">
         <v>79697</v>
@@ -1253,13 +1248,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564369</v>
+        <v>564433</v>
       </c>
       <c r="R7" t="n">
-        <v>6991688</v>
+        <v>6991692</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1289,11 +1284,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121798905</v>
+        <v>121797957</v>
       </c>
       <c r="B8" t="n">
-        <v>79726</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,25 +1322,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1360,13 +1350,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564433</v>
+        <v>564365</v>
       </c>
       <c r="R8" t="n">
-        <v>6991692</v>
+        <v>6991638</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1396,6 +1386,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1524,7 +1519,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121797975</v>
+        <v>121798188</v>
       </c>
       <c r="B10" t="n">
         <v>79697</v>
@@ -1564,13 +1559,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564433</v>
+        <v>564369</v>
       </c>
       <c r="R10" t="n">
-        <v>6991692</v>
+        <v>6991688</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1600,6 +1595,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121742191</v>
+        <v>121742429</v>
       </c>
       <c r="B2" t="n">
-        <v>79697</v>
+        <v>97067</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564496</v>
+        <v>564502</v>
       </c>
       <c r="R2" t="n">
-        <v>6991571</v>
+        <v>6991645</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -754,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Lunglav på flera granar samt sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121742198</v>
+        <v>121742191</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564489</v>
+        <v>564496</v>
       </c>
       <c r="R3" t="n">
-        <v>6991655</v>
+        <v>6991571</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,6 +861,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lunglav på flera granar samt sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121742429</v>
+        <v>121742198</v>
       </c>
       <c r="B4" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,31 +905,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564502</v>
+        <v>564489</v>
       </c>
       <c r="R4" t="n">
-        <v>6991645</v>
+        <v>6991655</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121797975</v>
+        <v>121797957</v>
       </c>
       <c r="B7" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,21 +1224,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,13 +1248,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564433</v>
+        <v>564365</v>
       </c>
       <c r="R7" t="n">
-        <v>6991692</v>
+        <v>6991638</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,6 +1284,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121797957</v>
+        <v>121798890</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>79726</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,25 +1327,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564365</v>
+        <v>564502</v>
       </c>
       <c r="R8" t="n">
-        <v>6991638</v>
+        <v>6991645</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1386,11 +1391,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121798890</v>
+        <v>121798188</v>
       </c>
       <c r="B9" t="n">
-        <v>79726</v>
+        <v>79697</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,13 +1457,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564502</v>
+        <v>564369</v>
       </c>
       <c r="R9" t="n">
-        <v>6991645</v>
+        <v>6991688</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1493,6 +1493,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1519,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121798188</v>
+        <v>121798373</v>
       </c>
       <c r="B10" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1559,13 +1564,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564369</v>
+        <v>564425</v>
       </c>
       <c r="R10" t="n">
-        <v>6991688</v>
+        <v>6991636</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1599,7 +1604,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Lunglav på björk</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121798373</v>
+        <v>121797975</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>79697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,21 +1647,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1666,13 +1671,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564425</v>
+        <v>564433</v>
       </c>
       <c r="R11" t="n">
-        <v>6991636</v>
+        <v>6991692</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1702,11 +1707,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121742429</v>
+        <v>121742198</v>
       </c>
       <c r="B2" t="n">
-        <v>97067</v>
+        <v>78629</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564502</v>
+        <v>564489</v>
       </c>
       <c r="R2" t="n">
-        <v>6991645</v>
+        <v>6991655</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121742191</v>
+        <v>121742429</v>
       </c>
       <c r="B3" t="n">
-        <v>79697</v>
+        <v>97085</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,30 +793,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564496</v>
+        <v>564502</v>
       </c>
       <c r="R3" t="n">
-        <v>6991571</v>
+        <v>6991645</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -861,11 +861,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lunglav på flera granar samt sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121742198</v>
+        <v>121742191</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>79710</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,13 +931,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564489</v>
+        <v>564496</v>
       </c>
       <c r="R4" t="n">
-        <v>6991655</v>
+        <v>6991571</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,6 +967,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Lunglav på flera granar samt sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,7 +1002,7 @@
         <v>121760563</v>
       </c>
       <c r="B5" t="n">
-        <v>79697</v>
+        <v>79710</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>121798905</v>
       </c>
       <c r="B6" t="n">
-        <v>79726</v>
+        <v>79739</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121797957</v>
+        <v>121798188</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>79710</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,21 +1224,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,13 +1248,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564365</v>
+        <v>564369</v>
       </c>
       <c r="R7" t="n">
-        <v>6991638</v>
+        <v>6991688</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,7 +1318,7 @@
         <v>121798890</v>
       </c>
       <c r="B8" t="n">
-        <v>79726</v>
+        <v>79739</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121798188</v>
+        <v>121797957</v>
       </c>
       <c r="B9" t="n">
-        <v>79697</v>
+        <v>57365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,13 +1457,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564369</v>
+        <v>564365</v>
       </c>
       <c r="R9" t="n">
-        <v>6991688</v>
+        <v>6991638</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Lunglav på björk</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121798373</v>
+        <v>121797975</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>79710</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1564,13 +1564,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564425</v>
+        <v>564433</v>
       </c>
       <c r="R10" t="n">
-        <v>6991636</v>
+        <v>6991692</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1600,11 +1600,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,10 +1626,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121797975</v>
+        <v>121798373</v>
       </c>
       <c r="B11" t="n">
-        <v>79697</v>
+        <v>57365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,21 +1642,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1671,13 +1666,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564433</v>
+        <v>564425</v>
       </c>
       <c r="R11" t="n">
-        <v>6991692</v>
+        <v>6991636</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1707,6 +1702,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,6 +1730,210 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122040092</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79710</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>564556</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6991632</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122040095</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79710</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>564541</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6991646</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -1733,10 +1733,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122040092</v>
+        <v>122040095</v>
       </c>
       <c r="B12" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564556</v>
+        <v>564541</v>
       </c>
       <c r="R12" t="n">
-        <v>6991632</v>
+        <v>6991646</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1835,10 +1835,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122040095</v>
+        <v>122040092</v>
       </c>
       <c r="B13" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564541</v>
+        <v>564556</v>
       </c>
       <c r="R13" t="n">
-        <v>6991646</v>
+        <v>6991632</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1937,10 +1937,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122188795</v>
+        <v>122188793</v>
       </c>
       <c r="B14" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564449</v>
+        <v>564424</v>
       </c>
       <c r="R14" t="n">
-        <v>6991626</v>
+        <v>6991686</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2044,10 +2044,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122188793</v>
+        <v>122188795</v>
       </c>
       <c r="B15" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564424</v>
+        <v>564449</v>
       </c>
       <c r="R15" t="n">
-        <v>6991686</v>
+        <v>6991626</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -1733,7 +1733,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122040095</v>
+        <v>122040092</v>
       </c>
       <c r="B12" t="n">
         <v>79727</v>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564541</v>
+        <v>564556</v>
       </c>
       <c r="R12" t="n">
-        <v>6991646</v>
+        <v>6991632</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1835,7 +1835,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122040092</v>
+        <v>122040095</v>
       </c>
       <c r="B13" t="n">
         <v>79727</v>
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564556</v>
+        <v>564541</v>
       </c>
       <c r="R13" t="n">
-        <v>6991632</v>
+        <v>6991646</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1937,7 +1937,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122188793</v>
+        <v>122188795</v>
       </c>
       <c r="B14" t="n">
         <v>98185</v>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564424</v>
+        <v>564449</v>
       </c>
       <c r="R14" t="n">
-        <v>6991686</v>
+        <v>6991626</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2044,7 +2044,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122188795</v>
+        <v>122188793</v>
       </c>
       <c r="B15" t="n">
         <v>98185</v>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564449</v>
+        <v>564424</v>
       </c>
       <c r="R15" t="n">
-        <v>6991626</v>
+        <v>6991686</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -1736,7 +1736,7 @@
         <v>122040092</v>
       </c>
       <c r="B12" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>122040095</v>
       </c>
       <c r="B13" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>122188795</v>
       </c>
       <c r="B14" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>122188793</v>
       </c>
       <c r="B15" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -1733,7 +1733,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122040092</v>
+        <v>122040095</v>
       </c>
       <c r="B12" t="n">
         <v>79732</v>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564556</v>
+        <v>564541</v>
       </c>
       <c r="R12" t="n">
-        <v>6991632</v>
+        <v>6991646</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1835,7 +1835,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122040095</v>
+        <v>122040092</v>
       </c>
       <c r="B13" t="n">
         <v>79732</v>
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564541</v>
+        <v>564556</v>
       </c>
       <c r="R13" t="n">
-        <v>6991646</v>
+        <v>6991632</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1937,10 +1937,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122188795</v>
+        <v>122188793</v>
       </c>
       <c r="B14" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564449</v>
+        <v>564424</v>
       </c>
       <c r="R14" t="n">
-        <v>6991626</v>
+        <v>6991686</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2044,10 +2044,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122188793</v>
+        <v>122188795</v>
       </c>
       <c r="B15" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564424</v>
+        <v>564449</v>
       </c>
       <c r="R15" t="n">
-        <v>6991686</v>
+        <v>6991626</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -1937,10 +1937,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122188793</v>
+        <v>122188795</v>
       </c>
       <c r="B14" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1954,11 +1954,6 @@
       </c>
       <c r="E14" t="n">
         <v>220787</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1981,10 +1976,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564424</v>
+        <v>564449</v>
       </c>
       <c r="R14" t="n">
-        <v>6991686</v>
+        <v>6991626</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2044,10 +2039,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122188795</v>
+        <v>122188793</v>
       </c>
       <c r="B15" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2061,11 +2056,6 @@
       </c>
       <c r="E15" t="n">
         <v>220787</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2088,10 +2078,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564449</v>
+        <v>564424</v>
       </c>
       <c r="R15" t="n">
-        <v>6991626</v>
+        <v>6991686</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -1937,10 +1937,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122188795</v>
+        <v>122188793</v>
       </c>
       <c r="B14" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1954,6 +1954,11 @@
       </c>
       <c r="E14" t="n">
         <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1976,10 +1981,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564449</v>
+        <v>564424</v>
       </c>
       <c r="R14" t="n">
-        <v>6991626</v>
+        <v>6991686</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2039,10 +2044,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122188793</v>
+        <v>122188795</v>
       </c>
       <c r="B15" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2056,6 +2061,11 @@
       </c>
       <c r="E15" t="n">
         <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2078,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564424</v>
+        <v>564449</v>
       </c>
       <c r="R15" t="n">
-        <v>6991686</v>
+        <v>6991626</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -1940,7 +1940,7 @@
         <v>122188793</v>
       </c>
       <c r="B14" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>122188795</v>
       </c>
       <c r="B15" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -1937,7 +1937,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122188793</v>
+        <v>122188795</v>
       </c>
       <c r="B14" t="n">
         <v>98237</v>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564424</v>
+        <v>564449</v>
       </c>
       <c r="R14" t="n">
-        <v>6991686</v>
+        <v>6991626</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2044,7 +2044,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122188795</v>
+        <v>122188793</v>
       </c>
       <c r="B15" t="n">
         <v>98237</v>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564449</v>
+        <v>564424</v>
       </c>
       <c r="R15" t="n">
-        <v>6991626</v>
+        <v>6991686</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2149,6 +2149,526 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124048482</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>564473</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6991618</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124048509</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>564479</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6991672</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124048430</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>564473</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6991618</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124048300</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>564449</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6991568</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124048336</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>564479</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6991569</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -2365,7 +2365,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124048430</v>
+        <v>124048300</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564473</v>
+        <v>564449</v>
       </c>
       <c r="R18" t="n">
-        <v>6991618</v>
+        <v>6991568</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124048300</v>
+        <v>124048336</v>
       </c>
       <c r="B19" t="n">
         <v>98079</v>
@@ -2507,13 +2507,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564449</v>
+        <v>564479</v>
       </c>
       <c r="R19" t="n">
-        <v>6991568</v>
+        <v>6991569</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124048336</v>
+        <v>124048430</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2609,13 +2609,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564479</v>
+        <v>564473</v>
       </c>
       <c r="R20" t="n">
-        <v>6991569</v>
+        <v>6991618</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -2151,10 +2151,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124048482</v>
+        <v>124048509</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2163,46 +2163,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564473</v>
+        <v>564479</v>
       </c>
       <c r="R16" t="n">
-        <v>6991618</v>
+        <v>6991672</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2232,11 +2227,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,7 +2253,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124048509</v>
+        <v>124048300</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2303,13 +2293,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564479</v>
+        <v>564449</v>
       </c>
       <c r="R17" t="n">
-        <v>6991672</v>
+        <v>6991568</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2365,7 +2355,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124048300</v>
+        <v>124048430</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2405,13 +2395,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564449</v>
+        <v>564473</v>
       </c>
       <c r="R18" t="n">
-        <v>6991568</v>
+        <v>6991618</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2467,10 +2457,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124048336</v>
+        <v>124048482</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
+        <v>57491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2479,41 +2469,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564479</v>
+        <v>564473</v>
       </c>
       <c r="R19" t="n">
-        <v>6991569</v>
+        <v>6991618</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2543,6 +2538,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2569,7 +2569,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124048430</v>
+        <v>124048336</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2609,13 +2609,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564473</v>
+        <v>564479</v>
       </c>
       <c r="R20" t="n">
-        <v>6991618</v>
+        <v>6991569</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -2151,7 +2151,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124048509</v>
+        <v>124048300</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2191,13 +2191,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564479</v>
+        <v>564449</v>
       </c>
       <c r="R16" t="n">
-        <v>6991672</v>
+        <v>6991568</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124048300</v>
+        <v>124048336</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2293,13 +2293,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564449</v>
+        <v>564479</v>
       </c>
       <c r="R17" t="n">
-        <v>6991568</v>
+        <v>6991569</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124048430</v>
+        <v>124048509</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564473</v>
+        <v>564479</v>
       </c>
       <c r="R18" t="n">
-        <v>6991618</v>
+        <v>6991672</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124048336</v>
+        <v>124048430</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2609,13 +2609,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564479</v>
+        <v>564473</v>
       </c>
       <c r="R20" t="n">
-        <v>6991569</v>
+        <v>6991618</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -2151,10 +2151,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124048482</v>
+        <v>124048336</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2163,46 +2163,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564473</v>
+        <v>564479</v>
       </c>
       <c r="R16" t="n">
-        <v>6991618</v>
+        <v>6991569</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2232,11 +2227,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,10 +2253,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124048430</v>
+        <v>124048482</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2275,28 +2265,33 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stortjärndalen, Jmt</t>
@@ -2339,6 +2334,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,7 +2467,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124048300</v>
+        <v>124048430</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2507,13 +2507,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564449</v>
+        <v>564473</v>
       </c>
       <c r="R19" t="n">
-        <v>6991568</v>
+        <v>6991618</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124048336</v>
+        <v>124048300</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2609,13 +2609,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564479</v>
+        <v>564449</v>
       </c>
       <c r="R20" t="n">
-        <v>6991569</v>
+        <v>6991568</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -2151,7 +2151,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124048336</v>
+        <v>124048430</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2191,13 +2191,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564479</v>
+        <v>564473</v>
       </c>
       <c r="R16" t="n">
-        <v>6991569</v>
+        <v>6991618</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2253,10 +2253,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124048482</v>
+        <v>124048336</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2265,46 +2265,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564473</v>
+        <v>564479</v>
       </c>
       <c r="R17" t="n">
-        <v>6991618</v>
+        <v>6991569</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2334,11 +2329,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2365,7 +2355,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124048509</v>
+        <v>124048300</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2405,13 +2395,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564479</v>
+        <v>564449</v>
       </c>
       <c r="R18" t="n">
-        <v>6991672</v>
+        <v>6991568</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2467,10 +2457,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124048430</v>
+        <v>124048482</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2479,28 +2469,33 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stortjärndalen, Jmt</t>
@@ -2543,6 +2538,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2569,7 +2569,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124048300</v>
+        <v>124048509</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2609,13 +2609,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564449</v>
+        <v>564479</v>
       </c>
       <c r="R20" t="n">
-        <v>6991568</v>
+        <v>6991672</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -2253,10 +2253,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124048336</v>
+        <v>124048482</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2265,41 +2265,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564479</v>
+        <v>564473</v>
       </c>
       <c r="R17" t="n">
-        <v>6991569</v>
+        <v>6991618</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2329,6 +2334,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,7 +2365,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124048300</v>
+        <v>124048336</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2395,13 +2405,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564449</v>
+        <v>564479</v>
       </c>
       <c r="R18" t="n">
-        <v>6991568</v>
+        <v>6991569</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2457,10 +2467,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124048482</v>
+        <v>124048300</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2469,46 +2479,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564473</v>
+        <v>564449</v>
       </c>
       <c r="R19" t="n">
-        <v>6991618</v>
+        <v>6991568</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2538,11 +2543,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -2365,7 +2365,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124048336</v>
+        <v>124048300</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564479</v>
+        <v>564449</v>
       </c>
       <c r="R18" t="n">
-        <v>6991569</v>
+        <v>6991568</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124048300</v>
+        <v>124048509</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2507,13 +2507,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564449</v>
+        <v>564479</v>
       </c>
       <c r="R19" t="n">
-        <v>6991568</v>
+        <v>6991672</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124048509</v>
+        <v>124048336</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2612,10 +2612,10 @@
         <v>564479</v>
       </c>
       <c r="R20" t="n">
-        <v>6991672</v>
+        <v>6991569</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -2151,7 +2151,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124048430</v>
+        <v>124048336</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2191,13 +2191,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564473</v>
+        <v>564479</v>
       </c>
       <c r="R16" t="n">
-        <v>6991618</v>
+        <v>6991569</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2253,10 +2253,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124048482</v>
+        <v>124048509</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2265,46 +2265,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564473</v>
+        <v>564479</v>
       </c>
       <c r="R17" t="n">
-        <v>6991618</v>
+        <v>6991672</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2334,11 +2329,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2365,7 +2355,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124048300</v>
+        <v>124048430</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2405,13 +2395,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564449</v>
+        <v>564473</v>
       </c>
       <c r="R18" t="n">
-        <v>6991568</v>
+        <v>6991618</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2467,7 +2457,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124048509</v>
+        <v>124048300</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2507,13 +2497,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564479</v>
+        <v>564449</v>
       </c>
       <c r="R19" t="n">
-        <v>6991672</v>
+        <v>6991568</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2569,10 +2559,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124048336</v>
+        <v>124048482</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2581,41 +2571,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564479</v>
+        <v>564473</v>
       </c>
       <c r="R20" t="n">
-        <v>6991569</v>
+        <v>6991618</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2645,6 +2640,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -2151,7 +2151,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124048336</v>
+        <v>124048430</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2191,13 +2191,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564479</v>
+        <v>564473</v>
       </c>
       <c r="R16" t="n">
-        <v>6991569</v>
+        <v>6991618</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124048509</v>
+        <v>124048336</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2296,10 +2296,10 @@
         <v>564479</v>
       </c>
       <c r="R17" t="n">
-        <v>6991672</v>
+        <v>6991569</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124048430</v>
+        <v>124048482</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2367,28 +2367,33 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stortjärndalen, Jmt</t>
@@ -2431,6 +2436,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2457,7 +2467,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124048300</v>
+        <v>124048509</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2497,13 +2507,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564449</v>
+        <v>564479</v>
       </c>
       <c r="R19" t="n">
-        <v>6991568</v>
+        <v>6991672</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2559,10 +2569,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124048482</v>
+        <v>124048300</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2571,46 +2581,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564473</v>
+        <v>564449</v>
       </c>
       <c r="R20" t="n">
-        <v>6991618</v>
+        <v>6991568</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2640,11 +2645,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2669,6 +2669,2896 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125396762</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>658</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>564441</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6991661</v>
+      </c>
+      <c r="S21" t="n">
+        <v>14</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125396355</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>564463</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6991617</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125396221</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>564445</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6991608</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125398468</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>564441</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6991674</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På kolad ved på två gamla tallhögstubbar</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125397829</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>564401</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6991629</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikliga ringhack på gammal tall</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125397175</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>564453</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6991658</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125396883</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>564440</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6991655</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125397300</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>564442</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6991680</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125396498</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>564463</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6991617</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125397495</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79795</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>564410</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6991660</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125396600</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>564463</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6991617</v>
+      </c>
+      <c r="S31" t="n">
+        <v>11</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125395199</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>564521</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6991610</v>
+      </c>
+      <c r="S32" t="n">
+        <v>12</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På gråal</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125397385</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>564442</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6991680</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På sälg i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125397801</v>
+      </c>
+      <c r="B34" t="n">
+        <v>74901</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>564440</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6991662</v>
+      </c>
+      <c r="S34" t="n">
+        <v>9</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125395933</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>564463</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6991559</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125398718</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>564439</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6991676</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ett stort områden typ 10 kvadratmeter</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125398524</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>564457</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6991682</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125396949</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>564440</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6991655</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125397089</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>564452</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6991661</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt på marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125398362</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>564453</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6991691</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125398434</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>564420</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6991658</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>125398578</v>
+      </c>
+      <c r="B42" t="n">
+        <v>82597</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>564440</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6991662</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>125396843</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>564431</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6991652</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>125397219</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>564440</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6991662</v>
+      </c>
+      <c r="S44" t="n">
+        <v>11</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3995,7 +3995,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125395199</v>
+        <v>125397385</v>
       </c>
       <c r="B32" t="n">
         <v>79891</v>
@@ -4028,29 +4028,20 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>564521</v>
+        <v>564442</v>
       </c>
       <c r="R32" t="n">
-        <v>6991610</v>
+        <v>6991680</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4079,7 +4070,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4089,12 +4080,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gråal</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4109,19 +4100,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125397385</v>
+        <v>125395199</v>
       </c>
       <c r="B33" t="n">
         <v>79891</v>
@@ -4154,20 +4145,29 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>564442</v>
+        <v>564521</v>
       </c>
       <c r="R33" t="n">
-        <v>6991680</v>
+        <v>6991610</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På gråal</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4226,22 +4226,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125397801</v>
+        <v>125395933</v>
       </c>
       <c r="B34" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4254,37 +4254,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>564440</v>
+        <v>564463</v>
       </c>
       <c r="R34" t="n">
-        <v>6991662</v>
+        <v>6991559</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4313,7 +4318,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4323,12 +4328,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4355,10 +4360,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125395933</v>
+        <v>125397801</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4371,42 +4376,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>564463</v>
+        <v>564440</v>
       </c>
       <c r="R35" t="n">
-        <v>6991559</v>
+        <v>6991662</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4846,10 +4846,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125397089</v>
+        <v>125398362</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4858,52 +4858,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>564452</v>
+        <v>564453</v>
       </c>
       <c r="R39" t="n">
-        <v>6991661</v>
+        <v>6991691</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4935,7 +4921,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4945,12 +4931,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Rikligt på marken i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4977,10 +4963,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125398362</v>
+        <v>125398434</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4993,21 +4979,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5017,10 +5003,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>564453</v>
+        <v>564420</v>
       </c>
       <c r="R40" t="n">
-        <v>6991691</v>
+        <v>6991658</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5052,7 +5038,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5062,12 +5048,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5082,22 +5068,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125398434</v>
+        <v>125397089</v>
       </c>
       <c r="B41" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5106,38 +5092,52 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>564420</v>
+        <v>564452</v>
       </c>
       <c r="R41" t="n">
-        <v>6991658</v>
+        <v>6991661</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Lunglav på björk</t>
+          <t>Rikligt på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5199,12 +5199,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5559,6 +5559,4854 @@
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>125426260</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>564551</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6991633</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>125426281</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>564408</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6991646</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>125420524</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>564474</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6991608</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Helt färska och äldre ringhack, rikligt på gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125420539</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>564466</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6991587</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>60 plantor på marken i gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>125420529</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78792</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>336</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Solfjäderlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cheiromycina flabelliformis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>B.Sutton</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>564492</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6991578</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På bark vid basen av gammal död sälg i fuktig gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125426255</v>
+      </c>
+      <c r="B50" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>564448</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6991620</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>125426267</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>658</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>564405</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6991645</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>125426252</v>
+      </c>
+      <c r="B52" t="n">
+        <v>96354</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>53</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>564532</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6991656</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>125420533</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79919</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>564582</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6991673</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>125426250</v>
+      </c>
+      <c r="B54" t="n">
+        <v>105102</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>564528</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6991624</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>125426251</v>
+      </c>
+      <c r="B55" t="n">
+        <v>74901</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>564469</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6991678</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>125420543</v>
+      </c>
+      <c r="B56" t="n">
+        <v>74893</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>308</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>564520</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6991622</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På ved på gammal granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125426280</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>564364</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6991670</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>125426285</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79926</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>564561</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6991616</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>125426277</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>564468</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6991658</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>125420541</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>564525</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6991662</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>10 plantor på marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>125420528</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98122</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>564555</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6991665</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>125438544</v>
+      </c>
+      <c r="B62" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>564517</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6991669</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>125420531</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>658</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>564486</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6991573</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>125426265</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>658</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>564336</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6991633</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>125420520</v>
+      </c>
+      <c r="B65" t="n">
+        <v>105102</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>564498</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6991598</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>125426258</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>564461</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6991657</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>125420527</v>
+      </c>
+      <c r="B67" t="n">
+        <v>98122</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>564499</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6991597</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>125426272</v>
+      </c>
+      <c r="B68" t="n">
+        <v>95335</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>564515</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6991646</v>
+      </c>
+      <c r="S68" t="n">
+        <v>15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>125420522</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79428</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>564449</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6991631</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På ved på gammal tallhögstubbe i gammal tallskog</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>125420535</v>
+      </c>
+      <c r="B70" t="n">
+        <v>95335</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>564539</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6991663</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På marken i gammal fuktig granskog</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>125426262</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91457</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>564395</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6991654</v>
+      </c>
+      <c r="S71" t="n">
+        <v>15</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>125438549</v>
+      </c>
+      <c r="B72" t="n">
+        <v>77743</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>564542</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6991657</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>125420536</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>564470</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6991585</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Mycket rikligt på gran under grov asp</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>125420534</v>
+      </c>
+      <c r="B74" t="n">
+        <v>74677</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>98</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Mörk rödprick</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Arthonia incarnata</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Th.Fr. ex Almq.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>564500</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6991603</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På bark vid basen av gammal levande grov sälg (75 cm dbh) i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>125426269</v>
+      </c>
+      <c r="B75" t="n">
+        <v>98135</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>564521</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6991595</v>
+      </c>
+      <c r="S75" t="n">
+        <v>15</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>125426254</v>
+      </c>
+      <c r="B76" t="n">
+        <v>96354</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>53</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>564412</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6991656</v>
+      </c>
+      <c r="S76" t="n">
+        <v>15</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>125420538</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>564491</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6991571</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På gammal sälg i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>125420530</v>
+      </c>
+      <c r="B78" t="n">
+        <v>74713</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>564520</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6991626</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>125438545</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>564535</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6991601</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>125426286</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79926</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>564556</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6991665</v>
+      </c>
+      <c r="S80" t="n">
+        <v>15</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>125426257</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>564337</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6991632</v>
+      </c>
+      <c r="S81" t="n">
+        <v>15</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>125426278</v>
+      </c>
+      <c r="B82" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>564453</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6991629</v>
+      </c>
+      <c r="S82" t="n">
+        <v>15</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>125420542</v>
+      </c>
+      <c r="B83" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>564429</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6991627</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Rikligt på gamla granar i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>125420540</v>
+      </c>
+      <c r="B84" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>564495</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6991590</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>40 plantor på marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>125420537</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>564470</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6991561</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>125426279</v>
+      </c>
+      <c r="B86" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>564474</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6991589</v>
+      </c>
+      <c r="S86" t="n">
+        <v>15</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>125420523</v>
+      </c>
+      <c r="B87" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>564516</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6991629</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>125438548</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79927</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>564548</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6991664</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -2671,10 +2671,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125396762</v>
+        <v>125397300</v>
       </c>
       <c r="B21" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2683,31 +2683,40 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2716,13 +2725,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564441</v>
+        <v>564442</v>
       </c>
       <c r="R21" t="n">
-        <v>6991661</v>
+        <v>6991680</v>
       </c>
       <c r="S21" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2751,7 +2760,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2761,7 +2770,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2776,22 +2790,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125396355</v>
+        <v>125395933</v>
       </c>
       <c r="B22" t="n">
-        <v>78547</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2804,24 +2818,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
@@ -2831,7 +2850,7 @@
         <v>564463</v>
       </c>
       <c r="R22" t="n">
-        <v>6991617</v>
+        <v>6991559</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2863,7 +2882,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2873,7 +2892,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2893,17 +2917,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125396221</v>
+        <v>125398434</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2916,39 +2940,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564445</v>
+        <v>564420</v>
       </c>
       <c r="R23" t="n">
-        <v>6991608</v>
+        <v>6991658</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,7 +2999,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2990,12 +3009,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3010,22 +3029,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125398468</v>
+        <v>125397829</v>
       </c>
       <c r="B24" t="n">
-        <v>78547</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3038,34 +3057,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>564441</v>
+        <v>564401</v>
       </c>
       <c r="R24" t="n">
-        <v>6991674</v>
+        <v>6991629</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3097,7 +3121,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3107,12 +3131,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På kolad ved på två gamla tallhögstubbar</t>
+          <t>Rikliga ringhack på gammal tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3127,22 +3151,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125397829</v>
+        <v>125397089</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3151,31 +3175,40 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3184,10 +3217,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>564401</v>
+        <v>564452</v>
       </c>
       <c r="R25" t="n">
-        <v>6991629</v>
+        <v>6991661</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3219,7 +3252,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3229,12 +3262,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikliga ringhack på gammal tall</t>
+          <t>Rikligt på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3249,22 +3282,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125397175</v>
+        <v>125396762</v>
       </c>
       <c r="B26" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3277,37 +3310,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>564453</v>
+        <v>564441</v>
       </c>
       <c r="R26" t="n">
-        <v>6991658</v>
+        <v>6991661</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3336,7 +3374,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3346,12 +3384,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3366,22 +3399,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125396883</v>
+        <v>125398524</v>
       </c>
       <c r="B27" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3394,27 +3427,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3423,10 +3460,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>564440</v>
+        <v>564457</v>
       </c>
       <c r="R27" t="n">
-        <v>6991655</v>
+        <v>6991682</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3458,7 +3495,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3468,12 +3505,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3500,10 +3537,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125397300</v>
+        <v>125397495</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>79795</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3512,52 +3549,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>564442</v>
+        <v>564410</v>
       </c>
       <c r="R28" t="n">
-        <v>6991680</v>
+        <v>6991660</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3589,7 +3612,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3599,12 +3622,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3631,10 +3654,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125396498</v>
+        <v>125397385</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3643,55 +3666,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>564463</v>
+        <v>564442</v>
       </c>
       <c r="R29" t="n">
-        <v>6991617</v>
+        <v>6991680</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3720,7 +3729,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3730,7 +3739,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3745,7 +3759,7 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -3757,10 +3771,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125397495</v>
+        <v>125396498</v>
       </c>
       <c r="B30" t="n">
-        <v>79795</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3769,41 +3783,55 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>564410</v>
+        <v>564463</v>
       </c>
       <c r="R30" t="n">
-        <v>6991660</v>
+        <v>6991617</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3832,7 +3860,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3842,12 +3870,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3862,22 +3885,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125396600</v>
+        <v>125398718</v>
       </c>
       <c r="B31" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3886,35 +3909,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3923,13 +3946,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>564463</v>
+        <v>564439</v>
       </c>
       <c r="R31" t="n">
-        <v>6991617</v>
+        <v>6991676</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3958,7 +3981,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3968,7 +3991,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ett stort områden typ 10 kvadratmeter</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3983,22 +4011,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125397385</v>
+        <v>125397801</v>
       </c>
       <c r="B32" t="n">
-        <v>79891</v>
+        <v>74901</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4011,21 +4039,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4035,13 +4063,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>564442</v>
+        <v>564440</v>
       </c>
       <c r="R32" t="n">
-        <v>6991680</v>
+        <v>6991662</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4070,7 +4098,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4080,12 +4108,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4100,22 +4128,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125395199</v>
+        <v>125396600</v>
       </c>
       <c r="B33" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4124,25 +4152,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4161,13 +4189,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>564521</v>
+        <v>564463</v>
       </c>
       <c r="R33" t="n">
-        <v>6991610</v>
+        <v>6991617</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4196,7 +4224,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4206,12 +4234,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På gråal</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4238,10 +4261,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125395933</v>
+        <v>125397175</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4254,39 +4277,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>564463</v>
+        <v>564453</v>
       </c>
       <c r="R34" t="n">
-        <v>6991559</v>
+        <v>6991658</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4318,7 +4336,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4328,12 +4346,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4348,22 +4366,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125397801</v>
+        <v>125398468</v>
       </c>
       <c r="B35" t="n">
-        <v>74901</v>
+        <v>78547</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4376,21 +4394,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4400,13 +4418,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>564440</v>
+        <v>564441</v>
       </c>
       <c r="R35" t="n">
-        <v>6991662</v>
+        <v>6991674</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4435,7 +4453,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4445,12 +4463,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På kolad ved på två gamla tallhögstubbar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4465,22 +4483,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125398718</v>
+        <v>125398362</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4489,47 +4507,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>564439</v>
+        <v>564453</v>
       </c>
       <c r="R36" t="n">
-        <v>6991676</v>
+        <v>6991691</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4561,7 +4570,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4571,12 +4580,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ett stort områden typ 10 kvadratmeter</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4591,22 +4600,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125398524</v>
+        <v>125395199</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4619,26 +4628,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4652,13 +4661,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>564457</v>
+        <v>564521</v>
       </c>
       <c r="R37" t="n">
-        <v>6991682</v>
+        <v>6991610</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4687,7 +4696,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4697,12 +4706,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På gråal</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4717,19 +4726,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125396949</v>
+        <v>125396355</v>
       </c>
       <c r="B38" t="n">
         <v>78547</v>
@@ -4769,10 +4778,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>564440</v>
+        <v>564463</v>
       </c>
       <c r="R38" t="n">
-        <v>6991655</v>
+        <v>6991617</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4804,7 +4813,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4814,12 +4823,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4834,19 +4838,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125398362</v>
+        <v>125396843</v>
       </c>
       <c r="B39" t="n">
         <v>91012</v>
@@ -4886,10 +4890,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>564453</v>
+        <v>564431</v>
       </c>
       <c r="R39" t="n">
-        <v>6991691</v>
+        <v>6991652</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4921,7 +4925,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4931,12 +4935,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4963,10 +4967,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125398434</v>
+        <v>125396883</v>
       </c>
       <c r="B40" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4979,34 +4983,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>564420</v>
+        <v>564440</v>
       </c>
       <c r="R40" t="n">
-        <v>6991658</v>
+        <v>6991655</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5038,7 +5047,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5048,12 +5057,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Lunglav på björk</t>
+          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5068,22 +5077,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125397089</v>
+        <v>125397219</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5092,40 +5101,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5134,13 +5138,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>564452</v>
+        <v>564440</v>
       </c>
       <c r="R41" t="n">
-        <v>6991661</v>
+        <v>6991662</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5169,7 +5173,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5179,12 +5183,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt på marken i gammal granskog</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5199,12 +5198,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5323,7 +5322,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125396843</v>
+        <v>125396221</v>
       </c>
       <c r="B43" t="n">
         <v>91012</v>
@@ -5357,16 +5356,21 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>564431</v>
+        <v>564445</v>
       </c>
       <c r="R43" t="n">
-        <v>6991652</v>
+        <v>6991608</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5398,7 +5402,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5408,12 +5412,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5428,7 +5432,7 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -5440,10 +5444,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125397219</v>
+        <v>125396949</v>
       </c>
       <c r="B44" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5456,33 +5460,24 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
@@ -5492,10 +5487,10 @@
         <v>564440</v>
       </c>
       <c r="R44" t="n">
-        <v>6991662</v>
+        <v>6991655</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5524,7 +5519,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5534,7 +5529,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5549,22 +5549,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125426260</v>
+        <v>125420523</v>
       </c>
       <c r="B45" t="n">
-        <v>79920</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5573,41 +5573,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>564551</v>
+        <v>564516</v>
       </c>
       <c r="R45" t="n">
-        <v>6991633</v>
+        <v>6991629</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5634,9 +5634,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5651,19 +5666,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125426281</v>
+        <v>125420542</v>
       </c>
       <c r="B46" t="n">
         <v>78810</v>
@@ -5699,17 +5714,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>564408</v>
+        <v>564429</v>
       </c>
       <c r="R46" t="n">
-        <v>6991646</v>
+        <v>6991627</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5736,9 +5751,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5753,22 +5783,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125420524</v>
+        <v>125426252</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>96354</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5781,37 +5811,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>564474</v>
+        <v>564532</v>
       </c>
       <c r="R47" t="n">
-        <v>6991608</v>
+        <v>6991656</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5838,24 +5868,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Helt färska och äldre ringhack, rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5870,22 +5885,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125420539</v>
+        <v>125420534</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>74677</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5898,21 +5913,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>98</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk rödprick</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia incarnata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Th.Fr. ex Almq.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5922,10 +5937,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>564466</v>
+        <v>564500</v>
       </c>
       <c r="R48" t="n">
-        <v>6991587</v>
+        <v>6991603</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5957,7 +5972,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5967,12 +5982,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>60 plantor på marken i gammal barrblandskog</t>
+          <t>På bark vid basen av gammal levande grov sälg (75 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5999,10 +6014,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125420529</v>
+        <v>125420530</v>
       </c>
       <c r="B49" t="n">
-        <v>78792</v>
+        <v>74713</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6011,25 +6026,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>336</v>
+        <v>6428</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Solfjäderlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cheiromycina flabelliformis</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>B.Sutton</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6039,10 +6054,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>564492</v>
+        <v>564520</v>
       </c>
       <c r="R49" t="n">
-        <v>6991578</v>
+        <v>6991626</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6074,7 +6089,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6084,12 +6099,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal död sälg i fuktig gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6116,10 +6131,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125426255</v>
+        <v>125420537</v>
       </c>
       <c r="B50" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6128,41 +6143,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>564448</v>
+        <v>564470</v>
       </c>
       <c r="R50" t="n">
-        <v>6991620</v>
+        <v>6991561</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6189,9 +6204,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6206,22 +6236,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125426267</v>
+        <v>125438545</v>
       </c>
       <c r="B51" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6234,37 +6264,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>564405</v>
+        <v>564535</v>
       </c>
       <c r="R51" t="n">
-        <v>6991645</v>
+        <v>6991601</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6294,6 +6324,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6308,22 +6343,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125426252</v>
+        <v>125420539</v>
       </c>
       <c r="B52" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6332,41 +6367,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>564532</v>
+        <v>564466</v>
       </c>
       <c r="R52" t="n">
-        <v>6991656</v>
+        <v>6991587</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6393,9 +6428,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>60 plantor på marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6410,22 +6460,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125420533</v>
+        <v>125420535</v>
       </c>
       <c r="B53" t="n">
-        <v>79919</v>
+        <v>95335</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6438,21 +6488,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6461</v>
+        <v>2809</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6462,10 +6512,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>564582</v>
+        <v>564539</v>
       </c>
       <c r="R53" t="n">
-        <v>6991673</v>
+        <v>6991663</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6497,7 +6547,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6507,12 +6557,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6539,10 +6589,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125426250</v>
+        <v>125426258</v>
       </c>
       <c r="B54" t="n">
-        <v>105102</v>
+        <v>57513</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6551,38 +6601,46 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>564528</v>
+        <v>564461</v>
       </c>
       <c r="R54" t="n">
-        <v>6991624</v>
+        <v>6991657</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6615,6 +6673,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6641,10 +6704,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125426251</v>
+        <v>125426257</v>
       </c>
       <c r="B55" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6657,21 +6720,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6681,10 +6744,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>564469</v>
+        <v>564337</v>
       </c>
       <c r="R55" t="n">
-        <v>6991678</v>
+        <v>6991632</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6743,10 +6806,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125420543</v>
+        <v>125426285</v>
       </c>
       <c r="B56" t="n">
-        <v>74893</v>
+        <v>79926</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6755,41 +6818,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>308</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>564520</v>
+        <v>564561</v>
       </c>
       <c r="R56" t="n">
-        <v>6991622</v>
+        <v>6991616</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6816,24 +6879,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På ved på gammal granhögstubbe</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6848,22 +6896,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125426280</v>
+        <v>125420522</v>
       </c>
       <c r="B57" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6876,37 +6924,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>564364</v>
+        <v>564449</v>
       </c>
       <c r="R57" t="n">
-        <v>6991670</v>
+        <v>6991631</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6933,9 +6981,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På ved på gammal tallhögstubbe i gammal tallskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6950,22 +7013,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125426285</v>
+        <v>125420538</v>
       </c>
       <c r="B58" t="n">
-        <v>79926</v>
+        <v>79891</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6974,41 +7037,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>564561</v>
+        <v>564491</v>
       </c>
       <c r="R58" t="n">
-        <v>6991616</v>
+        <v>6991571</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7035,9 +7098,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7052,22 +7130,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125426277</v>
+        <v>125426269</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>98135</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7076,46 +7154,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>564468</v>
+        <v>564521</v>
       </c>
       <c r="R59" t="n">
-        <v>6991658</v>
+        <v>6991595</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7156,7 +7226,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7175,10 +7244,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125420541</v>
+        <v>125420531</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7187,25 +7256,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7215,10 +7284,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>564525</v>
+        <v>564486</v>
       </c>
       <c r="R60" t="n">
-        <v>6991662</v>
+        <v>6991573</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7250,7 +7319,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7260,12 +7329,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>10 plantor på marken i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7292,10 +7361,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125420528</v>
+        <v>125426279</v>
       </c>
       <c r="B61" t="n">
-        <v>98122</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7304,41 +7373,49 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>564555</v>
+        <v>564474</v>
       </c>
       <c r="R61" t="n">
-        <v>6991665</v>
+        <v>6991589</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7365,54 +7442,40 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125438544</v>
+        <v>125420541</v>
       </c>
       <c r="B62" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7421,25 +7484,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7449,10 +7512,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>564517</v>
+        <v>564525</v>
       </c>
       <c r="R62" t="n">
-        <v>6991669</v>
+        <v>6991662</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7482,14 +7545,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>10 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7504,22 +7577,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125420531</v>
+        <v>125420536</v>
       </c>
       <c r="B63" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7532,21 +7605,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7556,10 +7629,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>564486</v>
+        <v>564470</v>
       </c>
       <c r="R63" t="n">
-        <v>6991573</v>
+        <v>6991585</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7591,7 +7664,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7601,12 +7674,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Mycket rikligt på gran under grov asp</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7633,10 +7706,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125426265</v>
+        <v>125420533</v>
       </c>
       <c r="B64" t="n">
-        <v>91299</v>
+        <v>79919</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7645,41 +7718,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>6461</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>564336</v>
+        <v>564582</v>
       </c>
       <c r="R64" t="n">
-        <v>6991633</v>
+        <v>6991673</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7706,9 +7779,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7723,22 +7811,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125420520</v>
+        <v>125426255</v>
       </c>
       <c r="B65" t="n">
-        <v>105102</v>
+        <v>90977</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7751,37 +7839,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>564498</v>
+        <v>564448</v>
       </c>
       <c r="R65" t="n">
-        <v>6991598</v>
+        <v>6991620</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7808,24 +7896,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7840,22 +7913,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125426258</v>
+        <v>125420528</v>
       </c>
       <c r="B66" t="n">
-        <v>57513</v>
+        <v>98122</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7864,49 +7937,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>564461</v>
+        <v>564555</v>
       </c>
       <c r="R66" t="n">
-        <v>6991657</v>
+        <v>6991665</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7933,14 +7998,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7955,22 +8030,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125420527</v>
+        <v>125426262</v>
       </c>
       <c r="B67" t="n">
-        <v>98122</v>
+        <v>91457</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7979,41 +8054,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>564499</v>
+        <v>564395</v>
       </c>
       <c r="R67" t="n">
-        <v>6991597</v>
+        <v>6991654</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8040,24 +8115,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8072,22 +8132,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125426272</v>
+        <v>125420524</v>
       </c>
       <c r="B68" t="n">
-        <v>95335</v>
+        <v>57513</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8096,41 +8156,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>564515</v>
+        <v>564474</v>
       </c>
       <c r="R68" t="n">
-        <v>6991646</v>
+        <v>6991608</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8157,9 +8217,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Helt färska och äldre ringhack, rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8174,22 +8249,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125420522</v>
+        <v>125420529</v>
       </c>
       <c r="B69" t="n">
-        <v>79428</v>
+        <v>78792</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8202,21 +8277,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>336</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Solfjäderlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cheiromycina flabelliformis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>B.Sutton</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8226,10 +8301,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>564449</v>
+        <v>564492</v>
       </c>
       <c r="R69" t="n">
-        <v>6991631</v>
+        <v>6991578</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8261,7 +8336,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8271,12 +8346,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På ved på gammal tallhögstubbe i gammal tallskog</t>
+          <t>På bark vid basen av gammal död sälg i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8303,10 +8378,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125420535</v>
+        <v>125426281</v>
       </c>
       <c r="B70" t="n">
-        <v>95335</v>
+        <v>78810</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8315,41 +8390,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>564539</v>
+        <v>564408</v>
       </c>
       <c r="R70" t="n">
-        <v>6991663</v>
+        <v>6991646</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8376,24 +8451,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På marken i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8408,22 +8468,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125426262</v>
+        <v>125426278</v>
       </c>
       <c r="B71" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8436,34 +8496,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>564395</v>
+        <v>564453</v>
       </c>
       <c r="R71" t="n">
-        <v>6991654</v>
+        <v>6991629</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8504,6 +8572,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8522,10 +8591,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125438549</v>
+        <v>125420520</v>
       </c>
       <c r="B72" t="n">
-        <v>77743</v>
+        <v>105102</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8534,25 +8603,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228579</v>
+        <v>221725</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8562,10 +8631,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>564542</v>
+        <v>564498</v>
       </c>
       <c r="R72" t="n">
-        <v>6991657</v>
+        <v>6991598</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8595,14 +8664,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8617,22 +8696,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125420536</v>
+        <v>125438549</v>
       </c>
       <c r="B73" t="n">
-        <v>79891</v>
+        <v>77743</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8645,21 +8724,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8669,10 +8748,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>564470</v>
+        <v>564542</v>
       </c>
       <c r="R73" t="n">
-        <v>6991585</v>
+        <v>6991657</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8702,24 +8781,14 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>13:01</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>13:01</t>
-        </is>
-      </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Mycket rikligt på gran under grov asp</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8734,22 +8803,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125420534</v>
+        <v>125426260</v>
       </c>
       <c r="B74" t="n">
-        <v>74677</v>
+        <v>79920</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8758,41 +8827,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>98</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk rödprick</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Arthonia incarnata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Th.Fr. ex Almq.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>564500</v>
+        <v>564551</v>
       </c>
       <c r="R74" t="n">
-        <v>6991603</v>
+        <v>6991633</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8819,24 +8888,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På bark vid basen av gammal levande grov sälg (75 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8851,22 +8905,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125426269</v>
+        <v>125420543</v>
       </c>
       <c r="B75" t="n">
-        <v>98135</v>
+        <v>74893</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8875,41 +8929,41 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219874</v>
+        <v>308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>564521</v>
+        <v>564520</v>
       </c>
       <c r="R75" t="n">
-        <v>6991595</v>
+        <v>6991622</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8936,9 +8990,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På ved på gammal granhögstubbe</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8953,12 +9022,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9067,10 +9136,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125420538</v>
+        <v>125426286</v>
       </c>
       <c r="B77" t="n">
-        <v>79891</v>
+        <v>79926</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9079,41 +9148,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>564491</v>
+        <v>564556</v>
       </c>
       <c r="R77" t="n">
-        <v>6991571</v>
+        <v>6991665</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9140,24 +9209,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9172,22 +9226,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125420530</v>
+        <v>125438548</v>
       </c>
       <c r="B78" t="n">
-        <v>74713</v>
+        <v>79927</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9200,21 +9254,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6428</v>
+        <v>6464</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9224,10 +9278,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>564520</v>
+        <v>564548</v>
       </c>
       <c r="R78" t="n">
-        <v>6991626</v>
+        <v>6991664</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9257,24 +9311,14 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9289,22 +9333,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125438545</v>
+        <v>125420527</v>
       </c>
       <c r="B79" t="n">
-        <v>57513</v>
+        <v>98122</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9313,25 +9357,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9341,10 +9385,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>564535</v>
+        <v>564499</v>
       </c>
       <c r="R79" t="n">
-        <v>6991601</v>
+        <v>6991597</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9374,14 +9418,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9396,22 +9450,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125426286</v>
+        <v>125426272</v>
       </c>
       <c r="B80" t="n">
-        <v>79926</v>
+        <v>95335</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9424,21 +9478,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6463</v>
+        <v>2809</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9448,10 +9502,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>564556</v>
+        <v>564515</v>
       </c>
       <c r="R80" t="n">
-        <v>6991665</v>
+        <v>6991646</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -9510,10 +9564,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125426257</v>
+        <v>125426265</v>
       </c>
       <c r="B81" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9526,21 +9580,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9550,10 +9604,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>564337</v>
+        <v>564336</v>
       </c>
       <c r="R81" t="n">
-        <v>6991632</v>
+        <v>6991633</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -9612,10 +9666,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125426278</v>
+        <v>125426267</v>
       </c>
       <c r="B82" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9624,46 +9678,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>564453</v>
+        <v>564405</v>
       </c>
       <c r="R82" t="n">
-        <v>6991629</v>
+        <v>6991645</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9704,7 +9750,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9723,7 +9768,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125420542</v>
+        <v>125426280</v>
       </c>
       <c r="B83" t="n">
         <v>78810</v>
@@ -9759,17 +9804,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>564429</v>
+        <v>564364</v>
       </c>
       <c r="R83" t="n">
-        <v>6991627</v>
+        <v>6991670</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9796,24 +9841,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9828,12 +9858,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9957,10 +9987,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125420537</v>
+        <v>125426277</v>
       </c>
       <c r="B85" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9969,41 +9999,49 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>564470</v>
+        <v>564468</v>
       </c>
       <c r="R85" t="n">
-        <v>6991561</v>
+        <v>6991658</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10030,54 +10068,40 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125426279</v>
+        <v>125426251</v>
       </c>
       <c r="B86" t="n">
-        <v>98101</v>
+        <v>74901</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10086,46 +10110,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>564474</v>
+        <v>564469</v>
       </c>
       <c r="R86" t="n">
-        <v>6991589</v>
+        <v>6991678</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -10166,7 +10182,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -10185,10 +10200,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125420523</v>
+        <v>125426250</v>
       </c>
       <c r="B87" t="n">
-        <v>91012</v>
+        <v>105102</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10197,41 +10212,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>564516</v>
+        <v>564528</v>
       </c>
       <c r="R87" t="n">
-        <v>6991629</v>
+        <v>6991624</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10258,24 +10273,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10290,22 +10290,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125438548</v>
+        <v>125438544</v>
       </c>
       <c r="B88" t="n">
-        <v>79927</v>
+        <v>90977</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10318,21 +10318,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10342,10 +10342,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>564548</v>
+        <v>564517</v>
       </c>
       <c r="R88" t="n">
-        <v>6991664</v>
+        <v>6991669</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -2671,10 +2671,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125397300</v>
+        <v>125396355</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>78684</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2683,52 +2683,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564442</v>
+        <v>564463</v>
       </c>
       <c r="R21" t="n">
-        <v>6991680</v>
+        <v>6991617</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2760,7 +2746,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2770,12 +2756,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2790,22 +2771,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125395933</v>
+        <v>125397801</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>75025</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2818,42 +2799,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564463</v>
+        <v>564440</v>
       </c>
       <c r="R22" t="n">
-        <v>6991559</v>
+        <v>6991662</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2882,7 +2858,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2892,12 +2868,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2924,10 +2900,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125398434</v>
+        <v>125396221</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>91166</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2940,34 +2916,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564420</v>
+        <v>564445</v>
       </c>
       <c r="R23" t="n">
-        <v>6991658</v>
+        <v>6991608</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2999,7 +2980,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3009,12 +2990,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Lunglav på björk</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,22 +3010,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125397829</v>
+        <v>125396498</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>98269</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3053,31 +3034,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3086,13 +3076,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>564401</v>
+        <v>564463</v>
       </c>
       <c r="R24" t="n">
-        <v>6991629</v>
+        <v>6991617</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3121,7 +3111,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3131,12 +3121,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikliga ringhack på gammal tall</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3151,22 +3136,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125397089</v>
+        <v>125396843</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3175,52 +3160,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>564452</v>
+        <v>564431</v>
       </c>
       <c r="R25" t="n">
-        <v>6991661</v>
+        <v>6991652</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3252,7 +3223,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3262,12 +3233,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt på marken i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3294,10 +3265,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125396762</v>
+        <v>125397219</v>
       </c>
       <c r="B26" t="n">
-        <v>91299</v>
+        <v>80028</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3310,27 +3281,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3339,13 +3314,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>564441</v>
+        <v>564440</v>
       </c>
       <c r="R26" t="n">
-        <v>6991661</v>
+        <v>6991662</v>
       </c>
       <c r="S26" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3374,7 +3349,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3384,7 +3359,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3411,10 +3386,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125398524</v>
+        <v>125397175</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>80028</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3427,43 +3402,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>564457</v>
+        <v>564453</v>
       </c>
       <c r="R27" t="n">
-        <v>6991682</v>
+        <v>6991658</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3495,7 +3461,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3505,12 +3471,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3537,10 +3503,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125397495</v>
+        <v>125395199</v>
       </c>
       <c r="B28" t="n">
-        <v>79795</v>
+        <v>80028</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3549,41 +3515,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>564410</v>
+        <v>564521</v>
       </c>
       <c r="R28" t="n">
-        <v>6991660</v>
+        <v>6991610</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3612,7 +3587,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3622,12 +3597,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gråal</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3642,7 +3617,7 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -3654,10 +3629,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125397385</v>
+        <v>125396600</v>
       </c>
       <c r="B29" t="n">
-        <v>79891</v>
+        <v>80057</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3666,41 +3641,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>564442</v>
+        <v>564463</v>
       </c>
       <c r="R29" t="n">
-        <v>6991680</v>
+        <v>6991617</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3729,7 +3713,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3739,12 +3723,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På sälg i gammal granskog</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3759,7 +3738,7 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -3771,10 +3750,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125396498</v>
+        <v>125397300</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3806,7 +3785,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3825,13 +3804,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>564463</v>
+        <v>564442</v>
       </c>
       <c r="R30" t="n">
-        <v>6991617</v>
+        <v>6991680</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3860,7 +3839,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3870,7 +3849,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3885,22 +3869,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125398718</v>
+        <v>125396883</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>78683</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3909,35 +3893,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3946,10 +3926,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>564439</v>
+        <v>564440</v>
       </c>
       <c r="R31" t="n">
-        <v>6991676</v>
+        <v>6991655</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3981,7 +3961,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3991,12 +3971,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ett stort områden typ 10 kvadratmeter</t>
+          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4011,22 +3991,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125397801</v>
+        <v>125395933</v>
       </c>
       <c r="B32" t="n">
-        <v>74901</v>
+        <v>91166</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4039,37 +4019,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>564440</v>
+        <v>564463</v>
       </c>
       <c r="R32" t="n">
-        <v>6991662</v>
+        <v>6991559</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4098,7 +4083,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4108,12 +4093,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4133,17 +4118,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125396600</v>
+        <v>125397089</v>
       </c>
       <c r="B33" t="n">
-        <v>79920</v>
+        <v>98269</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4152,35 +4137,40 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4189,13 +4179,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>564463</v>
+        <v>564452</v>
       </c>
       <c r="R33" t="n">
-        <v>6991617</v>
+        <v>6991661</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4224,7 +4214,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4234,7 +4224,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4249,22 +4244,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125397175</v>
+        <v>125398468</v>
       </c>
       <c r="B34" t="n">
-        <v>79891</v>
+        <v>78684</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4277,21 +4272,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4301,10 +4296,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>564453</v>
+        <v>564441</v>
       </c>
       <c r="R34" t="n">
-        <v>6991658</v>
+        <v>6991674</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4336,7 +4331,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4346,12 +4341,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På kolad ved på två gamla tallhögstubbar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4378,10 +4373,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125398468</v>
+        <v>125397829</v>
       </c>
       <c r="B35" t="n">
-        <v>78547</v>
+        <v>57635</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4394,34 +4389,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>564441</v>
+        <v>564401</v>
       </c>
       <c r="R35" t="n">
-        <v>6991674</v>
+        <v>6991629</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På kolad ved på två gamla tallhögstubbar</t>
+          <t>Rikliga ringhack på gammal tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4483,12 +4483,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4498,7 +4498,7 @@
         <v>125398362</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4605,17 +4605,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125395199</v>
+        <v>125398524</v>
       </c>
       <c r="B37" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4628,26 +4628,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4661,13 +4661,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>564521</v>
+        <v>564457</v>
       </c>
       <c r="R37" t="n">
-        <v>6991610</v>
+        <v>6991682</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gråal</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4726,22 +4726,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125396355</v>
+        <v>125398718</v>
       </c>
       <c r="B38" t="n">
-        <v>78547</v>
+        <v>98269</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4750,38 +4750,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>564463</v>
+        <v>564439</v>
       </c>
       <c r="R38" t="n">
-        <v>6991617</v>
+        <v>6991676</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4813,7 +4822,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4823,7 +4832,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ett stort områden typ 10 kvadratmeter</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4838,22 +4852,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125396843</v>
+        <v>125398434</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>80028</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4866,21 +4880,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4890,10 +4904,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>564431</v>
+        <v>564420</v>
       </c>
       <c r="R39" t="n">
-        <v>6991652</v>
+        <v>6991658</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4925,7 +4939,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4935,12 +4949,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4955,22 +4969,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125396883</v>
+        <v>125396949</v>
       </c>
       <c r="B40" t="n">
-        <v>78546</v>
+        <v>78684</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4983,29 +4997,24 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
@@ -5047,7 +5056,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5057,7 +5066,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5089,10 +5098,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125397219</v>
+        <v>125396762</v>
       </c>
       <c r="B41" t="n">
-        <v>79891</v>
+        <v>91459</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5105,31 +5114,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5138,13 +5143,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>564440</v>
+        <v>564441</v>
       </c>
       <c r="R41" t="n">
-        <v>6991662</v>
+        <v>6991661</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5173,7 +5178,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5183,7 +5188,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5213,7 +5218,7 @@
         <v>125398578</v>
       </c>
       <c r="B42" t="n">
-        <v>82597</v>
+        <v>82737</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5322,10 +5327,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125396221</v>
+        <v>125397495</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>79932</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5334,43 +5339,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>564445</v>
+        <v>564410</v>
       </c>
       <c r="R43" t="n">
-        <v>6991608</v>
+        <v>6991660</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5432,22 +5432,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125396949</v>
+        <v>125397385</v>
       </c>
       <c r="B44" t="n">
-        <v>78547</v>
+        <v>80028</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5460,21 +5460,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>564440</v>
+        <v>564442</v>
       </c>
       <c r="R44" t="n">
-        <v>6991655</v>
+        <v>6991680</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5519,7 +5519,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5561,10 +5561,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125420523</v>
+        <v>125420536</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>80028</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5577,21 +5577,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>564516</v>
+        <v>564470</v>
       </c>
       <c r="R45" t="n">
-        <v>6991629</v>
+        <v>6991585</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Mycket rikligt på gran under grov asp</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5678,10 +5678,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125420542</v>
+        <v>125426252</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>96522</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5694,37 +5694,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>564429</v>
+        <v>564532</v>
       </c>
       <c r="R46" t="n">
-        <v>6991627</v>
+        <v>6991656</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5751,24 +5751,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5783,22 +5768,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125426252</v>
+        <v>125420527</v>
       </c>
       <c r="B47" t="n">
-        <v>96354</v>
+        <v>98290</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5807,41 +5792,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>564532</v>
+        <v>564499</v>
       </c>
       <c r="R47" t="n">
-        <v>6991656</v>
+        <v>6991597</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5868,9 +5853,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5885,22 +5885,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125420534</v>
+        <v>125438549</v>
       </c>
       <c r="B48" t="n">
-        <v>74677</v>
+        <v>77879</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5909,25 +5909,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>98</v>
+        <v>228579</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk rödprick</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Arthonia incarnata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Th.Fr. ex Almq.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>564500</v>
+        <v>564542</v>
       </c>
       <c r="R48" t="n">
-        <v>6991603</v>
+        <v>6991657</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5970,24 +5970,14 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande grov sälg (75 cm dbh) i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6002,22 +5992,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125420530</v>
+        <v>125426272</v>
       </c>
       <c r="B49" t="n">
-        <v>74713</v>
+        <v>95503</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6030,37 +6020,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6428</v>
+        <v>2809</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>564520</v>
+        <v>564515</v>
       </c>
       <c r="R49" t="n">
-        <v>6991626</v>
+        <v>6991646</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6087,24 +6077,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6119,22 +6094,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125420537</v>
+        <v>125426262</v>
       </c>
       <c r="B50" t="n">
-        <v>79891</v>
+        <v>91617</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6143,41 +6118,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>564470</v>
+        <v>564395</v>
       </c>
       <c r="R50" t="n">
-        <v>6991561</v>
+        <v>6991654</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6204,24 +6179,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6236,22 +6196,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125438545</v>
+        <v>125426255</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>91131</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6260,41 +6220,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>564535</v>
+        <v>564448</v>
       </c>
       <c r="R51" t="n">
-        <v>6991601</v>
+        <v>6991620</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6324,11 +6284,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6343,12 +6298,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6358,7 +6313,7 @@
         <v>125420539</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6472,10 +6427,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125420535</v>
+        <v>125420524</v>
       </c>
       <c r="B53" t="n">
-        <v>95335</v>
+        <v>57635</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6484,25 +6439,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6512,10 +6467,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>564539</v>
+        <v>564474</v>
       </c>
       <c r="R53" t="n">
-        <v>6991663</v>
+        <v>6991608</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6547,7 +6502,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6557,12 +6512,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På marken i gammal fuktig granskog</t>
+          <t>Helt färska och äldre ringhack, rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6589,10 +6544,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125426258</v>
+        <v>125420541</v>
       </c>
       <c r="B54" t="n">
-        <v>57513</v>
+        <v>98269</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6601,49 +6556,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>564461</v>
+        <v>564525</v>
       </c>
       <c r="R54" t="n">
-        <v>6991657</v>
+        <v>6991662</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6670,14 +6617,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>10 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6692,22 +6649,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125426257</v>
+        <v>125420535</v>
       </c>
       <c r="B55" t="n">
-        <v>91012</v>
+        <v>95503</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6716,41 +6673,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>564337</v>
+        <v>564539</v>
       </c>
       <c r="R55" t="n">
-        <v>6991632</v>
+        <v>6991663</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6777,9 +6734,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På marken i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6794,22 +6766,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125426285</v>
+        <v>125426258</v>
       </c>
       <c r="B56" t="n">
-        <v>79926</v>
+        <v>57635</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6818,38 +6790,46 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>564561</v>
+        <v>564461</v>
       </c>
       <c r="R56" t="n">
-        <v>6991616</v>
+        <v>6991657</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6882,6 +6862,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6908,10 +6893,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125420522</v>
+        <v>125426278</v>
       </c>
       <c r="B57" t="n">
-        <v>79428</v>
+        <v>98269</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6920,41 +6905,49 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>564449</v>
+        <v>564453</v>
       </c>
       <c r="R57" t="n">
-        <v>6991631</v>
+        <v>6991629</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6981,54 +6974,40 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På ved på gammal tallhögstubbe i gammal tallskog</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125420538</v>
+        <v>125426277</v>
       </c>
       <c r="B58" t="n">
-        <v>79891</v>
+        <v>98269</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7037,41 +7016,49 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>564491</v>
+        <v>564468</v>
       </c>
       <c r="R58" t="n">
-        <v>6991571</v>
+        <v>6991658</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7098,54 +7085,40 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På gammal sälg i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125426269</v>
+        <v>125426280</v>
       </c>
       <c r="B59" t="n">
-        <v>98135</v>
+        <v>78947</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7154,25 +7127,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7182,10 +7155,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>564521</v>
+        <v>564364</v>
       </c>
       <c r="R59" t="n">
-        <v>6991595</v>
+        <v>6991670</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7244,10 +7217,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125420531</v>
+        <v>125420538</v>
       </c>
       <c r="B60" t="n">
-        <v>91299</v>
+        <v>80028</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7260,21 +7233,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7284,10 +7257,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>564486</v>
+        <v>564491</v>
       </c>
       <c r="R60" t="n">
-        <v>6991573</v>
+        <v>6991571</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7319,7 +7292,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7329,12 +7302,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7361,10 +7334,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125426279</v>
+        <v>125426267</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>91459</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7373,46 +7346,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>564474</v>
+        <v>564405</v>
       </c>
       <c r="R61" t="n">
-        <v>6991589</v>
+        <v>6991645</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7453,7 +7418,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7472,10 +7436,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125420541</v>
+        <v>125426251</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>75025</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7484,41 +7448,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>564525</v>
+        <v>564469</v>
       </c>
       <c r="R62" t="n">
-        <v>6991662</v>
+        <v>6991678</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7545,24 +7509,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>10 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7577,22 +7526,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125420536</v>
+        <v>125426269</v>
       </c>
       <c r="B63" t="n">
-        <v>79891</v>
+        <v>98303</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7601,41 +7550,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>564470</v>
+        <v>564521</v>
       </c>
       <c r="R63" t="n">
-        <v>6991585</v>
+        <v>6991595</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7662,24 +7611,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>13:01</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Mycket rikligt på gran under grov asp</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7694,22 +7628,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125420533</v>
+        <v>125420534</v>
       </c>
       <c r="B64" t="n">
-        <v>79919</v>
+        <v>74800</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7718,25 +7652,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6461</v>
+        <v>98</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk rödprick</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Arthonia incarnata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Th.Fr. ex Almq.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7746,10 +7680,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>564582</v>
+        <v>564500</v>
       </c>
       <c r="R64" t="n">
-        <v>6991673</v>
+        <v>6991603</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7781,7 +7715,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7791,12 +7725,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På bark vid basen av gammal levande grov sälg (75 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7823,10 +7757,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125426255</v>
+        <v>125420542</v>
       </c>
       <c r="B65" t="n">
-        <v>90977</v>
+        <v>78947</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7835,41 +7769,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>564448</v>
+        <v>564429</v>
       </c>
       <c r="R65" t="n">
-        <v>6991620</v>
+        <v>6991627</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7896,9 +7830,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7913,22 +7862,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125420528</v>
+        <v>125426286</v>
       </c>
       <c r="B66" t="n">
-        <v>98122</v>
+        <v>80063</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7941,37 +7890,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>564555</v>
+        <v>564556</v>
       </c>
       <c r="R66" t="n">
         <v>6991665</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7998,24 +7947,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8030,22 +7964,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125426262</v>
+        <v>125420543</v>
       </c>
       <c r="B67" t="n">
-        <v>91457</v>
+        <v>75017</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8054,41 +7988,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>564395</v>
+        <v>564520</v>
       </c>
       <c r="R67" t="n">
-        <v>6991654</v>
+        <v>6991622</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8115,9 +8049,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På ved på gammal granhögstubbe</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8132,22 +8081,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125420524</v>
+        <v>125420523</v>
       </c>
       <c r="B68" t="n">
-        <v>57513</v>
+        <v>91166</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8160,21 +8109,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8184,10 +8133,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>564474</v>
+        <v>564516</v>
       </c>
       <c r="R68" t="n">
-        <v>6991608</v>
+        <v>6991629</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8219,7 +8168,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8229,12 +8178,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Helt färska och äldre ringhack, rikligt på gammal gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8261,10 +8210,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125420529</v>
+        <v>125438544</v>
       </c>
       <c r="B69" t="n">
-        <v>78792</v>
+        <v>91131</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8273,25 +8222,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>336</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Solfjäderlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cheiromycina flabelliformis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>B.Sutton</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8301,10 +8250,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>564492</v>
+        <v>564517</v>
       </c>
       <c r="R69" t="n">
-        <v>6991578</v>
+        <v>6991669</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8334,24 +8283,14 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal död sälg i fuktig gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8366,22 +8305,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125426281</v>
+        <v>125426279</v>
       </c>
       <c r="B70" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8390,38 +8329,46 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>564408</v>
+        <v>564474</v>
       </c>
       <c r="R70" t="n">
-        <v>6991646</v>
+        <v>6991589</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8462,6 +8409,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8480,10 +8428,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125426278</v>
+        <v>125426265</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>91459</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8492,46 +8440,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>564453</v>
+        <v>564336</v>
       </c>
       <c r="R71" t="n">
-        <v>6991629</v>
+        <v>6991633</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8572,7 +8512,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8591,10 +8530,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125420520</v>
+        <v>125420533</v>
       </c>
       <c r="B72" t="n">
-        <v>105102</v>
+        <v>80056</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8607,21 +8546,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221725</v>
+        <v>6461</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8631,10 +8570,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>564498</v>
+        <v>564582</v>
       </c>
       <c r="R72" t="n">
-        <v>6991598</v>
+        <v>6991673</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8666,7 +8605,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8676,7 +8615,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -8708,10 +8647,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125438549</v>
+        <v>125438548</v>
       </c>
       <c r="B73" t="n">
-        <v>77743</v>
+        <v>80064</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8720,25 +8659,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8748,10 +8687,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>564542</v>
+        <v>564548</v>
       </c>
       <c r="R73" t="n">
-        <v>6991657</v>
+        <v>6991664</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8788,7 +8727,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8815,10 +8754,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125426260</v>
+        <v>125420540</v>
       </c>
       <c r="B74" t="n">
-        <v>79920</v>
+        <v>98269</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8827,41 +8766,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>564551</v>
+        <v>564495</v>
       </c>
       <c r="R74" t="n">
-        <v>6991633</v>
+        <v>6991590</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8888,9 +8827,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>40 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8905,22 +8859,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125420543</v>
+        <v>125420528</v>
       </c>
       <c r="B75" t="n">
-        <v>74893</v>
+        <v>98290</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8929,25 +8883,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>308</v>
+        <v>221952</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8957,10 +8911,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>564520</v>
+        <v>564555</v>
       </c>
       <c r="R75" t="n">
-        <v>6991622</v>
+        <v>6991665</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8992,7 +8946,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9002,12 +8956,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9034,10 +8988,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125426254</v>
+        <v>125426285</v>
       </c>
       <c r="B76" t="n">
-        <v>96354</v>
+        <v>80063</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9046,25 +9000,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>53</v>
+        <v>6463</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9074,10 +9028,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>564412</v>
+        <v>564561</v>
       </c>
       <c r="R76" t="n">
-        <v>6991656</v>
+        <v>6991616</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -9136,10 +9090,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125426286</v>
+        <v>125420529</v>
       </c>
       <c r="B77" t="n">
-        <v>79926</v>
+        <v>78929</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9148,41 +9102,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6463</v>
+        <v>336</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Solfjäderlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cheiromycina flabelliformis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>B.Sutton</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>564556</v>
+        <v>564492</v>
       </c>
       <c r="R77" t="n">
-        <v>6991665</v>
+        <v>6991578</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9209,9 +9163,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På bark vid basen av gammal död sälg i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9226,22 +9195,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125438548</v>
+        <v>125426281</v>
       </c>
       <c r="B78" t="n">
-        <v>79927</v>
+        <v>78947</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9250,41 +9219,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>564548</v>
+        <v>564408</v>
       </c>
       <c r="R78" t="n">
-        <v>6991664</v>
+        <v>6991646</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9314,11 +9283,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9333,22 +9297,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125420527</v>
+        <v>125426250</v>
       </c>
       <c r="B79" t="n">
-        <v>98122</v>
+        <v>105278</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9361,37 +9325,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>564499</v>
+        <v>564528</v>
       </c>
       <c r="R79" t="n">
-        <v>6991597</v>
+        <v>6991624</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9418,24 +9382,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9450,22 +9399,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125426272</v>
+        <v>125420520</v>
       </c>
       <c r="B80" t="n">
-        <v>95335</v>
+        <v>105278</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9478,37 +9427,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2809</v>
+        <v>221725</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>564515</v>
+        <v>564498</v>
       </c>
       <c r="R80" t="n">
-        <v>6991646</v>
+        <v>6991598</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9535,9 +9484,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9552,22 +9516,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125426265</v>
+        <v>125426257</v>
       </c>
       <c r="B81" t="n">
-        <v>91299</v>
+        <v>91166</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9580,21 +9544,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9604,10 +9568,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>564336</v>
+        <v>564337</v>
       </c>
       <c r="R81" t="n">
-        <v>6991633</v>
+        <v>6991632</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -9666,10 +9630,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125426267</v>
+        <v>125420531</v>
       </c>
       <c r="B82" t="n">
-        <v>91299</v>
+        <v>91459</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9702,17 +9666,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>564405</v>
+        <v>564486</v>
       </c>
       <c r="R82" t="n">
-        <v>6991645</v>
+        <v>6991573</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9739,9 +9703,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9756,22 +9735,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125426280</v>
+        <v>125438545</v>
       </c>
       <c r="B83" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9784,37 +9763,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>564364</v>
+        <v>564535</v>
       </c>
       <c r="R83" t="n">
-        <v>6991670</v>
+        <v>6991601</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9844,6 +9823,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9858,22 +9842,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125420540</v>
+        <v>125420537</v>
       </c>
       <c r="B84" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9882,25 +9866,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9910,10 +9894,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>564495</v>
+        <v>564470</v>
       </c>
       <c r="R84" t="n">
-        <v>6991590</v>
+        <v>6991561</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9945,7 +9929,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9955,12 +9939,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>40 plantor på marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9987,10 +9971,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125426277</v>
+        <v>125420522</v>
       </c>
       <c r="B85" t="n">
-        <v>98101</v>
+        <v>79565</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9999,49 +9983,41 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>564468</v>
+        <v>564449</v>
       </c>
       <c r="R85" t="n">
-        <v>6991658</v>
+        <v>6991631</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10068,40 +10044,54 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På ved på gammal tallhögstubbe i gammal tallskog</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125426251</v>
+        <v>125420530</v>
       </c>
       <c r="B86" t="n">
-        <v>74901</v>
+        <v>74836</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10110,41 +10100,41 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6440</v>
+        <v>6428</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>564469</v>
+        <v>564520</v>
       </c>
       <c r="R86" t="n">
-        <v>6991678</v>
+        <v>6991626</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10171,9 +10161,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10188,22 +10193,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125426250</v>
+        <v>125426254</v>
       </c>
       <c r="B87" t="n">
-        <v>105102</v>
+        <v>96522</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10212,25 +10217,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221725</v>
+        <v>53</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10240,10 +10245,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>564528</v>
+        <v>564412</v>
       </c>
       <c r="R87" t="n">
-        <v>6991624</v>
+        <v>6991656</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -10302,10 +10307,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125438544</v>
+        <v>125426260</v>
       </c>
       <c r="B88" t="n">
-        <v>90977</v>
+        <v>80057</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10318,37 +10323,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>564517</v>
+        <v>564551</v>
       </c>
       <c r="R88" t="n">
-        <v>6991669</v>
+        <v>6991633</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10378,11 +10383,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10397,12 +10397,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -3386,7 +3386,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125397175</v>
+        <v>125395199</v>
       </c>
       <c r="B27" t="n">
         <v>80028</v>
@@ -3419,20 +3419,29 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>564453</v>
+        <v>564521</v>
       </c>
       <c r="R27" t="n">
-        <v>6991658</v>
+        <v>6991610</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3461,7 +3470,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3471,12 +3480,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På gråal</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3491,7 +3500,7 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -3503,10 +3512,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125395199</v>
+        <v>125396600</v>
       </c>
       <c r="B28" t="n">
-        <v>80028</v>
+        <v>80057</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3515,25 +3524,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3552,13 +3561,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>564521</v>
+        <v>564463</v>
       </c>
       <c r="R28" t="n">
-        <v>6991610</v>
+        <v>6991617</v>
       </c>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3587,7 +3596,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3597,12 +3606,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gråal</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3622,17 +3626,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125396600</v>
+        <v>125397175</v>
       </c>
       <c r="B29" t="n">
-        <v>80057</v>
+        <v>80028</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3641,50 +3645,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>564463</v>
+        <v>564453</v>
       </c>
       <c r="R29" t="n">
-        <v>6991617</v>
+        <v>6991658</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3713,7 +3708,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3723,7 +3718,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3738,12 +3738,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -6427,10 +6427,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125420524</v>
+        <v>125420535</v>
       </c>
       <c r="B53" t="n">
-        <v>57635</v>
+        <v>95503</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6439,25 +6439,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6467,10 +6467,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>564474</v>
+        <v>564539</v>
       </c>
       <c r="R53" t="n">
-        <v>6991608</v>
+        <v>6991663</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6502,7 +6502,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Helt färska och äldre ringhack, rikligt på gammal gran i gammal granskog</t>
+          <t>På marken i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6544,10 +6544,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125420541</v>
+        <v>125420524</v>
       </c>
       <c r="B54" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6556,25 +6556,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6584,10 +6584,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>564525</v>
+        <v>564474</v>
       </c>
       <c r="R54" t="n">
-        <v>6991662</v>
+        <v>6991608</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6629,12 +6629,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>10 plantor på marken i gammal granskog</t>
+          <t>Helt färska och äldre ringhack, rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6661,10 +6661,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125420535</v>
+        <v>125420541</v>
       </c>
       <c r="B55" t="n">
-        <v>95503</v>
+        <v>98269</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6673,25 +6673,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6701,10 +6701,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>564539</v>
+        <v>564525</v>
       </c>
       <c r="R55" t="n">
-        <v>6991663</v>
+        <v>6991662</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På marken i gammal fuktig granskog</t>
+          <t>10 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7217,10 +7217,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125420538</v>
+        <v>125426267</v>
       </c>
       <c r="B60" t="n">
-        <v>80028</v>
+        <v>91459</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7233,37 +7233,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>564491</v>
+        <v>564405</v>
       </c>
       <c r="R60" t="n">
-        <v>6991571</v>
+        <v>6991645</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7290,24 +7290,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7322,22 +7307,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125426267</v>
+        <v>125420538</v>
       </c>
       <c r="B61" t="n">
-        <v>91459</v>
+        <v>80028</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7350,37 +7335,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>564405</v>
+        <v>564491</v>
       </c>
       <c r="R61" t="n">
-        <v>6991645</v>
+        <v>6991571</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7407,9 +7392,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7424,12 +7424,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7640,10 +7640,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125420534</v>
+        <v>125420542</v>
       </c>
       <c r="B64" t="n">
-        <v>74800</v>
+        <v>78947</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7652,25 +7652,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>98</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk rödprick</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Arthonia incarnata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Th.Fr. ex Almq.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7680,10 +7680,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>564500</v>
+        <v>564429</v>
       </c>
       <c r="R64" t="n">
-        <v>6991603</v>
+        <v>6991627</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande grov sälg (75 cm dbh) i gammal granskog</t>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7757,10 +7757,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125420542</v>
+        <v>125420534</v>
       </c>
       <c r="B65" t="n">
-        <v>78947</v>
+        <v>74800</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7769,25 +7769,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>98</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk rödprick</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia incarnata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Th.Fr. ex Almq.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>564429</v>
+        <v>564500</v>
       </c>
       <c r="R65" t="n">
-        <v>6991627</v>
+        <v>6991603</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7832,7 +7832,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
+          <t>På bark vid basen av gammal levande grov sälg (75 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7874,10 +7874,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125426286</v>
+        <v>125420543</v>
       </c>
       <c r="B66" t="n">
-        <v>80063</v>
+        <v>75017</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7886,41 +7886,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6463</v>
+        <v>308</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>564556</v>
+        <v>564520</v>
       </c>
       <c r="R66" t="n">
-        <v>6991665</v>
+        <v>6991622</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7947,9 +7947,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På ved på gammal granhögstubbe</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7964,22 +7979,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125420543</v>
+        <v>125426286</v>
       </c>
       <c r="B67" t="n">
-        <v>75017</v>
+        <v>80063</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7988,41 +8003,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>308</v>
+        <v>6463</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>564520</v>
+        <v>564556</v>
       </c>
       <c r="R67" t="n">
-        <v>6991622</v>
+        <v>6991665</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8049,24 +8064,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På ved på gammal granhögstubbe</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8081,12 +8081,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8317,10 +8317,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125426279</v>
+        <v>125420533</v>
       </c>
       <c r="B70" t="n">
-        <v>98269</v>
+        <v>80056</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8329,49 +8329,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>564474</v>
+        <v>564582</v>
       </c>
       <c r="R70" t="n">
-        <v>6991589</v>
+        <v>6991673</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8398,30 +8390,44 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8530,10 +8536,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125420533</v>
+        <v>125426279</v>
       </c>
       <c r="B72" t="n">
-        <v>80056</v>
+        <v>98269</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8542,41 +8548,49 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>564582</v>
+        <v>564474</v>
       </c>
       <c r="R72" t="n">
-        <v>6991673</v>
+        <v>6991589</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8603,54 +8617,40 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125438548</v>
+        <v>125420540</v>
       </c>
       <c r="B73" t="n">
-        <v>80064</v>
+        <v>98269</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8659,25 +8659,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8687,10 +8687,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>564548</v>
+        <v>564495</v>
       </c>
       <c r="R73" t="n">
-        <v>6991664</v>
+        <v>6991590</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8720,14 +8720,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>40 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8742,22 +8752,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125420540</v>
+        <v>125438548</v>
       </c>
       <c r="B74" t="n">
-        <v>98269</v>
+        <v>80064</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8766,25 +8776,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8794,10 +8804,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>564495</v>
+        <v>564548</v>
       </c>
       <c r="R74" t="n">
-        <v>6991590</v>
+        <v>6991664</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8827,24 +8837,14 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>40 plantor på marken i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8859,12 +8859,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9528,10 +9528,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125426257</v>
+        <v>125420531</v>
       </c>
       <c r="B81" t="n">
-        <v>91166</v>
+        <v>91459</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9544,37 +9544,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>564337</v>
+        <v>564486</v>
       </c>
       <c r="R81" t="n">
-        <v>6991632</v>
+        <v>6991573</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9601,9 +9601,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9618,22 +9633,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125420531</v>
+        <v>125438545</v>
       </c>
       <c r="B82" t="n">
-        <v>91459</v>
+        <v>57635</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9646,21 +9661,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9670,10 +9685,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>564486</v>
+        <v>564535</v>
       </c>
       <c r="R82" t="n">
-        <v>6991573</v>
+        <v>6991601</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9703,24 +9718,14 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9735,22 +9740,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125438545</v>
+        <v>125420537</v>
       </c>
       <c r="B83" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9763,21 +9768,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9787,10 +9792,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>564535</v>
+        <v>564470</v>
       </c>
       <c r="R83" t="n">
-        <v>6991601</v>
+        <v>6991561</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9820,14 +9825,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9842,22 +9857,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125420537</v>
+        <v>125426257</v>
       </c>
       <c r="B84" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9870,37 +9885,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>564470</v>
+        <v>564337</v>
       </c>
       <c r="R84" t="n">
-        <v>6991561</v>
+        <v>6991632</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9927,24 +9942,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9959,12 +9959,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -2671,10 +2671,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125396355</v>
+        <v>125395850</v>
       </c>
       <c r="B21" t="n">
-        <v>78684</v>
+        <v>91166</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2687,24 +2687,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
@@ -2714,7 +2719,7 @@
         <v>564463</v>
       </c>
       <c r="R21" t="n">
-        <v>6991617</v>
+        <v>6991559</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2746,7 +2751,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2756,7 +2761,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2783,10 +2788,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125397801</v>
+        <v>125396883</v>
       </c>
       <c r="B22" t="n">
-        <v>75025</v>
+        <v>78683</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2799,24 +2804,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
@@ -2826,10 +2836,10 @@
         <v>564440</v>
       </c>
       <c r="R22" t="n">
-        <v>6991662</v>
+        <v>6991655</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2858,7 +2868,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2868,12 +2878,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2888,7 +2898,7 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -2900,10 +2910,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125396221</v>
+        <v>125396355</v>
       </c>
       <c r="B23" t="n">
-        <v>91166</v>
+        <v>78684</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2916,39 +2926,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564445</v>
+        <v>564463</v>
       </c>
       <c r="R23" t="n">
-        <v>6991608</v>
+        <v>6991617</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,7 +2985,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2990,12 +2995,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3022,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125396498</v>
+        <v>125398362</v>
       </c>
       <c r="B24" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3034,55 +3034,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>564463</v>
+        <v>564453</v>
       </c>
       <c r="R24" t="n">
-        <v>6991617</v>
+        <v>6991691</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3111,7 +3097,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3121,7 +3107,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,12 +3127,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3265,10 +3256,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125397219</v>
+        <v>125397259</v>
       </c>
       <c r="B26" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3277,35 +3268,40 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3314,13 +3310,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>564440</v>
+        <v>564442</v>
       </c>
       <c r="R26" t="n">
-        <v>6991662</v>
+        <v>6991680</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3349,7 +3345,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3359,7 +3355,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3374,22 +3375,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125395199</v>
+        <v>125396762</v>
       </c>
       <c r="B27" t="n">
-        <v>80028</v>
+        <v>91459</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3402,31 +3403,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3435,13 +3432,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>564521</v>
+        <v>564441</v>
       </c>
       <c r="R27" t="n">
-        <v>6991610</v>
+        <v>6991661</v>
       </c>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3470,7 +3467,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3480,12 +3477,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gråal</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3505,17 +3497,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125396600</v>
+        <v>125396949</v>
       </c>
       <c r="B28" t="n">
-        <v>80057</v>
+        <v>78684</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3524,50 +3516,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>564463</v>
+        <v>564440</v>
       </c>
       <c r="R28" t="n">
-        <v>6991617</v>
+        <v>6991655</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3596,7 +3579,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3606,7 +3589,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3621,19 +3609,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125397175</v>
+        <v>125395199</v>
       </c>
       <c r="B29" t="n">
         <v>80028</v>
@@ -3666,20 +3654,29 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>564453</v>
+        <v>564521</v>
       </c>
       <c r="R29" t="n">
-        <v>6991658</v>
+        <v>6991610</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3708,7 +3705,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3718,12 +3715,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På gråal</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3738,22 +3735,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125397300</v>
+        <v>125397175</v>
       </c>
       <c r="B30" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3762,52 +3759,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>564442</v>
+        <v>564453</v>
       </c>
       <c r="R30" t="n">
-        <v>6991680</v>
+        <v>6991658</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3839,7 +3822,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3849,12 +3832,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3881,10 +3864,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125396883</v>
+        <v>125397801</v>
       </c>
       <c r="B31" t="n">
-        <v>78683</v>
+        <v>75025</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3897,29 +3880,24 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
@@ -3929,10 +3907,10 @@
         <v>564440</v>
       </c>
       <c r="R31" t="n">
-        <v>6991655</v>
+        <v>6991662</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3961,7 +3939,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3971,12 +3949,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3991,22 +3969,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125395933</v>
+        <v>125398434</v>
       </c>
       <c r="B32" t="n">
-        <v>91166</v>
+        <v>80028</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4019,39 +3997,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>564463</v>
+        <v>564420</v>
       </c>
       <c r="R32" t="n">
-        <v>6991559</v>
+        <v>6991658</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4083,7 +4056,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4093,12 +4066,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4113,22 +4086,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125397089</v>
+        <v>125398524</v>
       </c>
       <c r="B33" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4137,25 +4110,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4165,12 +4138,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4179,10 +4147,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>564452</v>
+        <v>564457</v>
       </c>
       <c r="R33" t="n">
-        <v>6991661</v>
+        <v>6991682</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4214,7 +4182,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4224,12 +4192,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt på marken i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,10 +4224,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125398468</v>
+        <v>125396600</v>
       </c>
       <c r="B34" t="n">
-        <v>78684</v>
+        <v>80057</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4268,41 +4236,50 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>564441</v>
+        <v>564463</v>
       </c>
       <c r="R34" t="n">
-        <v>6991674</v>
+        <v>6991617</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4331,7 +4308,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4341,12 +4318,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På kolad ved på två gamla tallhögstubbar</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4361,22 +4333,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125397829</v>
+        <v>125397089</v>
       </c>
       <c r="B35" t="n">
-        <v>57635</v>
+        <v>98269</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4385,31 +4357,40 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4418,10 +4399,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>564401</v>
+        <v>564452</v>
       </c>
       <c r="R35" t="n">
-        <v>6991629</v>
+        <v>6991661</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4453,7 +4434,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4463,12 +4444,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikliga ringhack på gammal tall</t>
+          <t>Rikligt på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4483,22 +4464,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125398362</v>
+        <v>125397495</v>
       </c>
       <c r="B36" t="n">
-        <v>91166</v>
+        <v>79932</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4507,25 +4488,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4535,10 +4516,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>564453</v>
+        <v>564410</v>
       </c>
       <c r="R36" t="n">
-        <v>6991691</v>
+        <v>6991660</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4570,7 +4551,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4580,12 +4561,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4612,10 +4593,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125398524</v>
+        <v>125398718</v>
       </c>
       <c r="B37" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4624,35 +4605,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4661,10 +4642,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>564457</v>
+        <v>564439</v>
       </c>
       <c r="R37" t="n">
-        <v>6991682</v>
+        <v>6991676</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4696,7 +4677,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4706,12 +4687,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>Ett stort områden typ 10 kvadratmeter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4726,22 +4707,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125398718</v>
+        <v>125396221</v>
       </c>
       <c r="B38" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4750,35 +4731,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4787,10 +4764,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>564439</v>
+        <v>564445</v>
       </c>
       <c r="R38" t="n">
-        <v>6991676</v>
+        <v>6991608</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4822,7 +4799,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4832,12 +4809,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ett stort områden typ 10 kvadratmeter</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4852,19 +4829,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125398434</v>
+        <v>125397219</v>
       </c>
       <c r="B39" t="n">
         <v>80028</v>
@@ -4897,20 +4874,29 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>564420</v>
+        <v>564440</v>
       </c>
       <c r="R39" t="n">
-        <v>6991658</v>
+        <v>6991662</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4939,7 +4925,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4949,12 +4935,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4969,22 +4950,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125396949</v>
+        <v>125397385</v>
       </c>
       <c r="B40" t="n">
-        <v>78684</v>
+        <v>80028</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4997,21 +4978,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5021,10 +5002,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>564440</v>
+        <v>564442</v>
       </c>
       <c r="R40" t="n">
-        <v>6991655</v>
+        <v>6991680</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5056,7 +5037,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5066,12 +5047,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5098,10 +5079,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125396762</v>
+        <v>125397829</v>
       </c>
       <c r="B41" t="n">
-        <v>91459</v>
+        <v>57635</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5114,27 +5095,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5143,13 +5124,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>564441</v>
+        <v>564401</v>
       </c>
       <c r="R41" t="n">
-        <v>6991661</v>
+        <v>6991629</v>
       </c>
       <c r="S41" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5178,7 +5159,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5188,7 +5169,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikliga ringhack på gammal tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5203,22 +5189,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125398578</v>
+        <v>125398468</v>
       </c>
       <c r="B42" t="n">
-        <v>82737</v>
+        <v>78684</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5231,21 +5217,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5255,10 +5241,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>564440</v>
+        <v>564441</v>
       </c>
       <c r="R42" t="n">
-        <v>6991662</v>
+        <v>6991674</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5290,7 +5276,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5300,7 +5286,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På kolad ved på två gamla tallhögstubbar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5315,22 +5306,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125397495</v>
+        <v>125396498</v>
       </c>
       <c r="B43" t="n">
-        <v>79932</v>
+        <v>98269</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5339,41 +5330,55 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>564410</v>
+        <v>564463</v>
       </c>
       <c r="R43" t="n">
-        <v>6991660</v>
+        <v>6991617</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5402,7 +5407,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5412,12 +5417,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5432,22 +5432,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125397385</v>
+        <v>125398578</v>
       </c>
       <c r="B44" t="n">
-        <v>80028</v>
+        <v>82737</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5460,21 +5460,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>564442</v>
+        <v>564440</v>
       </c>
       <c r="R44" t="n">
-        <v>6991680</v>
+        <v>6991662</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5519,7 +5519,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5529,12 +5529,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På sälg i gammal granskog</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5549,22 +5544,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125420536</v>
+        <v>125420542</v>
       </c>
       <c r="B45" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5577,21 +5572,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5601,10 +5596,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>564470</v>
+        <v>564429</v>
       </c>
       <c r="R45" t="n">
-        <v>6991585</v>
+        <v>6991627</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5636,7 +5631,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5646,12 +5641,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Mycket rikligt på gran under grov asp</t>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5678,10 +5673,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125426252</v>
+        <v>125426260</v>
       </c>
       <c r="B46" t="n">
-        <v>96522</v>
+        <v>80057</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5690,25 +5685,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5718,10 +5713,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>564532</v>
+        <v>564551</v>
       </c>
       <c r="R46" t="n">
-        <v>6991656</v>
+        <v>6991633</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5780,10 +5775,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125420527</v>
+        <v>125420536</v>
       </c>
       <c r="B47" t="n">
-        <v>98290</v>
+        <v>80028</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5792,25 +5787,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5820,10 +5815,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>564499</v>
+        <v>564470</v>
       </c>
       <c r="R47" t="n">
-        <v>6991597</v>
+        <v>6991585</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5855,7 +5850,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5865,12 +5860,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>Mycket rikligt på gran under grov asp</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5897,10 +5892,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125438549</v>
+        <v>125420537</v>
       </c>
       <c r="B48" t="n">
-        <v>77879</v>
+        <v>80028</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5913,21 +5908,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5937,10 +5932,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>564542</v>
+        <v>564470</v>
       </c>
       <c r="R48" t="n">
-        <v>6991657</v>
+        <v>6991561</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5970,14 +5965,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5992,22 +5997,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125426272</v>
+        <v>125420524</v>
       </c>
       <c r="B49" t="n">
-        <v>95503</v>
+        <v>57635</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6016,41 +6021,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>564515</v>
+        <v>564474</v>
       </c>
       <c r="R49" t="n">
-        <v>6991646</v>
+        <v>6991608</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6077,9 +6082,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Helt färska och äldre ringhack, rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6094,22 +6114,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125426262</v>
+        <v>125426278</v>
       </c>
       <c r="B50" t="n">
-        <v>91617</v>
+        <v>98269</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6122,34 +6142,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>564395</v>
+        <v>564453</v>
       </c>
       <c r="R50" t="n">
-        <v>6991654</v>
+        <v>6991629</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6190,6 +6218,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6208,10 +6237,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125426255</v>
+        <v>125426277</v>
       </c>
       <c r="B51" t="n">
-        <v>91131</v>
+        <v>98269</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6220,38 +6249,46 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>564448</v>
+        <v>564468</v>
       </c>
       <c r="R51" t="n">
-        <v>6991620</v>
+        <v>6991658</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6292,6 +6329,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6310,10 +6348,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125420539</v>
+        <v>125426285</v>
       </c>
       <c r="B52" t="n">
-        <v>98269</v>
+        <v>80063</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6322,41 +6360,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>564466</v>
+        <v>564561</v>
       </c>
       <c r="R52" t="n">
-        <v>6991587</v>
+        <v>6991616</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6383,24 +6421,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>60 plantor på marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6415,22 +6438,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125420535</v>
+        <v>125438548</v>
       </c>
       <c r="B53" t="n">
-        <v>95503</v>
+        <v>80064</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6443,21 +6466,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2809</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6467,10 +6490,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>564539</v>
+        <v>564548</v>
       </c>
       <c r="R53" t="n">
-        <v>6991663</v>
+        <v>6991664</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6500,24 +6523,14 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På marken i gammal fuktig granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6532,22 +6545,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125420524</v>
+        <v>125426262</v>
       </c>
       <c r="B54" t="n">
-        <v>57635</v>
+        <v>91617</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6556,41 +6569,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>564474</v>
+        <v>564395</v>
       </c>
       <c r="R54" t="n">
-        <v>6991608</v>
+        <v>6991654</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6617,24 +6630,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Helt färska och äldre ringhack, rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6649,22 +6647,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125420541</v>
+        <v>125420523</v>
       </c>
       <c r="B55" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6673,25 +6671,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6701,10 +6699,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>564525</v>
+        <v>564516</v>
       </c>
       <c r="R55" t="n">
-        <v>6991662</v>
+        <v>6991629</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6736,7 +6734,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6746,12 +6744,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>10 plantor på marken i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6778,10 +6776,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125426258</v>
+        <v>125420522</v>
       </c>
       <c r="B56" t="n">
-        <v>57635</v>
+        <v>79565</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6794,45 +6792,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>564461</v>
+        <v>564449</v>
       </c>
       <c r="R56" t="n">
-        <v>6991657</v>
+        <v>6991631</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6859,14 +6849,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På ved på gammal tallhögstubbe i gammal tallskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6881,22 +6881,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125426278</v>
+        <v>125438545</v>
       </c>
       <c r="B57" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6905,49 +6905,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>564453</v>
+        <v>564535</v>
       </c>
       <c r="R57" t="n">
-        <v>6991629</v>
+        <v>6991601</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6979,35 +6971,39 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125426277</v>
+        <v>125420520</v>
       </c>
       <c r="B58" t="n">
-        <v>98269</v>
+        <v>105278</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7016,49 +7012,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>564468</v>
+        <v>564498</v>
       </c>
       <c r="R58" t="n">
-        <v>6991658</v>
+        <v>6991598</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7085,40 +7073,54 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125426280</v>
+        <v>125420540</v>
       </c>
       <c r="B59" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7127,41 +7129,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>564364</v>
+        <v>564495</v>
       </c>
       <c r="R59" t="n">
-        <v>6991670</v>
+        <v>6991590</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7188,9 +7190,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>40 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7205,22 +7222,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125426267</v>
+        <v>125426250</v>
       </c>
       <c r="B60" t="n">
-        <v>91459</v>
+        <v>105278</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7229,25 +7246,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>221725</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7257,10 +7274,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>564405</v>
+        <v>564528</v>
       </c>
       <c r="R60" t="n">
-        <v>6991645</v>
+        <v>6991624</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7319,10 +7336,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125420538</v>
+        <v>125426269</v>
       </c>
       <c r="B61" t="n">
-        <v>80028</v>
+        <v>98303</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7331,41 +7348,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>564491</v>
+        <v>564521</v>
       </c>
       <c r="R61" t="n">
-        <v>6991571</v>
+        <v>6991595</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7392,24 +7409,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7424,22 +7426,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125426251</v>
+        <v>125426255</v>
       </c>
       <c r="B62" t="n">
-        <v>75025</v>
+        <v>91131</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7448,25 +7450,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7476,10 +7478,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>564469</v>
+        <v>564448</v>
       </c>
       <c r="R62" t="n">
-        <v>6991678</v>
+        <v>6991620</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7538,10 +7540,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125426269</v>
+        <v>125420538</v>
       </c>
       <c r="B63" t="n">
-        <v>98303</v>
+        <v>80028</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7550,41 +7552,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>564521</v>
+        <v>564491</v>
       </c>
       <c r="R63" t="n">
-        <v>6991595</v>
+        <v>6991571</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7611,9 +7613,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7628,22 +7645,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125420542</v>
+        <v>125420533</v>
       </c>
       <c r="B64" t="n">
-        <v>78947</v>
+        <v>80056</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7652,25 +7669,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7680,10 +7697,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>564429</v>
+        <v>564582</v>
       </c>
       <c r="R64" t="n">
-        <v>6991627</v>
+        <v>6991673</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7715,7 +7732,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7725,12 +7742,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7757,10 +7774,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125420534</v>
+        <v>125420543</v>
       </c>
       <c r="B65" t="n">
-        <v>74800</v>
+        <v>75017</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7769,25 +7786,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>98</v>
+        <v>308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk rödprick</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Arthonia incarnata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Th.Fr. ex Almq.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7797,10 +7814,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>564500</v>
+        <v>564520</v>
       </c>
       <c r="R65" t="n">
-        <v>6991603</v>
+        <v>6991622</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7832,7 +7849,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7842,12 +7859,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande grov sälg (75 cm dbh) i gammal granskog</t>
+          <t>På ved på gammal granhögstubbe</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7874,10 +7891,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125420543</v>
+        <v>125420541</v>
       </c>
       <c r="B66" t="n">
-        <v>75017</v>
+        <v>98269</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7886,25 +7903,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7914,10 +7931,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>564520</v>
+        <v>564525</v>
       </c>
       <c r="R66" t="n">
-        <v>6991622</v>
+        <v>6991662</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7949,7 +7966,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7959,12 +7976,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe</t>
+          <t>10 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7991,10 +8008,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125426286</v>
+        <v>125420539</v>
       </c>
       <c r="B67" t="n">
-        <v>80063</v>
+        <v>98269</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8003,41 +8020,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>564556</v>
+        <v>564466</v>
       </c>
       <c r="R67" t="n">
-        <v>6991665</v>
+        <v>6991587</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8064,9 +8081,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>60 plantor på marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8081,22 +8113,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125420523</v>
+        <v>125438549</v>
       </c>
       <c r="B68" t="n">
-        <v>91166</v>
+        <v>77879</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8109,21 +8141,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8133,10 +8165,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>564516</v>
+        <v>564542</v>
       </c>
       <c r="R68" t="n">
-        <v>6991629</v>
+        <v>6991657</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8166,24 +8198,14 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8198,22 +8220,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125438544</v>
+        <v>125426257</v>
       </c>
       <c r="B69" t="n">
-        <v>91131</v>
+        <v>91166</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8222,41 +8244,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>564517</v>
+        <v>564337</v>
       </c>
       <c r="R69" t="n">
-        <v>6991669</v>
+        <v>6991632</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8286,11 +8308,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8305,22 +8322,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125420533</v>
+        <v>125426286</v>
       </c>
       <c r="B70" t="n">
-        <v>80056</v>
+        <v>80063</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8333,37 +8350,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6461</v>
+        <v>6463</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>564582</v>
+        <v>564556</v>
       </c>
       <c r="R70" t="n">
-        <v>6991673</v>
+        <v>6991665</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8390,24 +8407,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8422,22 +8424,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125426265</v>
+        <v>125420530</v>
       </c>
       <c r="B71" t="n">
-        <v>91459</v>
+        <v>74836</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8446,41 +8448,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>658</v>
+        <v>6428</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>564336</v>
+        <v>564520</v>
       </c>
       <c r="R71" t="n">
-        <v>6991633</v>
+        <v>6991626</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8507,9 +8509,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8524,22 +8541,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125426279</v>
+        <v>125426281</v>
       </c>
       <c r="B72" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8548,46 +8565,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>564474</v>
+        <v>564408</v>
       </c>
       <c r="R72" t="n">
-        <v>6991589</v>
+        <v>6991646</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8628,7 +8637,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8647,10 +8655,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125420540</v>
+        <v>125420534</v>
       </c>
       <c r="B73" t="n">
-        <v>98269</v>
+        <v>74800</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8663,21 +8671,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>98</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk rödprick</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia incarnata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Th.Fr. ex Almq.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8687,10 +8695,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>564495</v>
+        <v>564500</v>
       </c>
       <c r="R73" t="n">
-        <v>6991590</v>
+        <v>6991603</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8722,7 +8730,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8732,12 +8740,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>40 plantor på marken i gammal granskog</t>
+          <t>På bark vid basen av gammal levande grov sälg (75 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8764,10 +8772,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125438548</v>
+        <v>125426251</v>
       </c>
       <c r="B74" t="n">
-        <v>80064</v>
+        <v>75025</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8776,41 +8784,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>564548</v>
+        <v>564469</v>
       </c>
       <c r="R74" t="n">
-        <v>6991664</v>
+        <v>6991678</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8840,11 +8848,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8859,22 +8862,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125420528</v>
+        <v>125426267</v>
       </c>
       <c r="B75" t="n">
-        <v>98290</v>
+        <v>91459</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8883,41 +8886,41 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>564555</v>
+        <v>564405</v>
       </c>
       <c r="R75" t="n">
-        <v>6991665</v>
+        <v>6991645</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8944,24 +8947,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8976,22 +8964,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125426285</v>
+        <v>125426265</v>
       </c>
       <c r="B76" t="n">
-        <v>80063</v>
+        <v>91459</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9000,25 +8988,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9028,10 +9016,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>564561</v>
+        <v>564336</v>
       </c>
       <c r="R76" t="n">
-        <v>6991616</v>
+        <v>6991633</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -9090,10 +9078,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125420529</v>
+        <v>125426280</v>
       </c>
       <c r="B77" t="n">
-        <v>78929</v>
+        <v>78947</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9106,37 +9094,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>336</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Solfjäderlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cheiromycina flabelliformis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>B.Sutton</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>564492</v>
+        <v>564364</v>
       </c>
       <c r="R77" t="n">
-        <v>6991578</v>
+        <v>6991670</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9163,24 +9151,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På bark vid basen av gammal död sälg i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9195,22 +9168,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125426281</v>
+        <v>125426252</v>
       </c>
       <c r="B78" t="n">
-        <v>78947</v>
+        <v>96522</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9223,21 +9196,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9247,10 +9220,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>564408</v>
+        <v>564532</v>
       </c>
       <c r="R78" t="n">
-        <v>6991646</v>
+        <v>6991656</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -9309,10 +9282,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125426250</v>
+        <v>125426272</v>
       </c>
       <c r="B79" t="n">
-        <v>105278</v>
+        <v>95503</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9325,21 +9298,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221725</v>
+        <v>2809</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9349,10 +9322,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>564528</v>
+        <v>564515</v>
       </c>
       <c r="R79" t="n">
-        <v>6991624</v>
+        <v>6991646</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -9411,10 +9384,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125420520</v>
+        <v>125420535</v>
       </c>
       <c r="B80" t="n">
-        <v>105278</v>
+        <v>95503</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9427,21 +9400,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221725</v>
+        <v>2809</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9451,10 +9424,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>564498</v>
+        <v>564539</v>
       </c>
       <c r="R80" t="n">
-        <v>6991598</v>
+        <v>6991663</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9486,7 +9459,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9496,12 +9469,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9528,10 +9501,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125420531</v>
+        <v>125426258</v>
       </c>
       <c r="B81" t="n">
-        <v>91459</v>
+        <v>57635</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9544,37 +9517,45 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>564486</v>
+        <v>564461</v>
       </c>
       <c r="R81" t="n">
-        <v>6991573</v>
+        <v>6991657</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9601,24 +9582,14 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9633,22 +9604,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125438545</v>
+        <v>125426254</v>
       </c>
       <c r="B82" t="n">
-        <v>57635</v>
+        <v>96522</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9661,37 +9632,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>564535</v>
+        <v>564412</v>
       </c>
       <c r="R82" t="n">
-        <v>6991601</v>
+        <v>6991656</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9721,11 +9692,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9740,22 +9706,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125420537</v>
+        <v>125420531</v>
       </c>
       <c r="B83" t="n">
-        <v>80028</v>
+        <v>91459</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9768,21 +9734,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9792,10 +9758,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>564470</v>
+        <v>564486</v>
       </c>
       <c r="R83" t="n">
-        <v>6991561</v>
+        <v>6991573</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9827,7 +9793,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9837,12 +9803,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9869,10 +9835,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125426257</v>
+        <v>125420529</v>
       </c>
       <c r="B84" t="n">
-        <v>91166</v>
+        <v>78929</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9885,37 +9851,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>336</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Solfjäderlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cheiromycina flabelliformis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>B.Sutton</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>564337</v>
+        <v>564492</v>
       </c>
       <c r="R84" t="n">
-        <v>6991632</v>
+        <v>6991578</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9942,9 +9908,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På bark vid basen av gammal död sälg i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9959,22 +9940,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125420522</v>
+        <v>125438544</v>
       </c>
       <c r="B85" t="n">
-        <v>79565</v>
+        <v>91131</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9983,25 +9964,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10011,10 +9992,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>564449</v>
+        <v>564517</v>
       </c>
       <c r="R85" t="n">
-        <v>6991631</v>
+        <v>6991669</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10044,24 +10025,14 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På ved på gammal tallhögstubbe i gammal tallskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10076,22 +10047,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125420530</v>
+        <v>125426279</v>
       </c>
       <c r="B86" t="n">
-        <v>74836</v>
+        <v>98269</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10100,41 +10071,49 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>564520</v>
+        <v>564474</v>
       </c>
       <c r="R86" t="n">
-        <v>6991626</v>
+        <v>6991589</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10161,54 +10140,40 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125426254</v>
+        <v>125420527</v>
       </c>
       <c r="B87" t="n">
-        <v>96522</v>
+        <v>98290</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10217,41 +10182,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53</v>
+        <v>221952</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>564412</v>
+        <v>564499</v>
       </c>
       <c r="R87" t="n">
-        <v>6991656</v>
+        <v>6991597</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10278,9 +10243,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10295,22 +10275,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125426260</v>
+        <v>125420528</v>
       </c>
       <c r="B88" t="n">
-        <v>80057</v>
+        <v>98290</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10323,37 +10303,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>564551</v>
+        <v>564555</v>
       </c>
       <c r="R88" t="n">
-        <v>6991633</v>
+        <v>6991665</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10380,9 +10360,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10397,12 +10392,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -3504,10 +3504,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125396949</v>
+        <v>125395199</v>
       </c>
       <c r="B28" t="n">
-        <v>78684</v>
+        <v>80028</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3520,37 +3520,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>564440</v>
+        <v>564521</v>
       </c>
       <c r="R28" t="n">
-        <v>6991655</v>
+        <v>6991610</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3579,7 +3588,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3589,12 +3598,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
+          <t>På gråal</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3609,22 +3618,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125395199</v>
+        <v>125396949</v>
       </c>
       <c r="B29" t="n">
-        <v>80028</v>
+        <v>78684</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3637,46 +3646,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>564521</v>
+        <v>564440</v>
       </c>
       <c r="R29" t="n">
-        <v>6991610</v>
+        <v>6991655</v>
       </c>
       <c r="S29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gråal</t>
+          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3735,12 +3735,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -5079,10 +5079,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125397829</v>
+        <v>125398468</v>
       </c>
       <c r="B41" t="n">
-        <v>57635</v>
+        <v>78684</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5095,39 +5095,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>564401</v>
+        <v>564441</v>
       </c>
       <c r="R41" t="n">
-        <v>6991629</v>
+        <v>6991674</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5159,7 +5154,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5169,12 +5164,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rikliga ringhack på gammal tall</t>
+          <t>På kolad ved på två gamla tallhögstubbar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5189,22 +5184,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125398468</v>
+        <v>125396498</v>
       </c>
       <c r="B42" t="n">
-        <v>78684</v>
+        <v>98269</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5213,41 +5208,55 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>564441</v>
+        <v>564463</v>
       </c>
       <c r="R42" t="n">
-        <v>6991674</v>
+        <v>6991617</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5276,7 +5285,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5286,12 +5295,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På kolad ved på två gamla tallhögstubbar</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5306,7 +5310,7 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -5318,10 +5322,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125396498</v>
+        <v>125397829</v>
       </c>
       <c r="B43" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5330,40 +5334,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5372,13 +5367,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>564463</v>
+        <v>564401</v>
       </c>
       <c r="R43" t="n">
-        <v>6991617</v>
+        <v>6991629</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5407,7 +5402,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5417,7 +5412,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikliga ringhack på gammal tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5432,12 +5432,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6776,10 +6776,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125420522</v>
+        <v>125438545</v>
       </c>
       <c r="B56" t="n">
-        <v>79565</v>
+        <v>57635</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6792,21 +6792,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>564449</v>
+        <v>564535</v>
       </c>
       <c r="R56" t="n">
-        <v>6991631</v>
+        <v>6991601</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6849,24 +6849,14 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På ved på gammal tallhögstubbe i gammal tallskog</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6881,22 +6871,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125438545</v>
+        <v>125420520</v>
       </c>
       <c r="B57" t="n">
-        <v>57635</v>
+        <v>105278</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6905,25 +6895,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6933,10 +6923,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>564535</v>
+        <v>564498</v>
       </c>
       <c r="R57" t="n">
-        <v>6991601</v>
+        <v>6991598</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6966,14 +6956,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6988,22 +6988,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125420520</v>
+        <v>125420522</v>
       </c>
       <c r="B58" t="n">
-        <v>105278</v>
+        <v>79565</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7012,25 +7012,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7040,10 +7040,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>564498</v>
+        <v>564449</v>
       </c>
       <c r="R58" t="n">
-        <v>6991598</v>
+        <v>6991631</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På ved på gammal tallhögstubbe i gammal tallskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7891,10 +7891,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125420541</v>
+        <v>125426257</v>
       </c>
       <c r="B66" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7903,41 +7903,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>564525</v>
+        <v>564337</v>
       </c>
       <c r="R66" t="n">
-        <v>6991662</v>
+        <v>6991632</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7964,24 +7964,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>10 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7996,19 +7981,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125420539</v>
+        <v>125420541</v>
       </c>
       <c r="B67" t="n">
         <v>98269</v>
@@ -8048,10 +8033,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>564466</v>
+        <v>564525</v>
       </c>
       <c r="R67" t="n">
-        <v>6991587</v>
+        <v>6991662</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8083,7 +8068,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8093,12 +8078,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>60 plantor på marken i gammal barrblandskog</t>
+          <t>10 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8125,10 +8110,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125438549</v>
+        <v>125420539</v>
       </c>
       <c r="B68" t="n">
-        <v>77879</v>
+        <v>98269</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8137,25 +8122,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8165,10 +8150,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>564542</v>
+        <v>564466</v>
       </c>
       <c r="R68" t="n">
-        <v>6991657</v>
+        <v>6991587</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8198,14 +8183,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>60 plantor på marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8220,22 +8215,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125426257</v>
+        <v>125438549</v>
       </c>
       <c r="B69" t="n">
-        <v>91166</v>
+        <v>77879</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8248,37 +8243,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>564337</v>
+        <v>564542</v>
       </c>
       <c r="R69" t="n">
-        <v>6991632</v>
+        <v>6991657</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8308,6 +8303,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8322,12 +8322,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -2671,15 +2671,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125395850</v>
+        <v>125396762</v>
       </c>
       <c r="B21" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91513</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2687,21 +2682,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2716,13 +2711,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564463</v>
+        <v>564441</v>
       </c>
       <c r="R21" t="n">
-        <v>6991559</v>
+        <v>6991661</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2751,7 +2746,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2761,7 +2756,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2788,43 +2783,47 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125396883</v>
+        <v>125397300</v>
       </c>
       <c r="B22" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2833,10 +2832,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564440</v>
+        <v>564442</v>
       </c>
       <c r="R22" t="n">
-        <v>6991655</v>
+        <v>6991680</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2868,7 +2867,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2878,12 +2877,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2910,15 +2909,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125396355</v>
+        <v>125398434</v>
       </c>
       <c r="B23" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2926,21 +2920,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2950,10 +2944,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564463</v>
+        <v>564420</v>
       </c>
       <c r="R23" t="n">
-        <v>6991617</v>
+        <v>6991658</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2985,7 +2979,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2995,7 +2989,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3010,27 +3009,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125398362</v>
+        <v>125397219</v>
       </c>
       <c r="B24" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3038,37 +3032,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>564453</v>
+        <v>564440</v>
       </c>
       <c r="R24" t="n">
-        <v>6991691</v>
+        <v>6991662</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3097,7 +3100,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3107,12 +3110,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3127,27 +3125,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125396843</v>
+        <v>125396883</v>
       </c>
       <c r="B25" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3155,34 +3148,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>564431</v>
+        <v>564440</v>
       </c>
       <c r="R25" t="n">
-        <v>6991652</v>
+        <v>6991655</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3214,7 +3212,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3224,12 +3222,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3256,52 +3254,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125397259</v>
+        <v>125395199</v>
       </c>
       <c r="B26" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3310,13 +3298,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>564442</v>
+        <v>564521</v>
       </c>
       <c r="R26" t="n">
-        <v>6991680</v>
+        <v>6991610</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3345,7 +3333,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3355,12 +3343,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>På gråal</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3375,70 +3363,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125396762</v>
+        <v>125397495</v>
       </c>
       <c r="B27" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79974</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>564441</v>
+        <v>564410</v>
       </c>
       <c r="R27" t="n">
-        <v>6991661</v>
+        <v>6991660</v>
       </c>
       <c r="S27" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3467,7 +3445,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3477,7 +3455,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3492,59 +3475,54 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125395199</v>
+        <v>125398718</v>
       </c>
       <c r="B28" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3553,13 +3531,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>564521</v>
+        <v>564439</v>
       </c>
       <c r="R28" t="n">
-        <v>6991610</v>
+        <v>6991676</v>
       </c>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3588,7 +3566,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3598,12 +3576,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gråal</t>
+          <t>Ett stort områden typ 10 kvadratmeter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3618,27 +3596,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125396949</v>
+        <v>125398362</v>
       </c>
       <c r="B29" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,21 +3619,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3670,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>564440</v>
+        <v>564453</v>
       </c>
       <c r="R29" t="n">
-        <v>6991655</v>
+        <v>6991691</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3705,7 +3678,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3715,12 +3688,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3747,15 +3720,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125397175</v>
+        <v>125398524</v>
       </c>
       <c r="B30" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3763,34 +3731,43 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>564453</v>
+        <v>564457</v>
       </c>
       <c r="R30" t="n">
-        <v>6991658</v>
+        <v>6991682</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3822,7 +3799,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3832,12 +3809,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3864,15 +3841,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125397801</v>
+        <v>125398578</v>
       </c>
       <c r="B31" t="n">
-        <v>75025</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>82779</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3880,21 +3852,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3910,7 +3882,7 @@
         <v>6991662</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3939,7 +3911,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3949,12 +3921,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3981,15 +3948,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125398434</v>
+        <v>125395850</v>
       </c>
       <c r="B32" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3997,34 +3959,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>564420</v>
+        <v>564463</v>
       </c>
       <c r="R32" t="n">
-        <v>6991658</v>
+        <v>6991559</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4056,7 +4023,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4066,12 +4033,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4086,27 +4048,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125398524</v>
+        <v>125398468</v>
       </c>
       <c r="B33" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78726</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4114,43 +4071,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>564457</v>
+        <v>564441</v>
       </c>
       <c r="R33" t="n">
-        <v>6991682</v>
+        <v>6991674</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4182,7 +4130,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4192,12 +4140,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På kolad ved på två gamla tallhögstubbar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4224,62 +4172,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125396600</v>
+        <v>125397801</v>
       </c>
       <c r="B34" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75066</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>564463</v>
+        <v>564440</v>
       </c>
       <c r="R34" t="n">
-        <v>6991617</v>
+        <v>6991662</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4308,7 +4242,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4318,7 +4252,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4345,64 +4284,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125397089</v>
+        <v>125396949</v>
       </c>
       <c r="B35" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78726</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>564452</v>
+        <v>564440</v>
       </c>
       <c r="R35" t="n">
-        <v>6991661</v>
+        <v>6991655</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4434,7 +4354,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4444,12 +4364,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt på marken i gammal granskog</t>
+          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4476,37 +4396,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125397495</v>
+        <v>125396355</v>
       </c>
       <c r="B36" t="n">
-        <v>79932</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78726</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4516,10 +4431,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>564410</v>
+        <v>564463</v>
       </c>
       <c r="R36" t="n">
-        <v>6991660</v>
+        <v>6991617</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4551,7 +4466,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4561,12 +4476,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4581,7 +4491,7 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -4593,15 +4503,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125398718</v>
+        <v>125397089</v>
       </c>
       <c r="B37" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4628,7 +4533,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4636,16 +4541,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>564439</v>
+        <v>564452</v>
       </c>
       <c r="R37" t="n">
-        <v>6991676</v>
+        <v>6991661</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4677,7 +4587,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4687,12 +4597,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ett stort områden typ 10 kvadratmeter</t>
+          <t>Rikligt på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4707,27 +4617,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125396221</v>
+        <v>125397175</v>
       </c>
       <c r="B38" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4735,39 +4640,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>564445</v>
+        <v>564453</v>
       </c>
       <c r="R38" t="n">
-        <v>6991608</v>
+        <v>6991658</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4799,7 +4699,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4809,12 +4709,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4829,27 +4729,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125397219</v>
+        <v>125397385</v>
       </c>
       <c r="B39" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4874,29 +4769,20 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>564440</v>
+        <v>564442</v>
       </c>
       <c r="R39" t="n">
-        <v>6991662</v>
+        <v>6991680</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4925,7 +4811,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4935,7 +4821,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4950,65 +4841,74 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125397385</v>
+        <v>125396498</v>
       </c>
       <c r="B40" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>564442</v>
+        <v>564463</v>
       </c>
       <c r="R40" t="n">
-        <v>6991680</v>
+        <v>6991617</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5037,7 +4937,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5047,12 +4947,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På sälg i gammal granskog</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5067,27 +4962,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125398468</v>
+        <v>125396221</v>
       </c>
       <c r="B41" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5095,34 +4985,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>564441</v>
+        <v>564445</v>
       </c>
       <c r="R41" t="n">
-        <v>6991674</v>
+        <v>6991608</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5154,7 +5049,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5164,12 +5059,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På kolad ved på två gamla tallhögstubbar</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5184,64 +5079,54 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125396498</v>
+        <v>125396600</v>
       </c>
       <c r="B42" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5256,7 +5141,7 @@
         <v>6991617</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5285,7 +5170,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5295,7 +5180,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5315,22 +5200,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125397829</v>
+        <v>125396843</v>
       </c>
       <c r="B43" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5338,39 +5218,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>564401</v>
+        <v>564431</v>
       </c>
       <c r="R43" t="n">
-        <v>6991629</v>
+        <v>6991652</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5402,7 +5277,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5412,12 +5287,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikliga ringhack på gammal tall</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5432,27 +5307,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125398578</v>
+        <v>125420522</v>
       </c>
       <c r="B44" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79585</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5460,34 +5330,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>564440</v>
+        <v>564449</v>
       </c>
       <c r="R44" t="n">
-        <v>6991662</v>
+        <v>6991631</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5519,7 +5389,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5529,7 +5399,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På ved på gammal tallhögstubbe i gammal tallskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5544,49 +5419,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125420542</v>
+        <v>125438544</v>
       </c>
       <c r="B45" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5596,10 +5466,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>564429</v>
+        <v>564517</v>
       </c>
       <c r="R45" t="n">
-        <v>6991627</v>
+        <v>6991669</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5629,24 +5499,14 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5661,62 +5521,65 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125426260</v>
+        <v>125426277</v>
       </c>
       <c r="B46" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>564551</v>
+        <v>564468</v>
       </c>
       <c r="R46" t="n">
-        <v>6991633</v>
+        <v>6991658</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5757,6 +5620,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5775,37 +5639,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125420536</v>
+        <v>125420520</v>
       </c>
       <c r="B47" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105333</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>221725</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5815,10 +5674,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>564470</v>
+        <v>564498</v>
       </c>
       <c r="R47" t="n">
-        <v>6991585</v>
+        <v>6991598</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5850,7 +5709,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5860,12 +5719,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Mycket rikligt på gran under grov asp</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5892,37 +5751,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125420537</v>
+        <v>125420540</v>
       </c>
       <c r="B48" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5932,10 +5786,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>564470</v>
+        <v>564495</v>
       </c>
       <c r="R48" t="n">
-        <v>6991561</v>
+        <v>6991590</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5967,7 +5821,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5977,12 +5831,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>40 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6009,53 +5863,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125420524</v>
+        <v>125426255</v>
       </c>
       <c r="B49" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>564474</v>
+        <v>564448</v>
       </c>
       <c r="R49" t="n">
-        <v>6991608</v>
+        <v>6991620</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6082,24 +5931,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Helt färska och äldre ringhack, rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6114,70 +5948,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125426278</v>
+        <v>125426252</v>
       </c>
       <c r="B50" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96577</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>564453</v>
+        <v>564532</v>
       </c>
       <c r="R50" t="n">
-        <v>6991629</v>
+        <v>6991656</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6218,7 +6039,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6237,15 +6057,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125426277</v>
+        <v>125420534</v>
       </c>
       <c r="B51" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>74841</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6253,45 +6068,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>98</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk rödprick</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia incarnata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>Th.Fr. ex Almq.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>564468</v>
+        <v>564500</v>
       </c>
       <c r="R51" t="n">
-        <v>6991658</v>
+        <v>6991603</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6318,83 +6125,92 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På bark vid basen av gammal levande grov sälg (75 cm dbh) i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125426285</v>
+        <v>125420543</v>
       </c>
       <c r="B52" t="n">
-        <v>80063</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75058</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6463</v>
+        <v>308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>564561</v>
+        <v>564520</v>
       </c>
       <c r="R52" t="n">
-        <v>6991616</v>
+        <v>6991622</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6421,9 +6237,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På ved på gammal granhögstubbe</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6438,65 +6269,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125438548</v>
+        <v>125426262</v>
       </c>
       <c r="B53" t="n">
-        <v>80064</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91671</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>1209</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>564548</v>
+        <v>564395</v>
       </c>
       <c r="R53" t="n">
-        <v>6991664</v>
+        <v>6991654</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6526,11 +6352,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6545,49 +6366,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125426262</v>
+        <v>125426257</v>
       </c>
       <c r="B54" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6597,10 +6413,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>564395</v>
+        <v>564337</v>
       </c>
       <c r="R54" t="n">
-        <v>6991654</v>
+        <v>6991632</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6659,37 +6475,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125420523</v>
+        <v>125420533</v>
       </c>
       <c r="B55" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80098</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6699,10 +6510,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>564516</v>
+        <v>564582</v>
       </c>
       <c r="R55" t="n">
-        <v>6991629</v>
+        <v>6991673</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6734,7 +6545,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6744,12 +6555,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6776,53 +6587,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125438545</v>
+        <v>125426286</v>
       </c>
       <c r="B56" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80105</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>564535</v>
+        <v>564556</v>
       </c>
       <c r="R56" t="n">
-        <v>6991601</v>
+        <v>6991665</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6852,11 +6658,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6871,65 +6672,60 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125420520</v>
+        <v>125426267</v>
       </c>
       <c r="B57" t="n">
-        <v>105278</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91513</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221725</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>564498</v>
+        <v>564405</v>
       </c>
       <c r="R57" t="n">
-        <v>6991598</v>
+        <v>6991645</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6956,24 +6752,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6988,49 +6769,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125420522</v>
+        <v>125420528</v>
       </c>
       <c r="B58" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7040,10 +6816,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>564449</v>
+        <v>564555</v>
       </c>
       <c r="R58" t="n">
-        <v>6991631</v>
+        <v>6991665</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7075,7 +6851,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7085,12 +6861,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På ved på gammal tallhögstubbe i gammal tallskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7117,53 +6893,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125420540</v>
+        <v>125426281</v>
       </c>
       <c r="B59" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>564495</v>
+        <v>564408</v>
       </c>
       <c r="R59" t="n">
-        <v>6991590</v>
+        <v>6991646</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7190,24 +6961,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>40 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7222,62 +6978,65 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125426250</v>
+        <v>125426279</v>
       </c>
       <c r="B60" t="n">
-        <v>105278</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>564528</v>
+        <v>564474</v>
       </c>
       <c r="R60" t="n">
-        <v>6991624</v>
+        <v>6991589</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7318,6 +7077,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7336,15 +7096,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125426269</v>
+        <v>125426250</v>
       </c>
       <c r="B61" t="n">
-        <v>98303</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105333</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7352,21 +7107,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219874</v>
+        <v>221725</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7376,10 +7131,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>564521</v>
+        <v>564528</v>
       </c>
       <c r="R61" t="n">
-        <v>6991595</v>
+        <v>6991624</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7438,15 +7193,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125426255</v>
+        <v>125438548</v>
       </c>
       <c r="B62" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80106</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7454,37 +7204,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>564448</v>
+        <v>564548</v>
       </c>
       <c r="R62" t="n">
-        <v>6991620</v>
+        <v>6991664</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7514,6 +7264,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7528,12 +7283,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7543,12 +7298,7 @@
         <v>125420538</v>
       </c>
       <c r="B63" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7657,15 +7407,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125420533</v>
+        <v>125426269</v>
       </c>
       <c r="B64" t="n">
-        <v>80056</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98358</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7673,37 +7418,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6461</v>
+        <v>219874</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>564582</v>
+        <v>564521</v>
       </c>
       <c r="R64" t="n">
-        <v>6991673</v>
+        <v>6991595</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7730,24 +7475,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7762,27 +7492,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125420543</v>
+        <v>125420542</v>
       </c>
       <c r="B65" t="n">
-        <v>75017</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7790,21 +7515,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7814,10 +7539,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>564520</v>
+        <v>564429</v>
       </c>
       <c r="R65" t="n">
-        <v>6991622</v>
+        <v>6991627</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7849,7 +7574,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7859,12 +7584,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe</t>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7891,15 +7616,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125426257</v>
+        <v>125420529</v>
       </c>
       <c r="B66" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78956</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7907,37 +7627,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>336</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Solfjäderlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cheiromycina flabelliformis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>B.Sutton</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>564337</v>
+        <v>564492</v>
       </c>
       <c r="R66" t="n">
-        <v>6991632</v>
+        <v>6991578</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7964,9 +7684,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På bark vid basen av gammal död sälg i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7981,49 +7716,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125420541</v>
+        <v>125420530</v>
       </c>
       <c r="B67" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>74877</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8033,10 +7763,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>564525</v>
+        <v>564520</v>
       </c>
       <c r="R67" t="n">
-        <v>6991662</v>
+        <v>6991626</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8068,7 +7798,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8078,12 +7808,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>10 plantor på marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8110,37 +7840,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125420539</v>
+        <v>125420527</v>
       </c>
       <c r="B68" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8150,10 +7875,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>564466</v>
+        <v>564499</v>
       </c>
       <c r="R68" t="n">
-        <v>6991587</v>
+        <v>6991597</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8185,7 +7910,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8195,12 +7920,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>60 plantor på marken i gammal barrblandskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8227,15 +7952,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125438549</v>
+        <v>125426251</v>
       </c>
       <c r="B69" t="n">
-        <v>77879</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75066</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8243,37 +7963,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>564542</v>
+        <v>564469</v>
       </c>
       <c r="R69" t="n">
-        <v>6991657</v>
+        <v>6991678</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8303,11 +8023,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8322,44 +8037,39 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125426286</v>
+        <v>125426280</v>
       </c>
       <c r="B70" t="n">
-        <v>80063</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8374,10 +8084,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>564556</v>
+        <v>564364</v>
       </c>
       <c r="R70" t="n">
-        <v>6991665</v>
+        <v>6991670</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8436,37 +8146,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125420530</v>
+        <v>125420537</v>
       </c>
       <c r="B71" t="n">
-        <v>74836</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8476,10 +8181,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>564520</v>
+        <v>564470</v>
       </c>
       <c r="R71" t="n">
-        <v>6991626</v>
+        <v>6991561</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8511,7 +8216,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8521,7 +8226,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -8553,15 +8258,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125426281</v>
+        <v>125426254</v>
       </c>
       <c r="B72" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96577</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8569,21 +8269,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8593,10 +8293,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>564408</v>
+        <v>564412</v>
       </c>
       <c r="R72" t="n">
-        <v>6991646</v>
+        <v>6991656</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8655,15 +8355,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125420534</v>
+        <v>125420539</v>
       </c>
       <c r="B73" t="n">
-        <v>74800</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8671,21 +8366,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>98</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk rödprick</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Arthonia incarnata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Th.Fr. ex Almq.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8695,10 +8390,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>564500</v>
+        <v>564466</v>
       </c>
       <c r="R73" t="n">
-        <v>6991603</v>
+        <v>6991587</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8730,7 +8425,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8740,12 +8435,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande grov sälg (75 cm dbh) i gammal granskog</t>
+          <t>60 plantor på marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8772,15 +8467,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125426251</v>
+        <v>125420531</v>
       </c>
       <c r="B74" t="n">
-        <v>75025</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91513</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8788,37 +8478,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>564469</v>
+        <v>564486</v>
       </c>
       <c r="R74" t="n">
-        <v>6991678</v>
+        <v>6991573</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8845,9 +8535,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8862,49 +8567,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125426267</v>
+        <v>125426272</v>
       </c>
       <c r="B75" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95557</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8914,10 +8614,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>564405</v>
+        <v>564515</v>
       </c>
       <c r="R75" t="n">
-        <v>6991645</v>
+        <v>6991646</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8976,15 +8676,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125426265</v>
+        <v>125420536</v>
       </c>
       <c r="B76" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8992,37 +8687,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>564336</v>
+        <v>564470</v>
       </c>
       <c r="R76" t="n">
-        <v>6991633</v>
+        <v>6991585</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9049,9 +8744,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Mycket rikligt på gran under grov asp</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9066,65 +8776,60 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125426280</v>
+        <v>125420535</v>
       </c>
       <c r="B77" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95557</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>564364</v>
+        <v>564539</v>
       </c>
       <c r="R77" t="n">
-        <v>6991670</v>
+        <v>6991663</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9151,9 +8856,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På marken i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9168,27 +8888,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125426252</v>
+        <v>125438549</v>
       </c>
       <c r="B78" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>77921</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9196,37 +8911,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>228579</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>564532</v>
+        <v>564542</v>
       </c>
       <c r="R78" t="n">
-        <v>6991656</v>
+        <v>6991657</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9256,6 +8971,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9270,49 +8990,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125426272</v>
+        <v>125426265</v>
       </c>
       <c r="B79" t="n">
-        <v>95503</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91513</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9322,10 +9037,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>564515</v>
+        <v>564336</v>
       </c>
       <c r="R79" t="n">
-        <v>6991646</v>
+        <v>6991633</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -9384,15 +9099,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125420535</v>
+        <v>125426285</v>
       </c>
       <c r="B80" t="n">
-        <v>95503</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80105</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9400,37 +9110,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2809</v>
+        <v>6463</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>564539</v>
+        <v>564561</v>
       </c>
       <c r="R80" t="n">
-        <v>6991663</v>
+        <v>6991616</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9457,24 +9167,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På marken i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9489,73 +9184,60 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125426258</v>
+        <v>125420541</v>
       </c>
       <c r="B81" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>564461</v>
+        <v>564525</v>
       </c>
       <c r="R81" t="n">
-        <v>6991657</v>
+        <v>6991662</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9582,14 +9264,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>10 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9604,62 +9296,65 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125426254</v>
+        <v>125426278</v>
       </c>
       <c r="B82" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>564412</v>
+        <v>564453</v>
       </c>
       <c r="R82" t="n">
-        <v>6991656</v>
+        <v>6991629</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9700,6 +9395,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9718,15 +9414,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125420531</v>
+        <v>125420523</v>
       </c>
       <c r="B83" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9734,21 +9425,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9758,10 +9449,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>564486</v>
+        <v>564516</v>
       </c>
       <c r="R83" t="n">
-        <v>6991573</v>
+        <v>6991629</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9793,7 +9484,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9803,7 +9494,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -9835,53 +9526,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125420529</v>
+        <v>125426260</v>
       </c>
       <c r="B84" t="n">
-        <v>78929</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>336</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Solfjäderlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cheiromycina flabelliformis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>B.Sutton</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>564492</v>
+        <v>564551</v>
       </c>
       <c r="R84" t="n">
-        <v>6991578</v>
+        <v>6991633</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9908,24 +9594,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På bark vid basen av gammal död sälg i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9940,62 +9611,62 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125438544</v>
+        <v>125397829</v>
       </c>
       <c r="B85" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>564517</v>
+        <v>564401</v>
       </c>
       <c r="R85" t="n">
-        <v>6991669</v>
+        <v>6991629</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10025,14 +9696,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Rikliga ringhack på gammal tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10047,73 +9728,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125426279</v>
+        <v>125420524</v>
       </c>
       <c r="B86" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
         <v>564474</v>
       </c>
       <c r="R86" t="n">
-        <v>6991589</v>
+        <v>6991608</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10140,67 +9808,76 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Helt färska och äldre ringhack, rikligt på gammal gran i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125420527</v>
+        <v>125438545</v>
       </c>
       <c r="B87" t="n">
-        <v>98290</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10210,10 +9887,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>564499</v>
+        <v>564535</v>
       </c>
       <c r="R87" t="n">
-        <v>6991597</v>
+        <v>6991601</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10243,24 +9920,14 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10275,65 +9942,68 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125420528</v>
+        <v>125426258</v>
       </c>
       <c r="B88" t="n">
-        <v>98290</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>564555</v>
+        <v>564461</v>
       </c>
       <c r="R88" t="n">
-        <v>6991665</v>
+        <v>6991657</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10360,24 +10030,14 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10392,12 +10052,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -4284,7 +4284,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125396949</v>
+        <v>125396355</v>
       </c>
       <c r="B35" t="n">
         <v>78726</v>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>564440</v>
+        <v>564463</v>
       </c>
       <c r="R35" t="n">
-        <v>6991655</v>
+        <v>6991617</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4364,12 +4364,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4384,19 +4379,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125396355</v>
+        <v>125396949</v>
       </c>
       <c r="B36" t="n">
         <v>78726</v>
@@ -4431,10 +4426,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>564463</v>
+        <v>564440</v>
       </c>
       <c r="R36" t="n">
-        <v>6991617</v>
+        <v>6991655</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4466,7 +4461,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4476,7 +4471,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4491,12 +4491,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5091,57 +5091,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125396600</v>
+        <v>125396843</v>
       </c>
       <c r="B42" t="n">
-        <v>80099</v>
+        <v>91220</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>564463</v>
+        <v>564431</v>
       </c>
       <c r="R42" t="n">
-        <v>6991617</v>
+        <v>6991652</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5170,7 +5161,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5180,7 +5171,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5195,60 +5191,69 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125396843</v>
+        <v>125396600</v>
       </c>
       <c r="B43" t="n">
-        <v>91220</v>
+        <v>80099</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>564431</v>
+        <v>564463</v>
       </c>
       <c r="R43" t="n">
-        <v>6991652</v>
+        <v>6991617</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5277,7 +5282,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5287,12 +5292,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:33</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5307,12 +5307,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5639,10 +5639,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125420520</v>
+        <v>125426255</v>
       </c>
       <c r="B47" t="n">
-        <v>105333</v>
+        <v>91185</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5650,37 +5650,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>564498</v>
+        <v>564448</v>
       </c>
       <c r="R47" t="n">
-        <v>6991598</v>
+        <v>6991620</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5707,24 +5707,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5739,44 +5724,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125420540</v>
+        <v>125420520</v>
       </c>
       <c r="B48" t="n">
-        <v>98324</v>
+        <v>105333</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5786,10 +5771,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>564495</v>
+        <v>564498</v>
       </c>
       <c r="R48" t="n">
-        <v>6991590</v>
+        <v>6991598</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5821,7 +5806,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5831,12 +5816,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>40 plantor på marken i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5863,48 +5848,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125426255</v>
+        <v>125420540</v>
       </c>
       <c r="B49" t="n">
-        <v>91185</v>
+        <v>98324</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>564448</v>
+        <v>564495</v>
       </c>
       <c r="R49" t="n">
-        <v>6991620</v>
+        <v>6991590</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5931,9 +5916,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>40 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5948,12 +5948,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6990,53 +6990,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125426279</v>
+        <v>125426250</v>
       </c>
       <c r="B60" t="n">
-        <v>98324</v>
+        <v>105333</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>564474</v>
+        <v>564528</v>
       </c>
       <c r="R60" t="n">
-        <v>6991589</v>
+        <v>6991624</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7077,7 +7069,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7096,45 +7087,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125426250</v>
+        <v>125426279</v>
       </c>
       <c r="B61" t="n">
-        <v>105333</v>
+        <v>98324</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>564528</v>
+        <v>564474</v>
       </c>
       <c r="R61" t="n">
-        <v>6991624</v>
+        <v>6991589</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7175,6 +7174,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7504,10 +7504,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125420542</v>
+        <v>125420529</v>
       </c>
       <c r="B65" t="n">
-        <v>78967</v>
+        <v>78956</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7515,21 +7515,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>336</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Solfjäderlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cheiromycina flabelliformis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>B.Sutton</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7539,10 +7539,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>564429</v>
+        <v>564492</v>
       </c>
       <c r="R65" t="n">
-        <v>6991627</v>
+        <v>6991578</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
+          <t>På bark vid basen av gammal död sälg i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7616,10 +7616,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125420529</v>
+        <v>125420542</v>
       </c>
       <c r="B66" t="n">
-        <v>78956</v>
+        <v>78967</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7627,21 +7627,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>336</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Solfjäderlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cheiromycina flabelliformis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>B.Sutton</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7651,10 +7651,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>564492</v>
+        <v>564429</v>
       </c>
       <c r="R66" t="n">
-        <v>6991578</v>
+        <v>6991627</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7696,12 +7696,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal död sälg i fuktig gammal granskog</t>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -2671,38 +2671,47 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125396762</v>
+        <v>125397300</v>
       </c>
       <c r="B21" t="n">
-        <v>91513</v>
+        <v>98331</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2711,13 +2720,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564441</v>
+        <v>564442</v>
       </c>
       <c r="R21" t="n">
-        <v>6991661</v>
+        <v>6991680</v>
       </c>
       <c r="S21" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2746,7 +2755,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2756,7 +2765,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2771,59 +2785,50 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125397300</v>
+        <v>125396762</v>
       </c>
       <c r="B22" t="n">
-        <v>98324</v>
+        <v>91520</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2832,13 +2837,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564442</v>
+        <v>564441</v>
       </c>
       <c r="R22" t="n">
-        <v>6991680</v>
+        <v>6991661</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2867,7 +2872,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2877,12 +2882,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2897,12 +2897,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3490,7 +3490,7 @@
         <v>125398718</v>
       </c>
       <c r="B28" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>125398362</v>
       </c>
       <c r="B29" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,10 +3841,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125398578</v>
+        <v>125398468</v>
       </c>
       <c r="B31" t="n">
-        <v>82779</v>
+        <v>78726</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3852,21 +3852,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>564440</v>
+        <v>564441</v>
       </c>
       <c r="R31" t="n">
-        <v>6991662</v>
+        <v>6991674</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3921,7 +3921,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På kolad ved på två gamla tallhögstubbar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3936,22 +3941,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125395850</v>
+        <v>125398578</v>
       </c>
       <c r="B32" t="n">
-        <v>91220</v>
+        <v>82779</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3959,39 +3964,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>564463</v>
+        <v>564440</v>
       </c>
       <c r="R32" t="n">
-        <v>6991559</v>
+        <v>6991662</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4060,10 +4060,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125398468</v>
+        <v>125395850</v>
       </c>
       <c r="B33" t="n">
-        <v>78726</v>
+        <v>91227</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4071,34 +4071,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>564441</v>
+        <v>564463</v>
       </c>
       <c r="R33" t="n">
-        <v>6991674</v>
+        <v>6991559</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4130,7 +4135,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4140,12 +4145,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På kolad ved på två gamla tallhögstubbar</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4160,12 +4160,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4284,7 +4284,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125396355</v>
+        <v>125396949</v>
       </c>
       <c r="B35" t="n">
         <v>78726</v>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>564463</v>
+        <v>564440</v>
       </c>
       <c r="R35" t="n">
-        <v>6991617</v>
+        <v>6991655</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4364,7 +4364,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4379,19 +4384,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125396949</v>
+        <v>125396355</v>
       </c>
       <c r="B36" t="n">
         <v>78726</v>
@@ -4426,10 +4431,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>564440</v>
+        <v>564463</v>
       </c>
       <c r="R36" t="n">
-        <v>6991655</v>
+        <v>6991617</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4461,7 +4466,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4471,12 +4476,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4491,12 +4491,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4506,7 +4506,7 @@
         <v>125397089</v>
       </c>
       <c r="B37" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>125396498</v>
       </c>
       <c r="B40" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>125396221</v>
       </c>
       <c r="B41" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5091,48 +5091,57 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125396843</v>
+        <v>125396600</v>
       </c>
       <c r="B42" t="n">
-        <v>91220</v>
+        <v>80099</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>564431</v>
+        <v>564463</v>
       </c>
       <c r="R42" t="n">
-        <v>6991652</v>
+        <v>6991617</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5161,7 +5170,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5171,12 +5180,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:33</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5191,69 +5195,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125396600</v>
+        <v>125396843</v>
       </c>
       <c r="B43" t="n">
-        <v>80099</v>
+        <v>91227</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>564463</v>
+        <v>564431</v>
       </c>
       <c r="R43" t="n">
-        <v>6991617</v>
+        <v>6991652</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5282,7 +5277,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5292,7 +5287,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5307,12 +5307,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5434,7 +5434,7 @@
         <v>125438544</v>
       </c>
       <c r="B45" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>125426277</v>
       </c>
       <c r="B46" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5639,10 +5639,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125426255</v>
+        <v>125420520</v>
       </c>
       <c r="B47" t="n">
-        <v>91185</v>
+        <v>105340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5650,37 +5650,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>564448</v>
+        <v>564498</v>
       </c>
       <c r="R47" t="n">
-        <v>6991620</v>
+        <v>6991598</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5707,9 +5707,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5724,44 +5739,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125420520</v>
+        <v>125420540</v>
       </c>
       <c r="B48" t="n">
-        <v>105333</v>
+        <v>98331</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5771,10 +5786,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>564498</v>
+        <v>564495</v>
       </c>
       <c r="R48" t="n">
-        <v>6991598</v>
+        <v>6991590</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5806,7 +5821,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5816,12 +5831,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>40 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5848,48 +5863,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125420540</v>
+        <v>125426255</v>
       </c>
       <c r="B49" t="n">
-        <v>98324</v>
+        <v>91192</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>564495</v>
+        <v>564448</v>
       </c>
       <c r="R49" t="n">
-        <v>6991590</v>
+        <v>6991620</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5916,24 +5931,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>40 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5948,12 +5948,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5963,7 +5963,7 @@
         <v>125426252</v>
       </c>
       <c r="B50" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6281,32 +6281,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125426262</v>
+        <v>125426257</v>
       </c>
       <c r="B53" t="n">
-        <v>91671</v>
+        <v>91227</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>564395</v>
+        <v>564337</v>
       </c>
       <c r="R53" t="n">
-        <v>6991654</v>
+        <v>6991632</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6378,32 +6378,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125426257</v>
+        <v>125426262</v>
       </c>
       <c r="B54" t="n">
-        <v>91220</v>
+        <v>91678</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>564337</v>
+        <v>564395</v>
       </c>
       <c r="R54" t="n">
-        <v>6991632</v>
+        <v>6991654</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6587,32 +6587,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125426286</v>
+        <v>125426267</v>
       </c>
       <c r="B56" t="n">
-        <v>80105</v>
+        <v>91520</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6622,10 +6622,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>564556</v>
+        <v>564405</v>
       </c>
       <c r="R56" t="n">
-        <v>6991665</v>
+        <v>6991645</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6684,48 +6684,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125426267</v>
+        <v>125420528</v>
       </c>
       <c r="B57" t="n">
-        <v>91513</v>
+        <v>98352</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>564405</v>
+        <v>564555</v>
       </c>
       <c r="R57" t="n">
-        <v>6991645</v>
+        <v>6991665</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6752,9 +6752,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6769,22 +6784,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125420528</v>
+        <v>125426286</v>
       </c>
       <c r="B58" t="n">
-        <v>98345</v>
+        <v>80105</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6792,37 +6807,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>564555</v>
+        <v>564556</v>
       </c>
       <c r="R58" t="n">
         <v>6991665</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6849,24 +6864,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6881,12 +6881,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6990,45 +6990,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125426250</v>
+        <v>125426279</v>
       </c>
       <c r="B60" t="n">
-        <v>105333</v>
+        <v>98331</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>564528</v>
+        <v>564474</v>
       </c>
       <c r="R60" t="n">
-        <v>6991624</v>
+        <v>6991589</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7069,6 +7077,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7087,53 +7096,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125426279</v>
+        <v>125426250</v>
       </c>
       <c r="B61" t="n">
-        <v>98324</v>
+        <v>105340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>564474</v>
+        <v>564528</v>
       </c>
       <c r="R61" t="n">
-        <v>6991589</v>
+        <v>6991624</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7174,7 +7175,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>125426269</v>
       </c>
       <c r="B64" t="n">
-        <v>98358</v>
+        <v>98365</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>125420527</v>
       </c>
       <c r="B68" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         <v>125426254</v>
       </c>
       <c r="B72" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>125420539</v>
       </c>
       <c r="B73" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8467,48 +8467,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125420531</v>
+        <v>125426272</v>
       </c>
       <c r="B74" t="n">
-        <v>91513</v>
+        <v>95564</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>564486</v>
+        <v>564515</v>
       </c>
       <c r="R74" t="n">
-        <v>6991573</v>
+        <v>6991646</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8535,24 +8535,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8567,60 +8552,60 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125426272</v>
+        <v>125420531</v>
       </c>
       <c r="B75" t="n">
-        <v>95557</v>
+        <v>91520</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>564515</v>
+        <v>564486</v>
       </c>
       <c r="R75" t="n">
-        <v>6991646</v>
+        <v>6991573</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8647,9 +8632,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8664,12 +8664,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8788,32 +8788,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125420535</v>
+        <v>125438549</v>
       </c>
       <c r="B77" t="n">
-        <v>95557</v>
+        <v>77921</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2809</v>
+        <v>228579</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8823,10 +8823,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>564539</v>
+        <v>564542</v>
       </c>
       <c r="R77" t="n">
-        <v>6991663</v>
+        <v>6991657</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8856,24 +8856,14 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På marken i gammal fuktig granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8888,44 +8878,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125438549</v>
+        <v>125420535</v>
       </c>
       <c r="B78" t="n">
-        <v>77921</v>
+        <v>95564</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228579</v>
+        <v>2809</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8935,10 +8925,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>564542</v>
+        <v>564539</v>
       </c>
       <c r="R78" t="n">
-        <v>6991657</v>
+        <v>6991663</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8968,14 +8958,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På marken i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8990,12 +8990,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9005,7 +9005,7 @@
         <v>125426265</v>
       </c>
       <c r="B79" t="n">
-        <v>91513</v>
+        <v>91520</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>125420541</v>
       </c>
       <c r="B81" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9308,56 +9308,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125426278</v>
+        <v>125420523</v>
       </c>
       <c r="B82" t="n">
-        <v>98324</v>
+        <v>91227</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>564453</v>
+        <v>564516</v>
       </c>
       <c r="R82" t="n">
         <v>6991629</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9384,78 +9376,92 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125420523</v>
+        <v>125426260</v>
       </c>
       <c r="B83" t="n">
-        <v>91220</v>
+        <v>80099</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>564516</v>
+        <v>564551</v>
       </c>
       <c r="R83" t="n">
-        <v>6991629</v>
+        <v>6991633</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9482,24 +9488,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9514,57 +9505,65 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125426260</v>
+        <v>125426278</v>
       </c>
       <c r="B84" t="n">
-        <v>80099</v>
+        <v>98331</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>564551</v>
+        <v>564453</v>
       </c>
       <c r="R84" t="n">
-        <v>6991633</v>
+        <v>6991629</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9605,6 +9604,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -2671,47 +2671,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125397300</v>
+        <v>125396762</v>
       </c>
       <c r="B21" t="n">
-        <v>98331</v>
+        <v>91520</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2720,13 +2711,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564442</v>
+        <v>564441</v>
       </c>
       <c r="R21" t="n">
-        <v>6991680</v>
+        <v>6991661</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2755,7 +2746,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2765,12 +2756,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2785,50 +2771,59 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125396762</v>
+        <v>125397300</v>
       </c>
       <c r="B22" t="n">
-        <v>91520</v>
+        <v>98331</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2837,13 +2832,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564441</v>
+        <v>564442</v>
       </c>
       <c r="R22" t="n">
-        <v>6991661</v>
+        <v>6991680</v>
       </c>
       <c r="S22" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2872,7 +2867,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2882,7 +2877,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2897,12 +2897,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3487,54 +3487,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125398718</v>
+        <v>125398362</v>
       </c>
       <c r="B28" t="n">
-        <v>98331</v>
+        <v>91227</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>564439</v>
+        <v>564453</v>
       </c>
       <c r="R28" t="n">
-        <v>6991676</v>
+        <v>6991691</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3566,7 +3557,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3576,12 +3567,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ett stort områden typ 10 kvadratmeter</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3596,57 +3587,66 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125398362</v>
+        <v>125398718</v>
       </c>
       <c r="B29" t="n">
-        <v>91227</v>
+        <v>98331</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>564453</v>
+        <v>564439</v>
       </c>
       <c r="R29" t="n">
-        <v>6991691</v>
+        <v>6991676</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Ett stort områden typ 10 kvadratmeter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3708,12 +3708,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4629,48 +4629,62 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125397175</v>
+        <v>125396498</v>
       </c>
       <c r="B38" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>564453</v>
+        <v>564463</v>
       </c>
       <c r="R38" t="n">
-        <v>6991658</v>
+        <v>6991617</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4699,7 +4713,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4709,12 +4723,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4729,19 +4738,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125397385</v>
+        <v>125397175</v>
       </c>
       <c r="B39" t="n">
         <v>80070</v>
@@ -4776,10 +4785,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>564442</v>
+        <v>564453</v>
       </c>
       <c r="R39" t="n">
-        <v>6991680</v>
+        <v>6991658</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4811,7 +4820,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4821,12 +4830,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4853,62 +4862,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125396498</v>
+        <v>125397385</v>
       </c>
       <c r="B40" t="n">
-        <v>98331</v>
+        <v>80070</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>564463</v>
+        <v>564442</v>
       </c>
       <c r="R40" t="n">
-        <v>6991617</v>
+        <v>6991680</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4937,7 +4932,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4947,7 +4942,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4962,12 +4962,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -6684,10 +6684,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125420528</v>
+        <v>125426286</v>
       </c>
       <c r="B57" t="n">
-        <v>98352</v>
+        <v>80105</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>564555</v>
+        <v>564556</v>
       </c>
       <c r="R57" t="n">
         <v>6991665</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6752,24 +6752,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6784,22 +6769,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125426286</v>
+        <v>125420528</v>
       </c>
       <c r="B58" t="n">
-        <v>80105</v>
+        <v>98352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6807,37 +6792,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>564556</v>
+        <v>564555</v>
       </c>
       <c r="R58" t="n">
         <v>6991665</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6864,9 +6849,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6881,57 +6881,65 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125426281</v>
+        <v>125426279</v>
       </c>
       <c r="B59" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>564408</v>
+        <v>564474</v>
       </c>
       <c r="R59" t="n">
-        <v>6991646</v>
+        <v>6991589</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6972,6 +6980,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6990,53 +6999,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125426279</v>
+        <v>125426250</v>
       </c>
       <c r="B60" t="n">
-        <v>98331</v>
+        <v>105340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>564474</v>
+        <v>564528</v>
       </c>
       <c r="R60" t="n">
-        <v>6991589</v>
+        <v>6991624</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7077,7 +7078,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7096,32 +7096,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125426250</v>
+        <v>125426281</v>
       </c>
       <c r="B61" t="n">
-        <v>105340</v>
+        <v>78967</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7131,10 +7131,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>564528</v>
+        <v>564408</v>
       </c>
       <c r="R61" t="n">
-        <v>6991624</v>
+        <v>6991646</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -8788,32 +8788,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125438549</v>
+        <v>125420535</v>
       </c>
       <c r="B77" t="n">
-        <v>77921</v>
+        <v>95564</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228579</v>
+        <v>2809</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8823,10 +8823,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>564542</v>
+        <v>564539</v>
       </c>
       <c r="R77" t="n">
-        <v>6991657</v>
+        <v>6991663</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8856,14 +8856,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På marken i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8878,44 +8888,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125420535</v>
+        <v>125438549</v>
       </c>
       <c r="B78" t="n">
-        <v>95564</v>
+        <v>77921</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2809</v>
+        <v>228579</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8925,10 +8935,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>564539</v>
+        <v>564542</v>
       </c>
       <c r="R78" t="n">
-        <v>6991663</v>
+        <v>6991657</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8958,24 +8968,14 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På marken i gammal fuktig granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8990,12 +8990,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9099,48 +9099,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125426285</v>
+        <v>125420541</v>
       </c>
       <c r="B80" t="n">
-        <v>80105</v>
+        <v>98331</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>564561</v>
+        <v>564525</v>
       </c>
       <c r="R80" t="n">
-        <v>6991616</v>
+        <v>6991662</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9167,9 +9167,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>10 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9184,60 +9199,60 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125420541</v>
+        <v>125426285</v>
       </c>
       <c r="B81" t="n">
-        <v>98331</v>
+        <v>80105</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>564525</v>
+        <v>564561</v>
       </c>
       <c r="R81" t="n">
-        <v>6991662</v>
+        <v>6991616</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9264,24 +9279,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>10 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9296,12 +9296,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -4629,62 +4629,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125396498</v>
+        <v>125397175</v>
       </c>
       <c r="B38" t="n">
-        <v>98331</v>
+        <v>80070</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>564463</v>
+        <v>564453</v>
       </c>
       <c r="R38" t="n">
-        <v>6991617</v>
+        <v>6991658</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4713,7 +4699,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4723,7 +4709,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4738,19 +4729,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125397175</v>
+        <v>125397385</v>
       </c>
       <c r="B39" t="n">
         <v>80070</v>
@@ -4785,10 +4776,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>564453</v>
+        <v>564442</v>
       </c>
       <c r="R39" t="n">
-        <v>6991658</v>
+        <v>6991680</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4820,7 +4811,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4830,12 +4821,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4862,48 +4853,62 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125397385</v>
+        <v>125396498</v>
       </c>
       <c r="B40" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>564442</v>
+        <v>564463</v>
       </c>
       <c r="R40" t="n">
-        <v>6991680</v>
+        <v>6991617</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4932,7 +4937,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4942,12 +4947,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På sälg i gammal granskog</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4962,12 +4962,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5639,32 +5639,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125420520</v>
+        <v>125420540</v>
       </c>
       <c r="B47" t="n">
-        <v>105340</v>
+        <v>98331</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>564498</v>
+        <v>564495</v>
       </c>
       <c r="R47" t="n">
-        <v>6991598</v>
+        <v>6991590</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5719,12 +5719,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>40 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5751,32 +5751,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125420540</v>
+        <v>125420520</v>
       </c>
       <c r="B48" t="n">
-        <v>98331</v>
+        <v>105340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>564495</v>
+        <v>564498</v>
       </c>
       <c r="R48" t="n">
-        <v>6991590</v>
+        <v>6991598</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>40 plantor på marken i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6587,48 +6587,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125426267</v>
+        <v>125420528</v>
       </c>
       <c r="B56" t="n">
-        <v>91520</v>
+        <v>98352</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>564405</v>
+        <v>564555</v>
       </c>
       <c r="R56" t="n">
-        <v>6991645</v>
+        <v>6991665</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6655,9 +6655,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6672,44 +6687,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125426286</v>
+        <v>125426267</v>
       </c>
       <c r="B57" t="n">
-        <v>80105</v>
+        <v>91520</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6719,10 +6734,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>564556</v>
+        <v>564405</v>
       </c>
       <c r="R57" t="n">
-        <v>6991665</v>
+        <v>6991645</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6781,10 +6796,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125420528</v>
+        <v>125426286</v>
       </c>
       <c r="B58" t="n">
-        <v>98352</v>
+        <v>80105</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6792,37 +6807,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>564555</v>
+        <v>564556</v>
       </c>
       <c r="R58" t="n">
         <v>6991665</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6849,24 +6864,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6881,65 +6881,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125426279</v>
+        <v>125426281</v>
       </c>
       <c r="B59" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>564474</v>
+        <v>564408</v>
       </c>
       <c r="R59" t="n">
-        <v>6991589</v>
+        <v>6991646</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6980,7 +6972,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6999,45 +6990,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125426250</v>
+        <v>125426279</v>
       </c>
       <c r="B60" t="n">
-        <v>105340</v>
+        <v>98331</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>564528</v>
+        <v>564474</v>
       </c>
       <c r="R60" t="n">
-        <v>6991624</v>
+        <v>6991589</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7078,6 +7077,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7096,32 +7096,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125426281</v>
+        <v>125426250</v>
       </c>
       <c r="B61" t="n">
-        <v>78967</v>
+        <v>105340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7131,10 +7131,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>564408</v>
+        <v>564528</v>
       </c>
       <c r="R61" t="n">
-        <v>6991646</v>
+        <v>6991624</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -8467,48 +8467,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125426272</v>
+        <v>125420531</v>
       </c>
       <c r="B74" t="n">
-        <v>95564</v>
+        <v>91520</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>564515</v>
+        <v>564486</v>
       </c>
       <c r="R74" t="n">
-        <v>6991646</v>
+        <v>6991573</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8535,9 +8535,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8552,60 +8567,60 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125420531</v>
+        <v>125426272</v>
       </c>
       <c r="B75" t="n">
-        <v>91520</v>
+        <v>95564</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>564486</v>
+        <v>564515</v>
       </c>
       <c r="R75" t="n">
-        <v>6991573</v>
+        <v>6991646</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8632,24 +8647,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8664,12 +8664,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -2671,38 +2671,47 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125396762</v>
+        <v>125397300</v>
       </c>
       <c r="B21" t="n">
-        <v>91520</v>
+        <v>98334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2711,13 +2720,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564441</v>
+        <v>564442</v>
       </c>
       <c r="R21" t="n">
-        <v>6991661</v>
+        <v>6991680</v>
       </c>
       <c r="S21" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2746,7 +2755,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2756,7 +2765,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2771,59 +2785,50 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125397300</v>
+        <v>125396762</v>
       </c>
       <c r="B22" t="n">
-        <v>98331</v>
+        <v>91524</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2832,13 +2837,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564442</v>
+        <v>564441</v>
       </c>
       <c r="R22" t="n">
-        <v>6991680</v>
+        <v>6991661</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2867,7 +2872,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2877,12 +2882,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2897,12 +2897,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2912,7 +2912,7 @@
         <v>125398434</v>
       </c>
       <c r="B23" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>125397219</v>
       </c>
       <c r="B24" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>125396883</v>
       </c>
       <c r="B25" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>125395199</v>
       </c>
       <c r="B26" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>125397495</v>
       </c>
       <c r="B27" t="n">
-        <v>79974</v>
+        <v>79975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3487,45 +3487,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125398362</v>
+        <v>125398718</v>
       </c>
       <c r="B28" t="n">
-        <v>91227</v>
+        <v>98334</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>564453</v>
+        <v>564439</v>
       </c>
       <c r="R28" t="n">
-        <v>6991691</v>
+        <v>6991676</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3557,7 +3566,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3567,12 +3576,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Ett stort områden typ 10 kvadratmeter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3587,66 +3596,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125398718</v>
+        <v>125398362</v>
       </c>
       <c r="B29" t="n">
-        <v>98331</v>
+        <v>91228</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>564439</v>
+        <v>564453</v>
       </c>
       <c r="R29" t="n">
-        <v>6991676</v>
+        <v>6991691</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ett stort områden typ 10 kvadratmeter</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3708,12 +3708,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3723,7 +3723,7 @@
         <v>125398524</v>
       </c>
       <c r="B30" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3841,10 +3841,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125398468</v>
+        <v>125398578</v>
       </c>
       <c r="B31" t="n">
-        <v>78726</v>
+        <v>82780</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3852,21 +3852,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>564441</v>
+        <v>564440</v>
       </c>
       <c r="R31" t="n">
-        <v>6991674</v>
+        <v>6991662</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3921,12 +3921,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På kolad ved på två gamla tallhögstubbar</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3941,22 +3936,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125398578</v>
+        <v>125395850</v>
       </c>
       <c r="B32" t="n">
-        <v>82779</v>
+        <v>91228</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3964,34 +3959,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>564440</v>
+        <v>564463</v>
       </c>
       <c r="R32" t="n">
-        <v>6991662</v>
+        <v>6991559</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4060,10 +4060,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125395850</v>
+        <v>125398468</v>
       </c>
       <c r="B33" t="n">
-        <v>91227</v>
+        <v>78727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4071,39 +4071,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>564463</v>
+        <v>564441</v>
       </c>
       <c r="R33" t="n">
-        <v>6991559</v>
+        <v>6991674</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4135,7 +4130,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4145,7 +4140,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På kolad ved på två gamla tallhögstubbar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4160,12 +4160,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4175,7 +4175,7 @@
         <v>125397801</v>
       </c>
       <c r="B34" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>125396949</v>
       </c>
       <c r="B35" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>125396355</v>
       </c>
       <c r="B36" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>125397089</v>
       </c>
       <c r="B37" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>125397175</v>
       </c>
       <c r="B38" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>125397385</v>
       </c>
       <c r="B39" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>125396498</v>
       </c>
       <c r="B40" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>125396221</v>
       </c>
       <c r="B41" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5091,57 +5091,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125396600</v>
+        <v>125396843</v>
       </c>
       <c r="B42" t="n">
-        <v>80099</v>
+        <v>91228</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>564463</v>
+        <v>564431</v>
       </c>
       <c r="R42" t="n">
-        <v>6991617</v>
+        <v>6991652</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5170,7 +5161,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5180,7 +5171,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5195,60 +5191,69 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125396843</v>
+        <v>125396600</v>
       </c>
       <c r="B43" t="n">
-        <v>91227</v>
+        <v>80100</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>564431</v>
+        <v>564463</v>
       </c>
       <c r="R43" t="n">
-        <v>6991652</v>
+        <v>6991617</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5277,7 +5282,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5287,12 +5292,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:33</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5307,44 +5307,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125420522</v>
+        <v>125438544</v>
       </c>
       <c r="B44" t="n">
-        <v>79585</v>
+        <v>91193</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>564449</v>
+        <v>564517</v>
       </c>
       <c r="R44" t="n">
-        <v>6991631</v>
+        <v>6991669</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5387,24 +5387,14 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På ved på gammal tallhögstubbe i gammal tallskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5419,44 +5409,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125438544</v>
+        <v>125420522</v>
       </c>
       <c r="B45" t="n">
-        <v>91192</v>
+        <v>79586</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5466,10 +5456,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>564517</v>
+        <v>564449</v>
       </c>
       <c r="R45" t="n">
-        <v>6991669</v>
+        <v>6991631</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5499,14 +5489,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På ved på gammal tallhögstubbe i gammal tallskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5521,12 +5521,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5536,7 +5536,7 @@
         <v>125426277</v>
       </c>
       <c r="B46" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5639,32 +5639,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125420540</v>
+        <v>125420520</v>
       </c>
       <c r="B47" t="n">
-        <v>98331</v>
+        <v>105343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>564495</v>
+        <v>564498</v>
       </c>
       <c r="R47" t="n">
-        <v>6991590</v>
+        <v>6991598</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5719,12 +5719,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>40 plantor på marken i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5751,10 +5751,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125420520</v>
+        <v>125426255</v>
       </c>
       <c r="B48" t="n">
-        <v>105340</v>
+        <v>91193</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5762,37 +5762,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>564498</v>
+        <v>564448</v>
       </c>
       <c r="R48" t="n">
-        <v>6991598</v>
+        <v>6991620</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5819,24 +5819,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5851,60 +5836,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125426255</v>
+        <v>125420540</v>
       </c>
       <c r="B49" t="n">
-        <v>91192</v>
+        <v>98334</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>564448</v>
+        <v>564495</v>
       </c>
       <c r="R49" t="n">
-        <v>6991620</v>
+        <v>6991590</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5931,9 +5916,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>40 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5948,12 +5948,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5963,7 +5963,7 @@
         <v>125426252</v>
       </c>
       <c r="B50" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>125420534</v>
       </c>
       <c r="B51" t="n">
-        <v>74841</v>
+        <v>74842</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6169,48 +6169,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125420543</v>
+        <v>125426262</v>
       </c>
       <c r="B52" t="n">
-        <v>75058</v>
+        <v>91682</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>308</v>
+        <v>1209</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>564520</v>
+        <v>564395</v>
       </c>
       <c r="R52" t="n">
-        <v>6991622</v>
+        <v>6991654</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6237,24 +6237,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På ved på gammal granhögstubbe</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6269,22 +6254,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125426257</v>
+        <v>125420543</v>
       </c>
       <c r="B53" t="n">
-        <v>91227</v>
+        <v>75059</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6292,37 +6277,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>564337</v>
+        <v>564520</v>
       </c>
       <c r="R53" t="n">
-        <v>6991632</v>
+        <v>6991622</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6349,9 +6334,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På ved på gammal granhögstubbe</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6366,44 +6366,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125426262</v>
+        <v>125426257</v>
       </c>
       <c r="B54" t="n">
-        <v>91678</v>
+        <v>91228</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>564395</v>
+        <v>564337</v>
       </c>
       <c r="R54" t="n">
-        <v>6991654</v>
+        <v>6991632</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6478,7 +6478,7 @@
         <v>125420533</v>
       </c>
       <c r="B55" t="n">
-        <v>80098</v>
+        <v>80099</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>125420528</v>
       </c>
       <c r="B56" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>125426267</v>
       </c>
       <c r="B57" t="n">
-        <v>91520</v>
+        <v>91524</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>125426286</v>
       </c>
       <c r="B58" t="n">
-        <v>80105</v>
+        <v>80106</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6893,32 +6893,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125426281</v>
+        <v>125426250</v>
       </c>
       <c r="B59" t="n">
-        <v>78967</v>
+        <v>105343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>564408</v>
+        <v>564528</v>
       </c>
       <c r="R59" t="n">
-        <v>6991646</v>
+        <v>6991624</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6993,7 +6993,7 @@
         <v>125426279</v>
       </c>
       <c r="B60" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7096,32 +7096,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125426250</v>
+        <v>125426281</v>
       </c>
       <c r="B61" t="n">
-        <v>105340</v>
+        <v>78968</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7131,10 +7131,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>564528</v>
+        <v>564408</v>
       </c>
       <c r="R61" t="n">
-        <v>6991624</v>
+        <v>6991646</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7196,7 +7196,7 @@
         <v>125438548</v>
       </c>
       <c r="B62" t="n">
-        <v>80106</v>
+        <v>80107</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7295,48 +7295,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125420538</v>
+        <v>125426269</v>
       </c>
       <c r="B63" t="n">
-        <v>80070</v>
+        <v>98368</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>564491</v>
+        <v>564521</v>
       </c>
       <c r="R63" t="n">
-        <v>6991571</v>
+        <v>6991595</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7363,24 +7363,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7395,60 +7380,60 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125426269</v>
+        <v>125420538</v>
       </c>
       <c r="B64" t="n">
-        <v>98365</v>
+        <v>80071</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>564521</v>
+        <v>564491</v>
       </c>
       <c r="R64" t="n">
-        <v>6991595</v>
+        <v>6991571</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7475,9 +7460,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7492,12 +7492,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7507,7 +7507,7 @@
         <v>125420529</v>
       </c>
       <c r="B65" t="n">
-        <v>78956</v>
+        <v>78957</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>125420542</v>
       </c>
       <c r="B66" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>125420530</v>
       </c>
       <c r="B67" t="n">
-        <v>74877</v>
+        <v>74878</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>125420527</v>
       </c>
       <c r="B68" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7952,10 +7952,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125426251</v>
+        <v>125426254</v>
       </c>
       <c r="B69" t="n">
-        <v>75066</v>
+        <v>96587</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7963,21 +7963,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>564469</v>
+        <v>564412</v>
       </c>
       <c r="R69" t="n">
-        <v>6991678</v>
+        <v>6991656</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8052,7 +8052,7 @@
         <v>125426280</v>
       </c>
       <c r="B70" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8146,10 +8146,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125420537</v>
+        <v>125426251</v>
       </c>
       <c r="B71" t="n">
-        <v>80070</v>
+        <v>75067</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8157,37 +8157,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>564470</v>
+        <v>564469</v>
       </c>
       <c r="R71" t="n">
-        <v>6991561</v>
+        <v>6991678</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8214,24 +8214,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8246,22 +8231,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125426254</v>
+        <v>125420537</v>
       </c>
       <c r="B72" t="n">
-        <v>96584</v>
+        <v>80071</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8269,37 +8254,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>564412</v>
+        <v>564470</v>
       </c>
       <c r="R72" t="n">
-        <v>6991656</v>
+        <v>6991561</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8326,9 +8311,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8343,44 +8343,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125420539</v>
+        <v>125420531</v>
       </c>
       <c r="B73" t="n">
-        <v>98331</v>
+        <v>91524</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8390,10 +8390,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>564466</v>
+        <v>564486</v>
       </c>
       <c r="R73" t="n">
-        <v>6991587</v>
+        <v>6991573</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>60 plantor på marken i gammal barrblandskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8467,48 +8467,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125420531</v>
+        <v>125426272</v>
       </c>
       <c r="B74" t="n">
-        <v>91520</v>
+        <v>95567</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>564486</v>
+        <v>564515</v>
       </c>
       <c r="R74" t="n">
-        <v>6991573</v>
+        <v>6991646</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8535,24 +8535,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8567,60 +8552,60 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125426272</v>
+        <v>125420539</v>
       </c>
       <c r="B75" t="n">
-        <v>95564</v>
+        <v>98334</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>564515</v>
+        <v>564466</v>
       </c>
       <c r="R75" t="n">
-        <v>6991646</v>
+        <v>6991587</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8647,9 +8632,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>60 plantor på marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8664,12 +8664,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8679,7 +8679,7 @@
         <v>125420536</v>
       </c>
       <c r="B76" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8788,32 +8788,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125420535</v>
+        <v>125438549</v>
       </c>
       <c r="B77" t="n">
-        <v>95564</v>
+        <v>77922</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2809</v>
+        <v>228579</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8823,10 +8823,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>564539</v>
+        <v>564542</v>
       </c>
       <c r="R77" t="n">
-        <v>6991663</v>
+        <v>6991657</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8856,24 +8856,14 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På marken i gammal fuktig granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8888,44 +8878,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125438549</v>
+        <v>125420535</v>
       </c>
       <c r="B78" t="n">
-        <v>77921</v>
+        <v>95567</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228579</v>
+        <v>2809</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8935,10 +8925,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>564542</v>
+        <v>564539</v>
       </c>
       <c r="R78" t="n">
-        <v>6991657</v>
+        <v>6991663</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8968,14 +8958,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På marken i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8990,12 +8990,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9005,7 +9005,7 @@
         <v>125426265</v>
       </c>
       <c r="B79" t="n">
-        <v>91520</v>
+        <v>91524</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9099,48 +9099,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125420541</v>
+        <v>125426285</v>
       </c>
       <c r="B80" t="n">
-        <v>98331</v>
+        <v>80106</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>564525</v>
+        <v>564561</v>
       </c>
       <c r="R80" t="n">
-        <v>6991662</v>
+        <v>6991616</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9167,24 +9167,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>10 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9199,60 +9184,60 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125426285</v>
+        <v>125420541</v>
       </c>
       <c r="B81" t="n">
-        <v>80105</v>
+        <v>98334</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>564561</v>
+        <v>564525</v>
       </c>
       <c r="R81" t="n">
-        <v>6991616</v>
+        <v>6991662</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9279,9 +9264,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>10 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9296,12 +9296,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9311,7 +9311,7 @@
         <v>125420523</v>
       </c>
       <c r="B82" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>125426260</v>
       </c>
       <c r="B83" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>125426278</v>
       </c>
       <c r="B84" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -2671,47 +2671,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125397300</v>
+        <v>125396762</v>
       </c>
       <c r="B21" t="n">
-        <v>98334</v>
+        <v>91524</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2720,13 +2711,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564442</v>
+        <v>564441</v>
       </c>
       <c r="R21" t="n">
-        <v>6991680</v>
+        <v>6991661</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2755,7 +2746,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2765,12 +2756,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2785,50 +2771,59 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125396762</v>
+        <v>125397300</v>
       </c>
       <c r="B22" t="n">
-        <v>91524</v>
+        <v>98334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2837,13 +2832,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564441</v>
+        <v>564442</v>
       </c>
       <c r="R22" t="n">
-        <v>6991661</v>
+        <v>6991680</v>
       </c>
       <c r="S22" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2872,7 +2867,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2882,7 +2877,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2897,12 +2897,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -5091,48 +5091,57 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125396843</v>
+        <v>125396600</v>
       </c>
       <c r="B42" t="n">
-        <v>91228</v>
+        <v>80100</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>564431</v>
+        <v>564463</v>
       </c>
       <c r="R42" t="n">
-        <v>6991652</v>
+        <v>6991617</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5161,7 +5170,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5171,12 +5180,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:33</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5191,69 +5195,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125396600</v>
+        <v>125396843</v>
       </c>
       <c r="B43" t="n">
-        <v>80100</v>
+        <v>91228</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>564463</v>
+        <v>564431</v>
       </c>
       <c r="R43" t="n">
-        <v>6991617</v>
+        <v>6991652</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5282,7 +5277,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5292,7 +5287,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5307,12 +5307,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -2674,7 +2674,7 @@
         <v>125396762</v>
       </c>
       <c r="B21" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>125397300</v>
       </c>
       <c r="B22" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>125398434</v>
       </c>
       <c r="B23" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>125397219</v>
       </c>
       <c r="B24" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>125396883</v>
       </c>
       <c r="B25" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>125395199</v>
       </c>
       <c r="B26" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>125397495</v>
       </c>
       <c r="B27" t="n">
-        <v>79975</v>
+        <v>79979</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>125398718</v>
       </c>
       <c r="B28" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>125398362</v>
       </c>
       <c r="B29" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>125398524</v>
       </c>
       <c r="B30" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>125398578</v>
       </c>
       <c r="B31" t="n">
-        <v>82780</v>
+        <v>82784</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3951,7 +3951,7 @@
         <v>125395850</v>
       </c>
       <c r="B32" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>125398468</v>
       </c>
       <c r="B33" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4287,7 +4287,7 @@
         <v>125396949</v>
       </c>
       <c r="B35" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>125396355</v>
       </c>
       <c r="B36" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>125397089</v>
       </c>
       <c r="B37" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4629,48 +4629,62 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125397175</v>
+        <v>125396498</v>
       </c>
       <c r="B38" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>564453</v>
+        <v>564463</v>
       </c>
       <c r="R38" t="n">
-        <v>6991658</v>
+        <v>6991617</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4699,7 +4713,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4709,12 +4723,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4729,22 +4738,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125397385</v>
+        <v>125397175</v>
       </c>
       <c r="B39" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4776,10 +4785,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>564442</v>
+        <v>564453</v>
       </c>
       <c r="R39" t="n">
-        <v>6991680</v>
+        <v>6991658</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4811,7 +4820,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4821,12 +4830,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4853,62 +4862,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125396498</v>
+        <v>125397385</v>
       </c>
       <c r="B40" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>564463</v>
+        <v>564442</v>
       </c>
       <c r="R40" t="n">
-        <v>6991617</v>
+        <v>6991680</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4937,7 +4932,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4947,7 +4942,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4962,12 +4962,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4977,7 +4977,7 @@
         <v>125396221</v>
       </c>
       <c r="B41" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5091,57 +5091,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125396600</v>
+        <v>125396843</v>
       </c>
       <c r="B42" t="n">
-        <v>80100</v>
+        <v>91232</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>564463</v>
+        <v>564431</v>
       </c>
       <c r="R42" t="n">
-        <v>6991617</v>
+        <v>6991652</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5170,7 +5161,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5180,7 +5171,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5195,60 +5191,69 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125396843</v>
+        <v>125396600</v>
       </c>
       <c r="B43" t="n">
-        <v>91228</v>
+        <v>80104</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>564431</v>
+        <v>564463</v>
       </c>
       <c r="R43" t="n">
-        <v>6991652</v>
+        <v>6991617</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5277,7 +5282,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5287,12 +5292,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:33</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5307,12 +5307,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5322,7 +5322,7 @@
         <v>125438544</v>
       </c>
       <c r="B44" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>125420522</v>
       </c>
       <c r="B45" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>125426277</v>
       </c>
       <c r="B46" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5639,32 +5639,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125420520</v>
+        <v>125420540</v>
       </c>
       <c r="B47" t="n">
-        <v>105343</v>
+        <v>98338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>564498</v>
+        <v>564495</v>
       </c>
       <c r="R47" t="n">
-        <v>6991598</v>
+        <v>6991590</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5719,12 +5719,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>40 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5751,10 +5751,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125426255</v>
+        <v>125420520</v>
       </c>
       <c r="B48" t="n">
-        <v>91193</v>
+        <v>105347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5762,37 +5762,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>564448</v>
+        <v>564498</v>
       </c>
       <c r="R48" t="n">
-        <v>6991620</v>
+        <v>6991598</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5819,9 +5819,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5836,60 +5851,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125420540</v>
+        <v>125426255</v>
       </c>
       <c r="B49" t="n">
-        <v>98334</v>
+        <v>91197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>564495</v>
+        <v>564448</v>
       </c>
       <c r="R49" t="n">
-        <v>6991590</v>
+        <v>6991620</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5916,24 +5931,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>40 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5948,12 +5948,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5963,7 +5963,7 @@
         <v>125426252</v>
       </c>
       <c r="B50" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>125426262</v>
       </c>
       <c r="B52" t="n">
-        <v>91682</v>
+        <v>91686</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>125426257</v>
       </c>
       <c r="B54" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>125420533</v>
       </c>
       <c r="B55" t="n">
-        <v>80099</v>
+        <v>80103</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>125420528</v>
       </c>
       <c r="B56" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>125426267</v>
       </c>
       <c r="B57" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>125426286</v>
       </c>
       <c r="B58" t="n">
-        <v>80106</v>
+        <v>80110</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6893,32 +6893,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125426250</v>
+        <v>125426281</v>
       </c>
       <c r="B59" t="n">
-        <v>105343</v>
+        <v>78972</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>564528</v>
+        <v>564408</v>
       </c>
       <c r="R59" t="n">
-        <v>6991624</v>
+        <v>6991646</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6993,7 +6993,7 @@
         <v>125426279</v>
       </c>
       <c r="B60" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7096,32 +7096,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125426281</v>
+        <v>125426250</v>
       </c>
       <c r="B61" t="n">
-        <v>78968</v>
+        <v>105347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7131,10 +7131,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>564408</v>
+        <v>564528</v>
       </c>
       <c r="R61" t="n">
-        <v>6991646</v>
+        <v>6991624</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7196,7 +7196,7 @@
         <v>125438548</v>
       </c>
       <c r="B62" t="n">
-        <v>80107</v>
+        <v>80111</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>125426269</v>
       </c>
       <c r="B63" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>125420538</v>
       </c>
       <c r="B64" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>125420529</v>
       </c>
       <c r="B65" t="n">
-        <v>78957</v>
+        <v>78961</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>125420542</v>
       </c>
       <c r="B66" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>125420527</v>
       </c>
       <c r="B68" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7952,10 +7952,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125426254</v>
+        <v>125426280</v>
       </c>
       <c r="B69" t="n">
-        <v>96587</v>
+        <v>78972</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7963,21 +7963,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>564412</v>
+        <v>564364</v>
       </c>
       <c r="R69" t="n">
-        <v>6991656</v>
+        <v>6991670</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8049,10 +8049,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125426280</v>
+        <v>125426251</v>
       </c>
       <c r="B70" t="n">
-        <v>78968</v>
+        <v>75067</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8060,21 +8060,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>564364</v>
+        <v>564469</v>
       </c>
       <c r="R70" t="n">
-        <v>6991670</v>
+        <v>6991678</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8146,10 +8146,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125426251</v>
+        <v>125420537</v>
       </c>
       <c r="B71" t="n">
-        <v>75067</v>
+        <v>80075</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8157,37 +8157,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>564469</v>
+        <v>564470</v>
       </c>
       <c r="R71" t="n">
-        <v>6991678</v>
+        <v>6991561</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8214,9 +8214,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8231,22 +8246,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125420537</v>
+        <v>125426254</v>
       </c>
       <c r="B72" t="n">
-        <v>80071</v>
+        <v>96591</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8254,37 +8269,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>564470</v>
+        <v>564412</v>
       </c>
       <c r="R72" t="n">
-        <v>6991561</v>
+        <v>6991656</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8311,24 +8326,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8343,60 +8343,60 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125420531</v>
+        <v>125426272</v>
       </c>
       <c r="B73" t="n">
-        <v>91524</v>
+        <v>95571</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>564486</v>
+        <v>564515</v>
       </c>
       <c r="R73" t="n">
-        <v>6991573</v>
+        <v>6991646</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8423,24 +8423,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8455,60 +8440,60 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125426272</v>
+        <v>125420531</v>
       </c>
       <c r="B74" t="n">
-        <v>95567</v>
+        <v>91528</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>564515</v>
+        <v>564486</v>
       </c>
       <c r="R74" t="n">
-        <v>6991646</v>
+        <v>6991573</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8535,9 +8520,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8552,12 +8552,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8567,7 +8567,7 @@
         <v>125420539</v>
       </c>
       <c r="B75" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>125420536</v>
       </c>
       <c r="B76" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8788,32 +8788,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125438549</v>
+        <v>125420535</v>
       </c>
       <c r="B77" t="n">
-        <v>77922</v>
+        <v>95571</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228579</v>
+        <v>2809</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8823,10 +8823,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>564542</v>
+        <v>564539</v>
       </c>
       <c r="R77" t="n">
-        <v>6991657</v>
+        <v>6991663</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8856,14 +8856,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På marken i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8878,44 +8888,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125420535</v>
+        <v>125438549</v>
       </c>
       <c r="B78" t="n">
-        <v>95567</v>
+        <v>77926</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2809</v>
+        <v>228579</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8925,10 +8935,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>564539</v>
+        <v>564542</v>
       </c>
       <c r="R78" t="n">
-        <v>6991663</v>
+        <v>6991657</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8958,24 +8968,14 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På marken i gammal fuktig granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8990,12 +8990,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9005,7 +9005,7 @@
         <v>125426265</v>
       </c>
       <c r="B79" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9099,48 +9099,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125426285</v>
+        <v>125420541</v>
       </c>
       <c r="B80" t="n">
-        <v>80106</v>
+        <v>98338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>564561</v>
+        <v>564525</v>
       </c>
       <c r="R80" t="n">
-        <v>6991616</v>
+        <v>6991662</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9167,9 +9167,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>10 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9184,60 +9199,60 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125420541</v>
+        <v>125426285</v>
       </c>
       <c r="B81" t="n">
-        <v>98334</v>
+        <v>80110</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>564525</v>
+        <v>564561</v>
       </c>
       <c r="R81" t="n">
-        <v>6991662</v>
+        <v>6991616</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9264,24 +9279,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>10 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9296,60 +9296,68 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125420523</v>
+        <v>125426278</v>
       </c>
       <c r="B82" t="n">
-        <v>91228</v>
+        <v>98338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>564516</v>
+        <v>564453</v>
       </c>
       <c r="R82" t="n">
         <v>6991629</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9376,92 +9384,78 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125426260</v>
+        <v>125420523</v>
       </c>
       <c r="B83" t="n">
-        <v>80100</v>
+        <v>91232</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>564551</v>
+        <v>564516</v>
       </c>
       <c r="R83" t="n">
-        <v>6991633</v>
+        <v>6991629</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9488,9 +9482,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9505,65 +9514,57 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125426278</v>
+        <v>125426260</v>
       </c>
       <c r="B84" t="n">
-        <v>98334</v>
+        <v>80104</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>564453</v>
+        <v>564551</v>
       </c>
       <c r="R84" t="n">
-        <v>6991629</v>
+        <v>6991633</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9604,7 +9605,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -6699,32 +6699,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125426267</v>
+        <v>125426286</v>
       </c>
       <c r="B57" t="n">
-        <v>91528</v>
+        <v>80110</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6734,10 +6734,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>564405</v>
+        <v>564556</v>
       </c>
       <c r="R57" t="n">
-        <v>6991645</v>
+        <v>6991665</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6796,32 +6796,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125426286</v>
+        <v>125426267</v>
       </c>
       <c r="B58" t="n">
-        <v>80110</v>
+        <v>91528</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6831,10 +6831,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>564556</v>
+        <v>564405</v>
       </c>
       <c r="R58" t="n">
-        <v>6991665</v>
+        <v>6991645</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6893,32 +6893,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125426281</v>
+        <v>125426250</v>
       </c>
       <c r="B59" t="n">
-        <v>78972</v>
+        <v>105347</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>564408</v>
+        <v>564528</v>
       </c>
       <c r="R59" t="n">
-        <v>6991646</v>
+        <v>6991624</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7096,32 +7096,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125426250</v>
+        <v>125426281</v>
       </c>
       <c r="B61" t="n">
-        <v>105347</v>
+        <v>78972</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7131,10 +7131,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>564528</v>
+        <v>564408</v>
       </c>
       <c r="R61" t="n">
-        <v>6991624</v>
+        <v>6991646</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7504,10 +7504,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125420529</v>
+        <v>125420542</v>
       </c>
       <c r="B65" t="n">
-        <v>78961</v>
+        <v>78972</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7515,21 +7515,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>336</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Solfjäderlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cheiromycina flabelliformis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>B.Sutton</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7539,10 +7539,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>564492</v>
+        <v>564429</v>
       </c>
       <c r="R65" t="n">
-        <v>6991578</v>
+        <v>6991627</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal död sälg i fuktig gammal granskog</t>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7616,10 +7616,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125420542</v>
+        <v>125420529</v>
       </c>
       <c r="B66" t="n">
-        <v>78972</v>
+        <v>78961</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7627,21 +7627,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>336</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Solfjäderlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cheiromycina flabelliformis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>B.Sutton</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7651,10 +7651,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>564429</v>
+        <v>564492</v>
       </c>
       <c r="R66" t="n">
-        <v>6991627</v>
+        <v>6991578</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7696,12 +7696,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
+          <t>På bark vid basen av gammal död sälg i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7952,10 +7952,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125426280</v>
+        <v>125426254</v>
       </c>
       <c r="B69" t="n">
-        <v>78972</v>
+        <v>96591</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7963,21 +7963,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>564364</v>
+        <v>564412</v>
       </c>
       <c r="R69" t="n">
-        <v>6991670</v>
+        <v>6991656</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8049,10 +8049,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125426251</v>
+        <v>125426280</v>
       </c>
       <c r="B70" t="n">
-        <v>75067</v>
+        <v>78972</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8060,21 +8060,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>564469</v>
+        <v>564364</v>
       </c>
       <c r="R70" t="n">
-        <v>6991678</v>
+        <v>6991670</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8146,10 +8146,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125420537</v>
+        <v>125426251</v>
       </c>
       <c r="B71" t="n">
-        <v>80075</v>
+        <v>75067</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8157,37 +8157,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>564470</v>
+        <v>564469</v>
       </c>
       <c r="R71" t="n">
-        <v>6991561</v>
+        <v>6991678</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8214,24 +8214,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8246,22 +8231,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125426254</v>
+        <v>125420537</v>
       </c>
       <c r="B72" t="n">
-        <v>96591</v>
+        <v>80075</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8269,37 +8254,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>564412</v>
+        <v>564470</v>
       </c>
       <c r="R72" t="n">
-        <v>6991656</v>
+        <v>6991561</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8326,9 +8311,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8343,60 +8343,60 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125426272</v>
+        <v>125420539</v>
       </c>
       <c r="B73" t="n">
-        <v>95571</v>
+        <v>98338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>564515</v>
+        <v>564466</v>
       </c>
       <c r="R73" t="n">
-        <v>6991646</v>
+        <v>6991587</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8423,9 +8423,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>60 plantor på marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8440,12 +8455,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8564,48 +8579,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125420539</v>
+        <v>125426272</v>
       </c>
       <c r="B75" t="n">
-        <v>98338</v>
+        <v>95571</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>564466</v>
+        <v>564515</v>
       </c>
       <c r="R75" t="n">
-        <v>6991587</v>
+        <v>6991646</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8632,24 +8647,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>60 plantor på marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8664,12 +8664,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9308,56 +9308,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125426278</v>
+        <v>125420523</v>
       </c>
       <c r="B82" t="n">
-        <v>98338</v>
+        <v>91232</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>564453</v>
+        <v>564516</v>
       </c>
       <c r="R82" t="n">
         <v>6991629</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9384,78 +9376,92 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125420523</v>
+        <v>125426260</v>
       </c>
       <c r="B83" t="n">
-        <v>91232</v>
+        <v>80104</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>564516</v>
+        <v>564551</v>
       </c>
       <c r="R83" t="n">
-        <v>6991629</v>
+        <v>6991633</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9482,24 +9488,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9514,57 +9505,65 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125426260</v>
+        <v>125426278</v>
       </c>
       <c r="B84" t="n">
-        <v>80104</v>
+        <v>98338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>564551</v>
+        <v>564453</v>
       </c>
       <c r="R84" t="n">
-        <v>6991633</v>
+        <v>6991629</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9605,6 +9604,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -2671,38 +2671,47 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125396762</v>
+        <v>125397300</v>
       </c>
       <c r="B21" t="n">
-        <v>91528</v>
+        <v>98339</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2711,13 +2720,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564441</v>
+        <v>564442</v>
       </c>
       <c r="R21" t="n">
-        <v>6991661</v>
+        <v>6991680</v>
       </c>
       <c r="S21" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2746,7 +2755,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2756,7 +2765,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2771,59 +2785,50 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125397300</v>
+        <v>125396762</v>
       </c>
       <c r="B22" t="n">
-        <v>98338</v>
+        <v>91528</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2832,13 +2837,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564442</v>
+        <v>564441</v>
       </c>
       <c r="R22" t="n">
-        <v>6991680</v>
+        <v>6991661</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2867,7 +2872,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2877,12 +2882,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2897,12 +2897,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3487,54 +3487,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125398718</v>
+        <v>125398362</v>
       </c>
       <c r="B28" t="n">
-        <v>98338</v>
+        <v>91232</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>564439</v>
+        <v>564453</v>
       </c>
       <c r="R28" t="n">
-        <v>6991676</v>
+        <v>6991691</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3566,7 +3557,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3576,12 +3567,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ett stort områden typ 10 kvadratmeter</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3596,57 +3587,66 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125398362</v>
+        <v>125398718</v>
       </c>
       <c r="B29" t="n">
-        <v>91232</v>
+        <v>98339</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>564453</v>
+        <v>564439</v>
       </c>
       <c r="R29" t="n">
-        <v>6991691</v>
+        <v>6991676</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Ett stort områden typ 10 kvadratmeter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3708,12 +3708,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4506,7 +4506,7 @@
         <v>125397089</v>
       </c>
       <c r="B37" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4629,62 +4629,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125396498</v>
+        <v>125397175</v>
       </c>
       <c r="B38" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>564463</v>
+        <v>564453</v>
       </c>
       <c r="R38" t="n">
-        <v>6991617</v>
+        <v>6991658</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4713,7 +4699,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4723,7 +4709,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4738,19 +4729,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125397175</v>
+        <v>125397385</v>
       </c>
       <c r="B39" t="n">
         <v>80075</v>
@@ -4785,10 +4776,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>564453</v>
+        <v>564442</v>
       </c>
       <c r="R39" t="n">
-        <v>6991658</v>
+        <v>6991680</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4820,7 +4811,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4830,12 +4821,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4862,48 +4853,62 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125397385</v>
+        <v>125396498</v>
       </c>
       <c r="B40" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>564442</v>
+        <v>564463</v>
       </c>
       <c r="R40" t="n">
-        <v>6991680</v>
+        <v>6991617</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4932,7 +4937,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4942,12 +4947,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På sälg i gammal granskog</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4962,12 +4962,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5091,48 +5091,57 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125396843</v>
+        <v>125396600</v>
       </c>
       <c r="B42" t="n">
-        <v>91232</v>
+        <v>80104</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>564431</v>
+        <v>564463</v>
       </c>
       <c r="R42" t="n">
-        <v>6991652</v>
+        <v>6991617</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5161,7 +5170,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5171,12 +5180,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:33</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5191,69 +5195,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125396600</v>
+        <v>125396843</v>
       </c>
       <c r="B43" t="n">
-        <v>80104</v>
+        <v>91232</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>564463</v>
+        <v>564431</v>
       </c>
       <c r="R43" t="n">
-        <v>6991617</v>
+        <v>6991652</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5282,7 +5277,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5292,7 +5287,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5307,44 +5307,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125438544</v>
+        <v>125420522</v>
       </c>
       <c r="B44" t="n">
-        <v>91197</v>
+        <v>79590</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>564517</v>
+        <v>564449</v>
       </c>
       <c r="R44" t="n">
-        <v>6991669</v>
+        <v>6991631</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5387,14 +5387,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På ved på gammal tallhögstubbe i gammal tallskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5409,60 +5419,68 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125420522</v>
+        <v>125426277</v>
       </c>
       <c r="B45" t="n">
-        <v>79590</v>
+        <v>98339</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>564449</v>
+        <v>564468</v>
       </c>
       <c r="R45" t="n">
-        <v>6991631</v>
+        <v>6991658</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5489,100 +5507,78 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På ved på gammal tallhögstubbe i gammal tallskog</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125426277</v>
+        <v>125438544</v>
       </c>
       <c r="B46" t="n">
-        <v>98338</v>
+        <v>91197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>564468</v>
+        <v>564517</v>
       </c>
       <c r="R46" t="n">
-        <v>6991658</v>
+        <v>6991669</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5614,73 +5610,77 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125420540</v>
+        <v>125426255</v>
       </c>
       <c r="B47" t="n">
-        <v>98338</v>
+        <v>91197</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>564495</v>
+        <v>564448</v>
       </c>
       <c r="R47" t="n">
-        <v>6991590</v>
+        <v>6991620</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5707,24 +5707,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>40 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5739,44 +5724,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125420520</v>
+        <v>125420540</v>
       </c>
       <c r="B48" t="n">
-        <v>105347</v>
+        <v>98339</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5786,10 +5771,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>564498</v>
+        <v>564495</v>
       </c>
       <c r="R48" t="n">
-        <v>6991598</v>
+        <v>6991590</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5821,7 +5806,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5831,12 +5816,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>40 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5863,10 +5848,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125426255</v>
+        <v>125420520</v>
       </c>
       <c r="B49" t="n">
-        <v>91197</v>
+        <v>105348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5874,37 +5859,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>564448</v>
+        <v>564498</v>
       </c>
       <c r="R49" t="n">
-        <v>6991620</v>
+        <v>6991598</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5931,9 +5916,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5948,12 +5948,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5963,7 +5963,7 @@
         <v>125426252</v>
       </c>
       <c r="B50" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6587,10 +6587,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125420528</v>
+        <v>125426286</v>
       </c>
       <c r="B56" t="n">
-        <v>98359</v>
+        <v>80110</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6598,37 +6598,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>564555</v>
+        <v>564556</v>
       </c>
       <c r="R56" t="n">
         <v>6991665</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6655,24 +6655,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6687,44 +6672,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125426286</v>
+        <v>125426267</v>
       </c>
       <c r="B57" t="n">
-        <v>80110</v>
+        <v>91528</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6734,10 +6719,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>564556</v>
+        <v>564405</v>
       </c>
       <c r="R57" t="n">
-        <v>6991665</v>
+        <v>6991645</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6796,48 +6781,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125426267</v>
+        <v>125420528</v>
       </c>
       <c r="B58" t="n">
-        <v>91528</v>
+        <v>98360</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>564405</v>
+        <v>564555</v>
       </c>
       <c r="R58" t="n">
-        <v>6991645</v>
+        <v>6991665</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6864,9 +6849,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6881,57 +6881,65 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125426250</v>
+        <v>125426279</v>
       </c>
       <c r="B59" t="n">
-        <v>105347</v>
+        <v>98339</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>564528</v>
+        <v>564474</v>
       </c>
       <c r="R59" t="n">
-        <v>6991624</v>
+        <v>6991589</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6972,6 +6980,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6990,53 +6999,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125426279</v>
+        <v>125426250</v>
       </c>
       <c r="B60" t="n">
-        <v>98338</v>
+        <v>105348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>564474</v>
+        <v>564528</v>
       </c>
       <c r="R60" t="n">
-        <v>6991589</v>
+        <v>6991624</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7077,7 +7078,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7295,48 +7295,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125426269</v>
+        <v>125420538</v>
       </c>
       <c r="B63" t="n">
-        <v>98372</v>
+        <v>80075</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>564521</v>
+        <v>564491</v>
       </c>
       <c r="R63" t="n">
-        <v>6991595</v>
+        <v>6991571</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7363,9 +7363,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7380,60 +7395,60 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125420538</v>
+        <v>125426269</v>
       </c>
       <c r="B64" t="n">
-        <v>80075</v>
+        <v>98373</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>564491</v>
+        <v>564521</v>
       </c>
       <c r="R64" t="n">
-        <v>6991571</v>
+        <v>6991595</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7460,24 +7475,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7492,22 +7492,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125420542</v>
+        <v>125420529</v>
       </c>
       <c r="B65" t="n">
-        <v>78972</v>
+        <v>78961</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7515,21 +7515,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>336</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Solfjäderlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cheiromycina flabelliformis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>B.Sutton</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7539,10 +7539,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>564429</v>
+        <v>564492</v>
       </c>
       <c r="R65" t="n">
-        <v>6991627</v>
+        <v>6991578</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
+          <t>På bark vid basen av gammal död sälg i fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7616,10 +7616,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125420529</v>
+        <v>125420542</v>
       </c>
       <c r="B66" t="n">
-        <v>78961</v>
+        <v>78972</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7627,21 +7627,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>336</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Solfjäderlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cheiromycina flabelliformis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>B.Sutton</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7651,10 +7651,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>564492</v>
+        <v>564429</v>
       </c>
       <c r="R66" t="n">
-        <v>6991578</v>
+        <v>6991627</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7696,12 +7696,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal död sälg i fuktig gammal granskog</t>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7843,7 +7843,7 @@
         <v>125420527</v>
       </c>
       <c r="B68" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>125426254</v>
       </c>
       <c r="B69" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8049,10 +8049,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125426280</v>
+        <v>125426251</v>
       </c>
       <c r="B70" t="n">
-        <v>78972</v>
+        <v>75067</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8060,21 +8060,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>564364</v>
+        <v>564469</v>
       </c>
       <c r="R70" t="n">
-        <v>6991670</v>
+        <v>6991678</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8146,10 +8146,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125426251</v>
+        <v>125426280</v>
       </c>
       <c r="B71" t="n">
-        <v>75067</v>
+        <v>78972</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8157,21 +8157,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8181,10 +8181,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>564469</v>
+        <v>564364</v>
       </c>
       <c r="R71" t="n">
-        <v>6991678</v>
+        <v>6991670</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8358,7 +8358,7 @@
         <v>125420539</v>
       </c>
       <c r="B73" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8467,48 +8467,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125420531</v>
+        <v>125426272</v>
       </c>
       <c r="B74" t="n">
-        <v>91528</v>
+        <v>95572</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>564486</v>
+        <v>564515</v>
       </c>
       <c r="R74" t="n">
-        <v>6991573</v>
+        <v>6991646</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8535,24 +8535,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8567,60 +8552,60 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125426272</v>
+        <v>125420531</v>
       </c>
       <c r="B75" t="n">
-        <v>95571</v>
+        <v>91528</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>564515</v>
+        <v>564486</v>
       </c>
       <c r="R75" t="n">
-        <v>6991646</v>
+        <v>6991573</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8647,9 +8632,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8664,12 +8664,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8791,7 +8791,7 @@
         <v>125420535</v>
       </c>
       <c r="B77" t="n">
-        <v>95571</v>
+        <v>95572</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9099,48 +9099,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125420541</v>
+        <v>125426285</v>
       </c>
       <c r="B80" t="n">
-        <v>98338</v>
+        <v>80110</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>564525</v>
+        <v>564561</v>
       </c>
       <c r="R80" t="n">
-        <v>6991662</v>
+        <v>6991616</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9167,24 +9167,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>10 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9199,60 +9184,60 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125426285</v>
+        <v>125420541</v>
       </c>
       <c r="B81" t="n">
-        <v>80110</v>
+        <v>98339</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>564561</v>
+        <v>564525</v>
       </c>
       <c r="R81" t="n">
-        <v>6991616</v>
+        <v>6991662</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9279,9 +9264,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>10 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9296,12 +9296,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9520,7 +9520,7 @@
         <v>125426278</v>
       </c>
       <c r="B84" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -3841,10 +3841,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125398578</v>
+        <v>125398468</v>
       </c>
       <c r="B31" t="n">
-        <v>82784</v>
+        <v>78731</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3852,21 +3852,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>564440</v>
+        <v>564441</v>
       </c>
       <c r="R31" t="n">
-        <v>6991662</v>
+        <v>6991674</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3921,7 +3921,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På kolad ved på två gamla tallhögstubbar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3936,7 +3941,7 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
@@ -3948,10 +3953,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125395850</v>
+        <v>125398578</v>
       </c>
       <c r="B32" t="n">
-        <v>91232</v>
+        <v>82784</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3959,39 +3964,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>564463</v>
+        <v>564440</v>
       </c>
       <c r="R32" t="n">
-        <v>6991559</v>
+        <v>6991662</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125398468</v>
+        <v>125395850</v>
       </c>
       <c r="B33" t="n">
-        <v>78731</v>
+        <v>91232</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4071,34 +4071,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>564441</v>
+        <v>564463</v>
       </c>
       <c r="R33" t="n">
-        <v>6991674</v>
+        <v>6991559</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4130,7 +4135,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4140,12 +4145,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På kolad ved på två gamla tallhögstubbar</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4160,12 +4160,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -5091,57 +5091,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125396600</v>
+        <v>125396843</v>
       </c>
       <c r="B42" t="n">
-        <v>80104</v>
+        <v>91232</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>564463</v>
+        <v>564431</v>
       </c>
       <c r="R42" t="n">
-        <v>6991617</v>
+        <v>6991652</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5170,7 +5161,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5180,7 +5171,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5195,60 +5191,69 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125396843</v>
+        <v>125396600</v>
       </c>
       <c r="B43" t="n">
-        <v>91232</v>
+        <v>80104</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>564431</v>
+        <v>564463</v>
       </c>
       <c r="R43" t="n">
-        <v>6991652</v>
+        <v>6991617</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5277,7 +5282,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5287,12 +5292,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:33</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5307,12 +5307,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -8788,32 +8788,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125420535</v>
+        <v>125438549</v>
       </c>
       <c r="B77" t="n">
-        <v>95572</v>
+        <v>77926</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2809</v>
+        <v>228579</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8823,10 +8823,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>564539</v>
+        <v>564542</v>
       </c>
       <c r="R77" t="n">
-        <v>6991663</v>
+        <v>6991657</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8856,24 +8856,14 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På marken i gammal fuktig granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8888,44 +8878,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125438549</v>
+        <v>125420535</v>
       </c>
       <c r="B78" t="n">
-        <v>77926</v>
+        <v>95572</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228579</v>
+        <v>2809</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8935,10 +8925,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>564542</v>
+        <v>564539</v>
       </c>
       <c r="R78" t="n">
-        <v>6991657</v>
+        <v>6991663</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8968,14 +8958,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På marken i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8990,12 +8990,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -5319,48 +5319,56 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125420522</v>
+        <v>125426277</v>
       </c>
       <c r="B44" t="n">
-        <v>79590</v>
+        <v>98339</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>564449</v>
+        <v>564468</v>
       </c>
       <c r="R44" t="n">
-        <v>6991631</v>
+        <v>6991658</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5387,100 +5395,78 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På ved på gammal tallhögstubbe i gammal tallskog</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125426277</v>
+        <v>125420522</v>
       </c>
       <c r="B45" t="n">
-        <v>98339</v>
+        <v>79590</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>564468</v>
+        <v>564449</v>
       </c>
       <c r="R45" t="n">
-        <v>6991658</v>
+        <v>6991631</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5507,30 +5493,44 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På ved på gammal tallhögstubbe i gammal tallskog</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5736,32 +5736,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125420540</v>
+        <v>125420520</v>
       </c>
       <c r="B48" t="n">
-        <v>98339</v>
+        <v>105348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>564495</v>
+        <v>564498</v>
       </c>
       <c r="R48" t="n">
-        <v>6991590</v>
+        <v>6991598</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>40 plantor på marken i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5848,32 +5848,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125420520</v>
+        <v>125420540</v>
       </c>
       <c r="B49" t="n">
-        <v>105348</v>
+        <v>98339</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>564498</v>
+        <v>564495</v>
       </c>
       <c r="R49" t="n">
-        <v>6991598</v>
+        <v>6991590</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>40 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -9626,7 +9626,7 @@
         <v>125397829</v>
       </c>
       <c r="B85" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>125420524</v>
       </c>
       <c r="B86" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>125438545</v>
       </c>
       <c r="B87" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>125426258</v>
       </c>
       <c r="B88" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -9845,7 +9845,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -9626,7 +9626,7 @@
         <v>125397829</v>
       </c>
       <c r="B85" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>125420524</v>
       </c>
       <c r="B86" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9855,7 +9855,7 @@
         <v>125438545</v>
       </c>
       <c r="B87" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>125426258</v>
       </c>
       <c r="B88" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -9626,7 +9626,7 @@
         <v>125397829</v>
       </c>
       <c r="B85" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>125420524</v>
       </c>
       <c r="B86" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>125438545</v>
       </c>
       <c r="B87" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>125426258</v>
       </c>
       <c r="B88" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AY101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121742429</v>
+        <v>125426252</v>
       </c>
       <c r="B2" t="n">
-        <v>97111</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564502</v>
+        <v>564532</v>
       </c>
       <c r="R2" t="n">
-        <v>6991645</v>
+        <v>6991656</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,34 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121742198</v>
+        <v>125426254</v>
       </c>
       <c r="B3" t="n">
-        <v>78643</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,40 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564489</v>
+        <v>564412</v>
       </c>
       <c r="R3" t="n">
-        <v>6991655</v>
+        <v>6991656</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,75 +851,66 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121742191</v>
+        <v>125420534</v>
       </c>
       <c r="B4" t="n">
-        <v>79724</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>98</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk rödprick</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia incarnata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Th.Fr. ex Almq.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564496</v>
+        <v>564500</v>
       </c>
       <c r="R4" t="n">
-        <v>6991571</v>
+        <v>6991603</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,17 +934,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Lunglav på flera granar samt sälg</t>
+          <t>På bark vid basen av gammal levande grov sälg (75 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,34 +963,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121760563</v>
+        <v>125420543</v>
       </c>
       <c r="B5" t="n">
-        <v>79726</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,13 +1016,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564489</v>
+        <v>564520</v>
       </c>
       <c r="R5" t="n">
-        <v>6991655</v>
+        <v>6991622</v>
       </c>
       <c r="S5" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1069,17 +1046,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Lunglav på häll av granit från revsundsviten</t>
+          <t>På ved på gammal granhögstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,27 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121798188</v>
+        <v>125399220</v>
       </c>
       <c r="B6" t="n">
-        <v>79726</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,37 +1104,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564369</v>
+        <v>564519</v>
       </c>
       <c r="R6" t="n">
-        <v>6991688</v>
+        <v>6991683</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1176,17 +1158,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Lunglav på björk</t>
+          <t>På toppknäckt granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,27 +1193,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121798373</v>
+        <v>125396762</v>
       </c>
       <c r="B7" t="n">
-        <v>57374</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,37 +1216,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564425</v>
+        <v>564441</v>
       </c>
       <c r="R7" t="n">
-        <v>6991636</v>
+        <v>6991661</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,17 +1275,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,49 +1305,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121798905</v>
+        <v>125420531</v>
       </c>
       <c r="B8" t="n">
-        <v>79755</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1360,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564433</v>
+        <v>564486</v>
       </c>
       <c r="R8" t="n">
-        <v>6991692</v>
+        <v>6991573</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1390,12 +1382,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1410,27 +1417,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121797957</v>
+        <v>125426264</v>
       </c>
       <c r="B9" t="n">
-        <v>57374</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,37 +1440,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564365</v>
+        <v>564514</v>
       </c>
       <c r="R9" t="n">
-        <v>6991638</v>
+        <v>6991688</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1492,17 +1494,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1517,65 +1514,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121798890</v>
+        <v>125426265</v>
       </c>
       <c r="B10" t="n">
-        <v>79755</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564502</v>
+        <v>564336</v>
       </c>
       <c r="R10" t="n">
-        <v>6991645</v>
+        <v>6991633</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1599,12 +1591,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1619,27 +1611,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121797975</v>
+        <v>125426267</v>
       </c>
       <c r="B11" t="n">
-        <v>79726</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1647,37 +1634,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564433</v>
+        <v>564405</v>
       </c>
       <c r="R11" t="n">
-        <v>6991692</v>
+        <v>6991645</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1701,12 +1688,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1721,27 +1708,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122040095</v>
+        <v>125395850</v>
       </c>
       <c r="B12" t="n">
-        <v>79732</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,37 +1731,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564541</v>
+        <v>564463</v>
       </c>
       <c r="R12" t="n">
-        <v>6991646</v>
+        <v>6991559</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1803,12 +1790,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1823,27 +1820,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122040092</v>
+        <v>125396221</v>
       </c>
       <c r="B13" t="n">
-        <v>79732</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,37 +1843,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564556</v>
+        <v>564445</v>
       </c>
       <c r="R13" t="n">
-        <v>6991632</v>
+        <v>6991608</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1905,12 +1902,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1925,69 +1937,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122188795</v>
+        <v>125396843</v>
       </c>
       <c r="B14" t="n">
-        <v>98237</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564449</v>
+        <v>564431</v>
       </c>
       <c r="R14" t="n">
-        <v>6991626</v>
+        <v>6991652</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2011,12 +2014,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2025,76 +2043,66 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122188793</v>
+        <v>125398362</v>
       </c>
       <c r="B15" t="n">
-        <v>98237</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564424</v>
+        <v>564453</v>
       </c>
       <c r="R15" t="n">
-        <v>6991686</v>
+        <v>6991691</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2118,12 +2126,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2132,72 +2155,66 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124048430</v>
+        <v>125398876</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564473</v>
+        <v>564507</v>
       </c>
       <c r="R16" t="n">
-        <v>6991618</v>
+        <v>6991687</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2221,12 +2238,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På två granlågor i lågabröt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2241,49 +2273,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124048336</v>
+        <v>125420523</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2293,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564479</v>
+        <v>564516</v>
       </c>
       <c r="R17" t="n">
-        <v>6991569</v>
+        <v>6991629</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2323,12 +2350,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2343,27 +2385,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124048482</v>
+        <v>125426257</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2371,42 +2408,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564473</v>
+        <v>564337</v>
       </c>
       <c r="R18" t="n">
-        <v>6991618</v>
+        <v>6991632</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2430,17 +2462,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2455,62 +2482,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124048509</v>
+        <v>125426262</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564479</v>
+        <v>564395</v>
       </c>
       <c r="R19" t="n">
-        <v>6991672</v>
+        <v>6991654</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2537,12 +2559,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2557,65 +2579,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124048300</v>
+        <v>125398578</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564449</v>
+        <v>564440</v>
       </c>
       <c r="R20" t="n">
-        <v>6991568</v>
+        <v>6991662</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2639,12 +2656,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2659,71 +2686,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Olsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125397300</v>
+        <v>125420535</v>
       </c>
       <c r="B21" t="n">
-        <v>98339</v>
+        <v>96338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564442</v>
+        <v>564539</v>
       </c>
       <c r="R21" t="n">
-        <v>6991680</v>
+        <v>6991663</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2755,7 +2768,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2765,12 +2778,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2797,53 +2810,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125396762</v>
+        <v>125426270</v>
       </c>
       <c r="B22" t="n">
-        <v>91528</v>
+        <v>96338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564441</v>
+        <v>564544</v>
       </c>
       <c r="R22" t="n">
-        <v>6991661</v>
+        <v>6991700</v>
       </c>
       <c r="S22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2870,19 +2878,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2897,60 +2895,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125398434</v>
+        <v>125426271</v>
       </c>
       <c r="B23" t="n">
-        <v>80075</v>
+        <v>96338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564420</v>
+        <v>564531</v>
       </c>
       <c r="R23" t="n">
-        <v>6991658</v>
+        <v>6991571</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2977,24 +2975,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3009,69 +2992,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125397219</v>
+        <v>125426272</v>
       </c>
       <c r="B24" t="n">
-        <v>80075</v>
+        <v>96338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>564440</v>
+        <v>564515</v>
       </c>
       <c r="R24" t="n">
-        <v>6991662</v>
+        <v>6991646</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3098,19 +3072,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3125,65 +3089,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125396883</v>
+        <v>125426255</v>
       </c>
       <c r="B25" t="n">
-        <v>78730</v>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>564440</v>
+        <v>564448</v>
       </c>
       <c r="R25" t="n">
-        <v>6991655</v>
+        <v>6991620</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3210,24 +3169,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3242,69 +3186,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125395199</v>
+        <v>125438544</v>
       </c>
       <c r="B26" t="n">
-        <v>80075</v>
+        <v>91872</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>564521</v>
+        <v>564517</v>
       </c>
       <c r="R26" t="n">
-        <v>6991610</v>
+        <v>6991669</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3331,24 +3266,14 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gråal</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3375,48 +3300,51 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125397495</v>
+        <v>121742198</v>
       </c>
       <c r="B27" t="n">
-        <v>79979</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>564410</v>
+        <v>564489</v>
       </c>
       <c r="R27" t="n">
-        <v>6991660</v>
+        <v>6991655</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3440,27 +3368,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:53</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3469,63 +3382,73 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125398362</v>
+        <v>125398524</v>
       </c>
       <c r="B28" t="n">
-        <v>91232</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>564453</v>
+        <v>564457</v>
       </c>
       <c r="R28" t="n">
-        <v>6991691</v>
+        <v>6991682</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3557,7 +3480,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3567,12 +3490,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3599,10 +3522,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125398718</v>
+        <v>125420542</v>
       </c>
       <c r="B29" t="n">
-        <v>98339</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3610,43 +3533,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>564439</v>
+        <v>564429</v>
       </c>
       <c r="R29" t="n">
-        <v>6991676</v>
+        <v>6991627</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3678,7 +3592,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3688,12 +3602,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ett stort områden typ 10 kvadratmeter</t>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3708,26 +3622,26 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125398524</v>
+        <v>125426280</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3748,29 +3662,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>564457</v>
+        <v>564364</v>
       </c>
       <c r="R30" t="n">
-        <v>6991682</v>
+        <v>6991670</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3797,24 +3702,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3829,60 +3719,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125398468</v>
+        <v>125426281</v>
       </c>
       <c r="B31" t="n">
-        <v>78731</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>564441</v>
+        <v>564408</v>
       </c>
       <c r="R31" t="n">
-        <v>6991674</v>
+        <v>6991646</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3909,24 +3799,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På kolad ved på två gamla tallhögstubbar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3941,57 +3816,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125398578</v>
+        <v>125420530</v>
       </c>
       <c r="B32" t="n">
-        <v>82784</v>
+        <v>75300</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6428</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>564440</v>
+        <v>564520</v>
       </c>
       <c r="R32" t="n">
-        <v>6991662</v>
+        <v>6991626</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4023,7 +3898,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4033,7 +3908,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4048,7 +3928,7 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -4060,10 +3940,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125395850</v>
+        <v>125397801</v>
       </c>
       <c r="B33" t="n">
-        <v>91232</v>
+        <v>83307</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4071,42 +3951,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>564463</v>
+        <v>564440</v>
       </c>
       <c r="R33" t="n">
-        <v>6991559</v>
+        <v>6991662</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4135,7 +4010,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4145,7 +4020,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4172,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125397801</v>
+        <v>125426251</v>
       </c>
       <c r="B34" t="n">
-        <v>75067</v>
+        <v>83307</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4203,17 +4083,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>564440</v>
+        <v>564469</v>
       </c>
       <c r="R34" t="n">
-        <v>6991662</v>
+        <v>6991678</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4240,24 +4120,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4272,22 +4137,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125396949</v>
+        <v>125396883</v>
       </c>
       <c r="B35" t="n">
-        <v>78731</v>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4295,24 +4160,29 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stortjärndalen, Stortjärndalen, Jmt</t>
@@ -4354,7 +4224,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4364,7 +4234,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4396,10 +4266,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125396355</v>
+        <v>125399514</v>
       </c>
       <c r="B36" t="n">
-        <v>78731</v>
+        <v>79946</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4407,21 +4277,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4431,10 +4301,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>564463</v>
+        <v>564559</v>
       </c>
       <c r="R36" t="n">
-        <v>6991617</v>
+        <v>6991707</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4466,7 +4336,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4476,7 +4346,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal tallhögstubbe i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4491,71 +4366,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125397089</v>
+        <v>125420522</v>
       </c>
       <c r="B37" t="n">
-        <v>98339</v>
+        <v>79946</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>564452</v>
+        <v>564449</v>
       </c>
       <c r="R37" t="n">
-        <v>6991661</v>
+        <v>6991631</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4587,7 +4448,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4597,12 +4458,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt på marken i gammal granskog</t>
+          <t>På ved på gammal tallhögstubbe i gammal tallskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4629,32 +4490,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125397175</v>
+        <v>125397495</v>
       </c>
       <c r="B38" t="n">
-        <v>80075</v>
+        <v>80336</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4664,10 +4525,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>564453</v>
+        <v>564410</v>
       </c>
       <c r="R38" t="n">
-        <v>6991658</v>
+        <v>6991660</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4699,7 +4560,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4709,12 +4570,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4734,17 +4595,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125397385</v>
+        <v>121742191</v>
       </c>
       <c r="B39" t="n">
-        <v>80075</v>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4770,19 +4631,22 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>564442</v>
+        <v>564496</v>
       </c>
       <c r="R39" t="n">
-        <v>6991680</v>
+        <v>6991571</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4806,27 +4670,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På sälg i gammal granskog</t>
+          <t>Lunglav på flera granar samt sälg</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4835,80 +4689,67 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125396498</v>
+        <v>121760563</v>
       </c>
       <c r="B40" t="n">
-        <v>98339</v>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>564463</v>
+        <v>564489</v>
       </c>
       <c r="R40" t="n">
-        <v>6991617</v>
+        <v>6991655</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4932,22 +4773,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:21</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:21</t>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Lunglav på häll av granit från revsundsviten</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4962,22 +4798,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125396221</v>
+        <v>121797975</v>
       </c>
       <c r="B41" t="n">
-        <v>91232</v>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4985,42 +4821,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>564445</v>
+        <v>564433</v>
       </c>
       <c r="R41" t="n">
-        <v>6991608</v>
+        <v>6991692</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5044,27 +4875,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:05</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5079,22 +4895,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125396843</v>
+        <v>121798037</v>
       </c>
       <c r="B42" t="n">
-        <v>91232</v>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5102,37 +4918,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>564431</v>
+        <v>564295</v>
       </c>
       <c r="R42" t="n">
-        <v>6991652</v>
+        <v>6991669</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5156,27 +4972,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>Gott om lunglav även på intilliggande granar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5191,69 +4997,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125396600</v>
+        <v>121798188</v>
       </c>
       <c r="B43" t="n">
-        <v>80104</v>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>564463</v>
+        <v>564369</v>
       </c>
       <c r="R43" t="n">
-        <v>6991617</v>
+        <v>6991688</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5277,22 +5074,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5307,68 +5099,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125426277</v>
+        <v>121798200</v>
       </c>
       <c r="B44" t="n">
-        <v>98339</v>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>564468</v>
+        <v>564333</v>
       </c>
       <c r="R44" t="n">
-        <v>6991658</v>
+        <v>6991691</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5392,12 +5176,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5406,29 +5190,28 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125420522</v>
+        <v>122040092</v>
       </c>
       <c r="B45" t="n">
-        <v>79590</v>
+        <v>80432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5436,21 +5219,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5460,13 +5243,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>564449</v>
+        <v>564556</v>
       </c>
       <c r="R45" t="n">
-        <v>6991631</v>
+        <v>6991632</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5490,27 +5273,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På ved på gammal tallhögstubbe i gammal tallskog</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5525,44 +5293,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125438544</v>
+        <v>122040095</v>
       </c>
       <c r="B46" t="n">
-        <v>91197</v>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5572,13 +5340,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>564517</v>
+        <v>564541</v>
       </c>
       <c r="R46" t="n">
-        <v>6991669</v>
+        <v>6991646</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5602,17 +5370,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5627,60 +5390,69 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125426255</v>
+        <v>125395199</v>
       </c>
       <c r="B47" t="n">
-        <v>91197</v>
+        <v>80432</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>564448</v>
+        <v>564521</v>
       </c>
       <c r="R47" t="n">
-        <v>6991620</v>
+        <v>6991610</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5707,9 +5479,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På gråal</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5724,57 +5511,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125420520</v>
+        <v>125397175</v>
       </c>
       <c r="B48" t="n">
-        <v>105348</v>
+        <v>80432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>564498</v>
+        <v>564453</v>
       </c>
       <c r="R48" t="n">
-        <v>6991598</v>
+        <v>6991658</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5806,7 +5593,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5816,12 +5603,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5848,48 +5635,57 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125420540</v>
+        <v>125397219</v>
       </c>
       <c r="B49" t="n">
-        <v>98339</v>
+        <v>80432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>564495</v>
+        <v>564440</v>
       </c>
       <c r="R49" t="n">
-        <v>6991590</v>
+        <v>6991662</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5918,7 +5714,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5928,12 +5724,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>40 plantor på marken i gammal granskog</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5948,22 +5739,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125426252</v>
+        <v>125397385</v>
       </c>
       <c r="B50" t="n">
-        <v>96592</v>
+        <v>80432</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5971,37 +5762,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>564532</v>
+        <v>564442</v>
       </c>
       <c r="R50" t="n">
-        <v>6991656</v>
+        <v>6991680</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6028,9 +5819,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6045,57 +5851,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125420534</v>
+        <v>125398434</v>
       </c>
       <c r="B51" t="n">
-        <v>74842</v>
+        <v>80432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>98</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk rödprick</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Arthonia incarnata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Th.Fr. ex Almq.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>564500</v>
+        <v>564420</v>
       </c>
       <c r="R51" t="n">
-        <v>6991603</v>
+        <v>6991658</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6127,7 +5933,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6137,12 +5943,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande grov sälg (75 cm dbh) i gammal granskog</t>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6157,60 +5963,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125426262</v>
+        <v>125420536</v>
       </c>
       <c r="B52" t="n">
-        <v>91686</v>
+        <v>80432</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>564395</v>
+        <v>564470</v>
       </c>
       <c r="R52" t="n">
-        <v>6991654</v>
+        <v>6991585</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6237,9 +6043,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Mycket rikligt på gran under grov asp</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6254,22 +6075,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125420543</v>
+        <v>125420537</v>
       </c>
       <c r="B53" t="n">
-        <v>75059</v>
+        <v>80432</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6277,21 +6098,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6301,10 +6122,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>564520</v>
+        <v>564470</v>
       </c>
       <c r="R53" t="n">
-        <v>6991622</v>
+        <v>6991561</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6336,7 +6157,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6346,12 +6167,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På ved på gammal granhögstubbe</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6378,10 +6199,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125426257</v>
+        <v>125420538</v>
       </c>
       <c r="B54" t="n">
-        <v>91232</v>
+        <v>80432</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6389,37 +6210,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>564337</v>
+        <v>564491</v>
       </c>
       <c r="R54" t="n">
-        <v>6991632</v>
+        <v>6991571</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6446,9 +6267,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6463,60 +6299,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125420533</v>
+        <v>125426274</v>
       </c>
       <c r="B55" t="n">
-        <v>80103</v>
+        <v>80432</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>564582</v>
+        <v>564334</v>
       </c>
       <c r="R55" t="n">
-        <v>6991673</v>
+        <v>6991672</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6543,24 +6379,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6575,60 +6396,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125426286</v>
+        <v>125438547</v>
       </c>
       <c r="B56" t="n">
-        <v>80110</v>
+        <v>80432</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>564556</v>
+        <v>564543</v>
       </c>
       <c r="R56" t="n">
-        <v>6991665</v>
+        <v>6991694</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6658,6 +6479,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6672,60 +6498,60 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125426267</v>
+        <v>125420533</v>
       </c>
       <c r="B57" t="n">
-        <v>91528</v>
+        <v>80460</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>6461</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>564405</v>
+        <v>564582</v>
       </c>
       <c r="R57" t="n">
-        <v>6991645</v>
+        <v>6991673</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6752,9 +6578,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6769,22 +6610,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125420528</v>
+        <v>121798890</v>
       </c>
       <c r="B58" t="n">
-        <v>98360</v>
+        <v>80461</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6792,21 +6633,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6816,13 +6657,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>564555</v>
+        <v>564502</v>
       </c>
       <c r="R58" t="n">
-        <v>6991665</v>
+        <v>6991645</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6846,27 +6687,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>10:56</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6881,68 +6707,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125426279</v>
+        <v>121798905</v>
       </c>
       <c r="B59" t="n">
-        <v>98339</v>
+        <v>80461</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>564474</v>
+        <v>564433</v>
       </c>
       <c r="R59" t="n">
-        <v>6991589</v>
+        <v>6991692</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6966,12 +6784,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6980,29 +6798,28 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125426250</v>
+        <v>125396600</v>
       </c>
       <c r="B60" t="n">
-        <v>105348</v>
+        <v>80461</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7010,37 +6827,46 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>564528</v>
+        <v>564463</v>
       </c>
       <c r="R60" t="n">
-        <v>6991624</v>
+        <v>6991617</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7067,9 +6893,19 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7084,44 +6920,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125426281</v>
+        <v>125426260</v>
       </c>
       <c r="B61" t="n">
-        <v>78972</v>
+        <v>80461</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7131,10 +6967,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>564408</v>
+        <v>564551</v>
       </c>
       <c r="R61" t="n">
-        <v>6991646</v>
+        <v>6991633</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7193,10 +7029,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125438548</v>
+        <v>125426285</v>
       </c>
       <c r="B62" t="n">
-        <v>80111</v>
+        <v>80467</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7204,37 +7040,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>564548</v>
+        <v>564561</v>
       </c>
       <c r="R62" t="n">
-        <v>6991664</v>
+        <v>6991616</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7264,11 +7100,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7283,60 +7114,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125420538</v>
+        <v>125426286</v>
       </c>
       <c r="B63" t="n">
-        <v>80075</v>
+        <v>80467</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>564491</v>
+        <v>564556</v>
       </c>
       <c r="R63" t="n">
-        <v>6991571</v>
+        <v>6991665</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7363,24 +7194,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7395,22 +7211,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125426269</v>
+        <v>125438548</v>
       </c>
       <c r="B64" t="n">
-        <v>98373</v>
+        <v>80468</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7418,37 +7234,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219874</v>
+        <v>6464</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>564521</v>
+        <v>564548</v>
       </c>
       <c r="R64" t="n">
-        <v>6991595</v>
+        <v>6991664</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7478,6 +7294,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7492,22 +7313,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125420529</v>
+        <v>121797957</v>
       </c>
       <c r="B65" t="n">
-        <v>78961</v>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7515,21 +7336,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>336</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Solfjäderlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cheiromycina flabelliformis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>B.Sutton</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7539,13 +7360,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>564492</v>
+        <v>564365</v>
       </c>
       <c r="R65" t="n">
-        <v>6991578</v>
+        <v>6991638</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7569,27 +7390,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>12:47</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>12:47</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal död sälg i fuktig gammal granskog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7604,22 +7415,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125420542</v>
+        <v>121798373</v>
       </c>
       <c r="B66" t="n">
-        <v>78972</v>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7627,21 +7438,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7651,13 +7462,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>564429</v>
+        <v>564425</v>
       </c>
       <c r="R66" t="n">
-        <v>6991627</v>
+        <v>6991636</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7681,27 +7492,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:29</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:29</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7716,60 +7517,65 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125420530</v>
+        <v>124048482</v>
       </c>
       <c r="B67" t="n">
-        <v>74878</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>564520</v>
+        <v>564473</v>
       </c>
       <c r="R67" t="n">
-        <v>6991626</v>
+        <v>6991618</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7793,27 +7599,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:39</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:39</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7828,57 +7624,62 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125420527</v>
+        <v>125397829</v>
       </c>
       <c r="B68" t="n">
-        <v>98360</v>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>564499</v>
+        <v>564401</v>
       </c>
       <c r="R68" t="n">
-        <v>6991597</v>
+        <v>6991629</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7910,7 +7711,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7920,12 +7721,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>Rikliga ringhack på gammal tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7940,22 +7741,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125426254</v>
+        <v>125420524</v>
       </c>
       <c r="B69" t="n">
-        <v>96592</v>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7963,37 +7764,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>564412</v>
+        <v>564474</v>
       </c>
       <c r="R69" t="n">
-        <v>6991656</v>
+        <v>6991608</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8020,9 +7821,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Helt färska och äldre ringhack, rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8037,22 +7853,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125426251</v>
+        <v>125426258</v>
       </c>
       <c r="B70" t="n">
-        <v>75067</v>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8060,34 +7876,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>564469</v>
+        <v>564461</v>
       </c>
       <c r="R70" t="n">
-        <v>6991678</v>
+        <v>6991657</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8120,6 +7944,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8146,10 +7975,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125426280</v>
+        <v>125438545</v>
       </c>
       <c r="B71" t="n">
-        <v>78972</v>
+        <v>57953</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8157,37 +7986,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>564364</v>
+        <v>564535</v>
       </c>
       <c r="R71" t="n">
-        <v>6991670</v>
+        <v>6991601</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8217,6 +8046,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8231,60 +8065,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125420537</v>
+        <v>125426269</v>
       </c>
       <c r="B72" t="n">
-        <v>80075</v>
+        <v>99153</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>564470</v>
+        <v>564521</v>
       </c>
       <c r="R72" t="n">
-        <v>6991561</v>
+        <v>6991595</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8311,24 +8145,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8343,22 +8162,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125420539</v>
+        <v>122188793</v>
       </c>
       <c r="B73" t="n">
-        <v>98339</v>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8384,19 +8203,23 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>564466</v>
+        <v>564424</v>
       </c>
       <c r="R73" t="n">
-        <v>6991587</v>
+        <v>6991686</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8420,27 +8243,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>12:58</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>60 plantor på marken i gammal barrblandskog</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8449,66 +8257,71 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125426272</v>
+        <v>122188795</v>
       </c>
       <c r="B74" t="n">
-        <v>95572</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>564515</v>
+        <v>564449</v>
       </c>
       <c r="R74" t="n">
-        <v>6991646</v>
+        <v>6991626</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8532,12 +8345,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8546,50 +8359,51 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125420531</v>
+        <v>122227587</v>
       </c>
       <c r="B75" t="n">
-        <v>91528</v>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8599,13 +8413,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>564486</v>
+        <v>564524</v>
       </c>
       <c r="R75" t="n">
-        <v>6991573</v>
+        <v>6991706</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8629,27 +8443,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>12:49</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8664,44 +8463,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125420536</v>
+        <v>124048300</v>
       </c>
       <c r="B76" t="n">
-        <v>80075</v>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8711,13 +8510,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>564470</v>
+        <v>564449</v>
       </c>
       <c r="R76" t="n">
-        <v>6991585</v>
+        <v>6991568</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8741,27 +8540,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>13:01</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Mycket rikligt på gran under grov asp</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8776,44 +8560,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125438549</v>
+        <v>124048336</v>
       </c>
       <c r="B77" t="n">
-        <v>77926</v>
+        <v>99118</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8823,10 +8607,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>564542</v>
+        <v>564479</v>
       </c>
       <c r="R77" t="n">
-        <v>6991657</v>
+        <v>6991569</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8853,17 +8637,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8878,44 +8657,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125420535</v>
+        <v>124048430</v>
       </c>
       <c r="B78" t="n">
-        <v>95572</v>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8925,13 +8704,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>564539</v>
+        <v>564473</v>
       </c>
       <c r="R78" t="n">
-        <v>6991663</v>
+        <v>6991618</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8955,27 +8734,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På marken i gammal fuktig granskog</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8990,57 +8754,57 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125426265</v>
+        <v>124048509</v>
       </c>
       <c r="B79" t="n">
-        <v>91528</v>
+        <v>99118</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>564336</v>
+        <v>564479</v>
       </c>
       <c r="R79" t="n">
-        <v>6991633</v>
+        <v>6991672</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -9067,12 +8831,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9087,60 +8851,74 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Joel Olsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125426285</v>
+        <v>125396498</v>
       </c>
       <c r="B80" t="n">
-        <v>80110</v>
+        <v>99118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>564561</v>
+        <v>564463</v>
       </c>
       <c r="R80" t="n">
-        <v>6991616</v>
+        <v>6991617</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9167,9 +8945,19 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9184,22 +8972,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125420541</v>
+        <v>125397089</v>
       </c>
       <c r="B81" t="n">
-        <v>98339</v>
+        <v>99118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9224,17 +9012,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>564525</v>
+        <v>564452</v>
       </c>
       <c r="R81" t="n">
-        <v>6991662</v>
+        <v>6991661</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9266,7 +9068,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9276,12 +9078,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>10 plantor på marken i gammal granskog</t>
+          <t>Rikligt på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9308,45 +9110,59 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125420523</v>
+        <v>125397259</v>
       </c>
       <c r="B82" t="n">
-        <v>91232</v>
+        <v>99118</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>564516</v>
+        <v>564442</v>
       </c>
       <c r="R82" t="n">
-        <v>6991629</v>
+        <v>6991680</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9378,7 +9194,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9388,12 +9204,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9420,48 +9236,57 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125426260</v>
+        <v>125398718</v>
       </c>
       <c r="B83" t="n">
-        <v>80104</v>
+        <v>99118</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>564551</v>
+        <v>564439</v>
       </c>
       <c r="R83" t="n">
-        <v>6991633</v>
+        <v>6991676</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9488,9 +9313,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ett stort områden typ 10 kvadratmeter</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9505,22 +9345,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125426278</v>
+        <v>125399292</v>
       </c>
       <c r="B84" t="n">
-        <v>98339</v>
+        <v>99118</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9547,26 +9387,32 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>564453</v>
+        <v>564535</v>
       </c>
       <c r="R84" t="n">
-        <v>6991629</v>
+        <v>6991702</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9593,80 +9439,89 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På marken i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125397829</v>
+        <v>125420539</v>
       </c>
       <c r="B85" t="n">
-        <v>57657</v>
+        <v>99118</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>564401</v>
+        <v>564466</v>
       </c>
       <c r="R85" t="n">
-        <v>6991629</v>
+        <v>6991587</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9698,7 +9553,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9708,12 +9563,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Rikliga ringhack på gammal tall</t>
+          <t>60 plantor på marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9728,44 +9583,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125420524</v>
+        <v>125420540</v>
       </c>
       <c r="B86" t="n">
-        <v>57657</v>
+        <v>99118</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9775,10 +9630,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>564474</v>
+        <v>564495</v>
       </c>
       <c r="R86" t="n">
-        <v>6991608</v>
+        <v>6991590</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9810,7 +9665,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9820,12 +9675,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Helt färska och äldre ringhack, rikligt på gammal gran i gammal granskog</t>
+          <t>40 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9852,32 +9707,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125438545</v>
+        <v>125420541</v>
       </c>
       <c r="B87" t="n">
-        <v>57657</v>
+        <v>99118</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9887,10 +9742,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>564535</v>
+        <v>564525</v>
       </c>
       <c r="R87" t="n">
-        <v>6991601</v>
+        <v>6991662</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9920,14 +9775,24 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>10 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9942,54 +9807,54 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125426258</v>
+        <v>125426276</v>
       </c>
       <c r="B88" t="n">
-        <v>57657</v>
+        <v>99118</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9997,10 +9862,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>564461</v>
+        <v>564534</v>
       </c>
       <c r="R88" t="n">
-        <v>6991657</v>
+        <v>6991686</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -10035,17 +9900,13 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -10061,6 +9922,1389 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>125426277</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>564468</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6991658</v>
+      </c>
+      <c r="S89" t="n">
+        <v>15</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>125426278</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>564453</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6991629</v>
+      </c>
+      <c r="S90" t="n">
+        <v>15</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>125426279</v>
+      </c>
+      <c r="B91" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>564474</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6991589</v>
+      </c>
+      <c r="S91" t="n">
+        <v>15</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>125420520</v>
+      </c>
+      <c r="B92" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>564498</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6991598</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>125426249</v>
+      </c>
+      <c r="B93" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>564520</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6991682</v>
+      </c>
+      <c r="S93" t="n">
+        <v>15</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>125426250</v>
+      </c>
+      <c r="B94" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>564528</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6991624</v>
+      </c>
+      <c r="S94" t="n">
+        <v>15</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>121742429</v>
+      </c>
+      <c r="B95" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>564502</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6991645</v>
+      </c>
+      <c r="S95" t="n">
+        <v>50</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-12-25</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-12-25</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>125420527</v>
+      </c>
+      <c r="B96" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>564499</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6991597</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>125420528</v>
+      </c>
+      <c r="B97" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>564555</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6991665</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>125438549</v>
+      </c>
+      <c r="B98" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>564542</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6991657</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>125396355</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>564463</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6991617</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>125396949</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>564440</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6991655</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal dimensionsavverkningsstubbe av tall i gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>125398468</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>564441</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6991674</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>På kolad ved på två gamla tallhögstubbar</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7508-2024 artfynd.xlsx
+++ b/artfynd/A 7508-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY101"/>
+  <dimension ref="A1:AZ101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426252</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426254</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125420534</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125420543</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125399220</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125396762</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125420531</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426264</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1620,6 +1665,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426265</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1717,6 +1767,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426267</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,6 +1884,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125395850</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1946,6 +2006,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125396221</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2058,6 +2123,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125396843</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125398362</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2282,6 +2357,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125398876</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2394,6 +2474,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125420523</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426257</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2588,6 +2678,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426262</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2695,6 +2790,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125398578</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2807,6 +2907,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125420535</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2904,6 +3009,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426270</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3001,6 +3111,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426271</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3098,6 +3213,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426272</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3195,6 +3315,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426255</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3297,6 +3422,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125438544</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3398,6 +3528,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121742198</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3519,6 +3654,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125398524</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3631,6 +3771,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125420542</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3728,6 +3873,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426280</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3825,6 +3975,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426281</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3937,6 +4092,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125420530</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4049,6 +4209,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125397801</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4146,6 +4311,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426251</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4263,6 +4433,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125396883</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4375,6 +4550,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125399514</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4487,6 +4667,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125420522</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4599,6 +4784,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125397495</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4705,6 +4895,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121742191</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4807,6 +5002,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121760563</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4904,6 +5104,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121797975</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5006,6 +5211,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121798037</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5108,6 +5318,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121798188</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5205,6 +5420,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121798200</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5302,6 +5522,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122040092</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5399,6 +5624,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122040095</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5520,6 +5750,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125395199</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5632,6 +5867,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125397175</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5748,6 +5988,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125397219</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5860,6 +6105,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125397385</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5972,6 +6222,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125398434</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6084,6 +6339,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125420536</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6196,6 +6456,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125420537</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6308,6 +6573,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125420538</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6405,6 +6675,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426274</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6507,6 +6782,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125438547</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6619,6 +6899,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125420533</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6716,6 +7001,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121798890</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6813,6 +7103,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121798905</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6929,6 +7224,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125396600</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7026,6 +7326,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426260</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7123,6 +7428,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426285</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7220,6 +7530,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426286</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7322,6 +7637,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125438548</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7424,6 +7744,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121797957</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7526,6 +7851,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121798373</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7633,6 +7963,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124048482</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7750,6 +8085,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125397829</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7862,6 +8202,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125420524</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7972,6 +8317,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426258</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8074,6 +8424,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125438545</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8171,6 +8526,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426269</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8273,6 +8633,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122188793</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8375,6 +8740,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122188795</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8472,6 +8842,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122227587</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8569,6 +8944,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124048300</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8666,6 +9046,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124048336</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8763,6 +9148,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124048430</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8860,6 +9250,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124048509</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8981,6 +9376,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125396498</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9107,6 +9507,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125397089</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9233,6 +9638,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125397259</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9354,6 +9764,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125398718</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9480,6 +9895,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125399292</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9592,6 +10012,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125420539</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9704,6 +10129,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125420540</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9816,6 +10246,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125420541</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9922,6 +10357,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426276</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10028,6 +10468,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426277</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10134,6 +10579,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426278</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10240,6 +10690,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426279</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10352,6 +10807,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125420520</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10449,6 +10909,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426249</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10546,6 +11011,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125426250</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10648,6 +11118,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121742429</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10760,6 +11235,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125420527</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10872,6 +11352,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125420528</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10974,6 +11459,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125438549</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11081,6 +11571,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125396355</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11193,6 +11688,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125396949</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11305,8 +11805,115 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125398468</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>